--- a/outputs/forecast_zori_by_tract.xlsx
+++ b/outputs/forecast_zori_by_tract.xlsx
@@ -386,7 +386,7 @@
         <v>2024</v>
       </c>
       <c r="D2">
-        <v>1626.30068904614</v>
+        <v>1644.468553953432</v>
       </c>
     </row>
     <row r="3">
@@ -399,7 +399,7 @@
         <v>2025</v>
       </c>
       <c r="D3">
-        <v>1713.446369943315</v>
+        <v>1763.161141046088</v>
       </c>
     </row>
     <row r="4">
@@ -412,7 +412,7 @@
         <v>2026</v>
       </c>
       <c r="D4">
-        <v>1795.231726815591</v>
+        <v>1890.430299849529</v>
       </c>
     </row>
     <row r="5">
@@ -425,7 +425,7 @@
         <v>2027</v>
       </c>
       <c r="D5">
-        <v>1871.583075736279</v>
+        <v>2026.886416254837</v>
       </c>
     </row>
     <row r="6">
@@ -438,7 +438,7 @@
         <v>2028</v>
       </c>
       <c r="D6">
-        <v>1942.526709128603</v>
+        <v>2173.192299660101</v>
       </c>
     </row>
     <row r="7">
@@ -451,7 +451,7 @@
         <v>2024</v>
       </c>
       <c r="D7">
-        <v>2098.716461775523</v>
+        <v>1757.42838366446</v>
       </c>
     </row>
     <row r="8">
@@ -464,7 +464,7 @@
         <v>2025</v>
       </c>
       <c r="D8">
-        <v>2709.474474084494</v>
+        <v>2117.284467499186</v>
       </c>
     </row>
     <row r="9">
@@ -477,7 +477,7 @@
         <v>2026</v>
       </c>
       <c r="D9">
-        <v>3196.583313883094</v>
+        <v>2544.638293631205</v>
       </c>
     </row>
     <row r="10">
@@ -490,7 +490,7 @@
         <v>2027</v>
       </c>
       <c r="D10">
-        <v>3557.620710708716</v>
+        <v>3057.665296737886</v>
       </c>
     </row>
     <row r="11">
@@ -503,7 +503,7 @@
         <v>2028</v>
       </c>
       <c r="D11">
-        <v>3812.764482865906</v>
+        <v>3674.06896857683</v>
       </c>
     </row>
     <row r="12">
@@ -581,7 +581,7 @@
         <v>2024</v>
       </c>
       <c r="D17">
-        <v>1806.806288361841</v>
+        <v>1814.329901781613</v>
       </c>
     </row>
     <row r="18">
@@ -594,7 +594,7 @@
         <v>2025</v>
       </c>
       <c r="D18">
-        <v>1878.89808010262</v>
+        <v>1902.273283930449</v>
       </c>
     </row>
     <row r="19">
@@ -607,7 +607,7 @@
         <v>2026</v>
       </c>
       <c r="D19">
-        <v>1944.95364576163</v>
+        <v>1993.00451414605</v>
       </c>
     </row>
     <row r="20">
@@ -620,7 +620,7 @@
         <v>2027</v>
       </c>
       <c r="D20">
-        <v>2005.218591915781</v>
+        <v>2087.046528694405</v>
       </c>
     </row>
     <row r="21">
@@ -633,7 +633,7 @@
         <v>2028</v>
       </c>
       <c r="D21">
-        <v>2059.99203847562</v>
+        <v>2184.825292974867</v>
       </c>
     </row>
     <row r="22">
@@ -646,7 +646,7 @@
         <v>2024</v>
       </c>
       <c r="D22">
-        <v>1567.401954460981</v>
+        <v>2355.181216088147</v>
       </c>
     </row>
     <row r="23">
@@ -659,7 +659,7 @@
         <v>2025</v>
       </c>
       <c r="D23">
-        <v>1568.35682826726</v>
+        <v>3321.616284702291</v>
       </c>
     </row>
     <row r="24">
@@ -672,7 +672,7 @@
         <v>2026</v>
       </c>
       <c r="D24">
-        <v>1568.466832666743</v>
+        <v>4745.244669698483</v>
       </c>
     </row>
     <row r="25">
@@ -685,7 +685,7 @@
         <v>2027</v>
       </c>
       <c r="D25">
-        <v>1568.479501704835</v>
+        <v>6762.728499307351</v>
       </c>
     </row>
     <row r="26">
@@ -698,7 +698,7 @@
         <v>2028</v>
       </c>
       <c r="D26">
-        <v>1568.480960728047</v>
+        <v>9642.311540100367</v>
       </c>
     </row>
     <row r="27">
@@ -711,7 +711,7 @@
         <v>2024</v>
       </c>
       <c r="D27">
-        <v>1627.498912533883</v>
+        <v>1644.498802468367</v>
       </c>
     </row>
     <row r="28">
@@ -724,7 +724,7 @@
         <v>2025</v>
       </c>
       <c r="D28">
-        <v>1683.041745242904</v>
+        <v>1730.871181668455</v>
       </c>
     </row>
     <row r="29">
@@ -737,7 +737,7 @@
         <v>2026</v>
       </c>
       <c r="D29">
-        <v>1732.654040772479</v>
+        <v>1823.502283141811</v>
       </c>
     </row>
     <row r="30">
@@ -750,7 +750,7 @@
         <v>2027</v>
       </c>
       <c r="D30">
-        <v>1776.78324590902</v>
+        <v>1921.93427335516</v>
       </c>
     </row>
     <row r="31">
@@ -763,7 +763,7 @@
         <v>2028</v>
       </c>
       <c r="D31">
-        <v>1815.892834275332</v>
+        <v>2026.092773112435</v>
       </c>
     </row>
     <row r="32">
@@ -776,7 +776,7 @@
         <v>2024</v>
       </c>
       <c r="D32">
-        <v>1818.36205577563</v>
+        <v>1959.108558761297</v>
       </c>
     </row>
     <row r="33">
@@ -789,7 +789,7 @@
         <v>2025</v>
       </c>
       <c r="D33">
-        <v>1845.091995511237</v>
+        <v>2078.81819665978</v>
       </c>
     </row>
     <row r="34">
@@ -802,7 +802,7 @@
         <v>2026</v>
       </c>
       <c r="D34">
-        <v>1863.600481427878</v>
+        <v>2251.938876374856</v>
       </c>
     </row>
     <row r="35">
@@ -815,7 +815,7 @@
         <v>2027</v>
       </c>
       <c r="D35">
-        <v>1876.366589122505</v>
+        <v>2411.116371843525</v>
       </c>
     </row>
     <row r="36">
@@ -828,7 +828,7 @@
         <v>2028</v>
       </c>
       <c r="D36">
-        <v>1885.14858397586</v>
+        <v>2598.670188862621</v>
       </c>
     </row>
     <row r="37">
@@ -841,7 +841,7 @@
         <v>2024</v>
       </c>
       <c r="D37">
-        <v>1818.362055775627</v>
+        <v>1959.108558950705</v>
       </c>
     </row>
     <row r="38">
@@ -854,7 +854,7 @@
         <v>2025</v>
       </c>
       <c r="D38">
-        <v>1845.091995511232</v>
+        <v>2078.818196945787</v>
       </c>
     </row>
     <row r="39">
@@ -867,7 +867,7 @@
         <v>2026</v>
       </c>
       <c r="D39">
-        <v>1863.600481427871</v>
+        <v>2251.938876849233</v>
       </c>
     </row>
     <row r="40">
@@ -880,7 +880,7 @@
         <v>2027</v>
       </c>
       <c r="D40">
-        <v>1876.366589122498</v>
+        <v>2411.116372482898</v>
       </c>
     </row>
     <row r="41">
@@ -893,7 +893,7 @@
         <v>2028</v>
       </c>
       <c r="D41">
-        <v>1885.148583975853</v>
+        <v>2598.670189721193</v>
       </c>
     </row>
     <row r="42">
@@ -906,7 +906,7 @@
         <v>2024</v>
       </c>
       <c r="D42">
-        <v>1818.362055775627</v>
+        <v>1959.108558950705</v>
       </c>
     </row>
     <row r="43">
@@ -919,7 +919,7 @@
         <v>2025</v>
       </c>
       <c r="D43">
-        <v>1845.091995511232</v>
+        <v>2078.818196945787</v>
       </c>
     </row>
     <row r="44">
@@ -932,7 +932,7 @@
         <v>2026</v>
       </c>
       <c r="D44">
-        <v>1863.600481427871</v>
+        <v>2251.938876849233</v>
       </c>
     </row>
     <row r="45">
@@ -945,7 +945,7 @@
         <v>2027</v>
       </c>
       <c r="D45">
-        <v>1876.366589122498</v>
+        <v>2411.116372482898</v>
       </c>
     </row>
     <row r="46">
@@ -958,7 +958,7 @@
         <v>2028</v>
       </c>
       <c r="D46">
-        <v>1885.148583975853</v>
+        <v>2598.670189721193</v>
       </c>
     </row>
     <row r="47">
@@ -971,7 +971,7 @@
         <v>2024</v>
       </c>
       <c r="D47">
-        <v>1818.362055775627</v>
+        <v>1959.108558950705</v>
       </c>
     </row>
     <row r="48">
@@ -984,7 +984,7 @@
         <v>2025</v>
       </c>
       <c r="D48">
-        <v>1845.091995511232</v>
+        <v>2078.818196945787</v>
       </c>
     </row>
     <row r="49">
@@ -997,7 +997,7 @@
         <v>2026</v>
       </c>
       <c r="D49">
-        <v>1863.600481427871</v>
+        <v>2251.938876849233</v>
       </c>
     </row>
     <row r="50">
@@ -1010,7 +1010,7 @@
         <v>2027</v>
       </c>
       <c r="D50">
-        <v>1876.366589122498</v>
+        <v>2411.116372482898</v>
       </c>
     </row>
     <row r="51">
@@ -1023,7 +1023,7 @@
         <v>2028</v>
       </c>
       <c r="D51">
-        <v>1885.148583975853</v>
+        <v>2598.670189721193</v>
       </c>
     </row>
     <row r="52">
@@ -1036,7 +1036,7 @@
         <v>2024</v>
       </c>
       <c r="D52">
-        <v>1818.362055775627</v>
+        <v>1959.108558950705</v>
       </c>
     </row>
     <row r="53">
@@ -1049,7 +1049,7 @@
         <v>2025</v>
       </c>
       <c r="D53">
-        <v>1845.091995511232</v>
+        <v>2078.818196945787</v>
       </c>
     </row>
     <row r="54">
@@ -1062,7 +1062,7 @@
         <v>2026</v>
       </c>
       <c r="D54">
-        <v>1863.600481427871</v>
+        <v>2251.938876849233</v>
       </c>
     </row>
     <row r="55">
@@ -1075,7 +1075,7 @@
         <v>2027</v>
       </c>
       <c r="D55">
-        <v>1876.366589122498</v>
+        <v>2411.116372482898</v>
       </c>
     </row>
     <row r="56">
@@ -1088,7 +1088,7 @@
         <v>2028</v>
       </c>
       <c r="D56">
-        <v>1885.148583975853</v>
+        <v>2598.670189721193</v>
       </c>
     </row>
     <row r="57">
@@ -1101,7 +1101,7 @@
         <v>2024</v>
       </c>
       <c r="D57">
-        <v>1818.362055775627</v>
+        <v>1959.108558950705</v>
       </c>
     </row>
     <row r="58">
@@ -1114,7 +1114,7 @@
         <v>2025</v>
       </c>
       <c r="D58">
-        <v>1845.091995511232</v>
+        <v>2078.818196945787</v>
       </c>
     </row>
     <row r="59">
@@ -1127,7 +1127,7 @@
         <v>2026</v>
       </c>
       <c r="D59">
-        <v>1863.600481427871</v>
+        <v>2251.938876849233</v>
       </c>
     </row>
     <row r="60">
@@ -1140,7 +1140,7 @@
         <v>2027</v>
       </c>
       <c r="D60">
-        <v>1876.366589122498</v>
+        <v>2411.116372482898</v>
       </c>
     </row>
     <row r="61">
@@ -1153,7 +1153,7 @@
         <v>2028</v>
       </c>
       <c r="D61">
-        <v>1885.148583975853</v>
+        <v>2598.670189721193</v>
       </c>
     </row>
     <row r="62">
@@ -1166,7 +1166,7 @@
         <v>2024</v>
       </c>
       <c r="D62">
-        <v>1626.30068904614</v>
+        <v>1644.468553953432</v>
       </c>
     </row>
     <row r="63">
@@ -1179,7 +1179,7 @@
         <v>2025</v>
       </c>
       <c r="D63">
-        <v>1713.446369943315</v>
+        <v>1763.161141046088</v>
       </c>
     </row>
     <row r="64">
@@ -1192,7 +1192,7 @@
         <v>2026</v>
       </c>
       <c r="D64">
-        <v>1795.231726815591</v>
+        <v>1890.430299849529</v>
       </c>
     </row>
     <row r="65">
@@ -1205,7 +1205,7 @@
         <v>2027</v>
       </c>
       <c r="D65">
-        <v>1871.583075736279</v>
+        <v>2026.886416254837</v>
       </c>
     </row>
     <row r="66">
@@ -1218,7 +1218,7 @@
         <v>2028</v>
       </c>
       <c r="D66">
-        <v>1942.526709128603</v>
+        <v>2173.192299660101</v>
       </c>
     </row>
     <row r="67">
@@ -1231,7 +1231,7 @@
         <v>2024</v>
       </c>
       <c r="D67">
-        <v>1626.30068904614</v>
+        <v>1644.468553953432</v>
       </c>
     </row>
     <row r="68">
@@ -1244,7 +1244,7 @@
         <v>2025</v>
       </c>
       <c r="D68">
-        <v>1713.446369943315</v>
+        <v>1763.161141046088</v>
       </c>
     </row>
     <row r="69">
@@ -1257,7 +1257,7 @@
         <v>2026</v>
       </c>
       <c r="D69">
-        <v>1795.231726815591</v>
+        <v>1890.430299849529</v>
       </c>
     </row>
     <row r="70">
@@ -1270,7 +1270,7 @@
         <v>2027</v>
       </c>
       <c r="D70">
-        <v>1871.583075736279</v>
+        <v>2026.886416254837</v>
       </c>
     </row>
     <row r="71">
@@ -1283,7 +1283,7 @@
         <v>2028</v>
       </c>
       <c r="D71">
-        <v>1942.526709128603</v>
+        <v>2173.192299660101</v>
       </c>
     </row>
     <row r="72">
@@ -1296,7 +1296,7 @@
         <v>2024</v>
       </c>
       <c r="D72">
-        <v>1841.689178953759</v>
+        <v>1741.268792148544</v>
       </c>
     </row>
     <row r="73">
@@ -1309,7 +1309,7 @@
         <v>2025</v>
       </c>
       <c r="D73">
-        <v>2296.433572292714</v>
+        <v>1986.478050560071</v>
       </c>
     </row>
     <row r="74">
@@ -1322,7 +1322,7 @@
         <v>2026</v>
       </c>
       <c r="D74">
-        <v>2878.236851146735</v>
+        <v>2243.746657681485</v>
       </c>
     </row>
     <row r="75">
@@ -1335,7 +1335,7 @@
         <v>2027</v>
       </c>
       <c r="D75">
-        <v>3588.707743944807</v>
+        <v>2516.354758902272</v>
       </c>
     </row>
     <row r="76">
@@ -1348,7 +1348,7 @@
         <v>2028</v>
       </c>
       <c r="D76">
-        <v>4418.37975195226</v>
+        <v>2807.765879089211</v>
       </c>
     </row>
     <row r="77">
@@ -1361,7 +1361,7 @@
         <v>2024</v>
       </c>
       <c r="D77">
-        <v>1649.806290672259</v>
+        <v>2105.957648999421</v>
       </c>
     </row>
     <row r="78">
@@ -1374,7 +1374,7 @@
         <v>2025</v>
       </c>
       <c r="D78">
-        <v>1650.344897770776</v>
+        <v>2587.640519698002</v>
       </c>
     </row>
     <row r="79">
@@ -1387,7 +1387,7 @@
         <v>2026</v>
       </c>
       <c r="D79">
-        <v>1650.38707848274</v>
+        <v>3208.805319116781</v>
       </c>
     </row>
     <row r="80">
@@ -1400,7 +1400,7 @@
         <v>2027</v>
       </c>
       <c r="D80">
-        <v>1650.390381305705</v>
+        <v>3971.169387048634</v>
       </c>
     </row>
     <row r="81">
@@ -1413,7 +1413,7 @@
         <v>2028</v>
       </c>
       <c r="D81">
-        <v>1650.390639919191</v>
+        <v>4916.781875690301</v>
       </c>
     </row>
     <row r="82">
@@ -1426,7 +1426,7 @@
         <v>2024</v>
       </c>
       <c r="D82">
-        <v>1567.928694920326</v>
+        <v>1580.480628691744</v>
       </c>
     </row>
     <row r="83">
@@ -1439,7 +1439,7 @@
         <v>2025</v>
       </c>
       <c r="D83">
-        <v>1672.071835941488</v>
+        <v>1715.722457254926</v>
       </c>
     </row>
     <row r="84">
@@ -1452,7 +1452,7 @@
         <v>2026</v>
       </c>
       <c r="D84">
-        <v>1758.432306222344</v>
+        <v>1854.825336237524</v>
       </c>
     </row>
     <row r="85">
@@ -1465,7 +1465,7 @@
         <v>2027</v>
       </c>
       <c r="D85">
-        <v>1826.704450249382</v>
+        <v>1998.185483823784</v>
       </c>
     </row>
     <row r="86">
@@ -1478,7 +1478,7 @@
         <v>2028</v>
       </c>
       <c r="D86">
-        <v>1878.299766579584</v>
+        <v>2146.253166782889</v>
       </c>
     </row>
     <row r="87">
@@ -1491,7 +1491,7 @@
         <v>2024</v>
       </c>
       <c r="D87">
-        <v>1567.928694920326</v>
+        <v>1580.480628691744</v>
       </c>
     </row>
     <row r="88">
@@ -1504,7 +1504,7 @@
         <v>2025</v>
       </c>
       <c r="D88">
-        <v>1672.071835941488</v>
+        <v>1715.722457254926</v>
       </c>
     </row>
     <row r="89">
@@ -1517,7 +1517,7 @@
         <v>2026</v>
       </c>
       <c r="D89">
-        <v>1758.432306222344</v>
+        <v>1854.825336237524</v>
       </c>
     </row>
     <row r="90">
@@ -1530,7 +1530,7 @@
         <v>2027</v>
       </c>
       <c r="D90">
-        <v>1826.704450249382</v>
+        <v>1998.185483823784</v>
       </c>
     </row>
     <row r="91">
@@ -1543,7 +1543,7 @@
         <v>2028</v>
       </c>
       <c r="D91">
-        <v>1878.299766579584</v>
+        <v>2146.253166782889</v>
       </c>
     </row>
     <row r="92">
@@ -1556,7 +1556,7 @@
         <v>2024</v>
       </c>
       <c r="D92">
-        <v>1818.362055463449</v>
+        <v>1959.108558844554</v>
       </c>
     </row>
     <row r="93">
@@ -1569,7 +1569,7 @@
         <v>2025</v>
       </c>
       <c r="D93">
-        <v>1845.091994761147</v>
+        <v>2078.818196807201</v>
       </c>
     </row>
     <row r="94">
@@ -1582,7 +1582,7 @@
         <v>2026</v>
       </c>
       <c r="D94">
-        <v>1863.600480221235</v>
+        <v>2251.938876603812</v>
       </c>
     </row>
     <row r="95">
@@ -1595,7 +1595,7 @@
         <v>2027</v>
       </c>
       <c r="D95">
-        <v>1876.366587495294</v>
+        <v>2411.116372167298</v>
       </c>
     </row>
     <row r="96">
@@ -1608,7 +1608,7 @@
         <v>2028</v>
       </c>
       <c r="D96">
-        <v>1885.148581986879</v>
+        <v>2598.670189288926</v>
       </c>
     </row>
     <row r="97">
@@ -1621,7 +1621,7 @@
         <v>2024</v>
       </c>
       <c r="D97">
-        <v>1626.30068904614</v>
+        <v>1644.468553953432</v>
       </c>
     </row>
     <row r="98">
@@ -1634,7 +1634,7 @@
         <v>2025</v>
       </c>
       <c r="D98">
-        <v>1713.446369943315</v>
+        <v>1763.161141046088</v>
       </c>
     </row>
     <row r="99">
@@ -1647,7 +1647,7 @@
         <v>2026</v>
       </c>
       <c r="D99">
-        <v>1795.231726815591</v>
+        <v>1890.430299849529</v>
       </c>
     </row>
     <row r="100">
@@ -1660,7 +1660,7 @@
         <v>2027</v>
       </c>
       <c r="D100">
-        <v>1871.583075736279</v>
+        <v>2026.886416254837</v>
       </c>
     </row>
     <row r="101">
@@ -1673,7 +1673,7 @@
         <v>2028</v>
       </c>
       <c r="D101">
-        <v>1942.526709128603</v>
+        <v>2173.192299660101</v>
       </c>
     </row>
     <row r="102">
@@ -1686,7 +1686,7 @@
         <v>2024</v>
       </c>
       <c r="D102">
-        <v>1626.30068904614</v>
+        <v>1644.468553953432</v>
       </c>
     </row>
     <row r="103">
@@ -1699,7 +1699,7 @@
         <v>2025</v>
       </c>
       <c r="D103">
-        <v>1713.446369943315</v>
+        <v>1763.161141046088</v>
       </c>
     </row>
     <row r="104">
@@ -1712,7 +1712,7 @@
         <v>2026</v>
       </c>
       <c r="D104">
-        <v>1795.231726815591</v>
+        <v>1890.430299849529</v>
       </c>
     </row>
     <row r="105">
@@ -1725,7 +1725,7 @@
         <v>2027</v>
       </c>
       <c r="D105">
-        <v>1871.583075736279</v>
+        <v>2026.886416254837</v>
       </c>
     </row>
     <row r="106">
@@ -1738,7 +1738,7 @@
         <v>2028</v>
       </c>
       <c r="D106">
-        <v>1942.526709128603</v>
+        <v>2173.192299660101</v>
       </c>
     </row>
     <row r="107">
@@ -1816,7 +1816,7 @@
         <v>2024</v>
       </c>
       <c r="D112">
-        <v>1567.928694920326</v>
+        <v>1580.480628691744</v>
       </c>
     </row>
     <row r="113">
@@ -1829,7 +1829,7 @@
         <v>2025</v>
       </c>
       <c r="D113">
-        <v>1672.071835941488</v>
+        <v>1715.722457254926</v>
       </c>
     </row>
     <row r="114">
@@ -1842,7 +1842,7 @@
         <v>2026</v>
       </c>
       <c r="D114">
-        <v>1758.432306222344</v>
+        <v>1854.825336237524</v>
       </c>
     </row>
     <row r="115">
@@ -1855,7 +1855,7 @@
         <v>2027</v>
       </c>
       <c r="D115">
-        <v>1826.704450249382</v>
+        <v>1998.185483823784</v>
       </c>
     </row>
     <row r="116">
@@ -1868,7 +1868,7 @@
         <v>2028</v>
       </c>
       <c r="D116">
-        <v>1878.299766579584</v>
+        <v>2146.253166782889</v>
       </c>
     </row>
     <row r="117">
@@ -1881,7 +1881,7 @@
         <v>2024</v>
       </c>
       <c r="D117">
-        <v>1567.928694920326</v>
+        <v>1580.480628691744</v>
       </c>
     </row>
     <row r="118">
@@ -1894,7 +1894,7 @@
         <v>2025</v>
       </c>
       <c r="D118">
-        <v>1672.071835941488</v>
+        <v>1715.722457254926</v>
       </c>
     </row>
     <row r="119">
@@ -1907,7 +1907,7 @@
         <v>2026</v>
       </c>
       <c r="D119">
-        <v>1758.432306222344</v>
+        <v>1854.825336237524</v>
       </c>
     </row>
     <row r="120">
@@ -1920,7 +1920,7 @@
         <v>2027</v>
       </c>
       <c r="D120">
-        <v>1826.704450249382</v>
+        <v>1998.185483823784</v>
       </c>
     </row>
     <row r="121">
@@ -1933,7 +1933,7 @@
         <v>2028</v>
       </c>
       <c r="D121">
-        <v>1878.299766579584</v>
+        <v>2146.253166782889</v>
       </c>
     </row>
     <row r="122">
@@ -1946,7 +1946,7 @@
         <v>2024</v>
       </c>
       <c r="D122">
-        <v>431.8440732598782</v>
+        <v>435.3023740847439</v>
       </c>
     </row>
     <row r="123">
@@ -1959,7 +1959,7 @@
         <v>2025</v>
       </c>
       <c r="D123">
-        <v>460.5259056958702</v>
+        <v>472.5523918214014</v>
       </c>
     </row>
     <row r="124">
@@ -1972,7 +1972,7 @@
         <v>2026</v>
       </c>
       <c r="D124">
-        <v>484.3087027777429</v>
+        <v>510.8664416287972</v>
       </c>
     </row>
     <row r="125">
@@ -1985,7 +1985,7 @@
         <v>2027</v>
       </c>
       <c r="D125">
-        <v>503.1083452078291</v>
+        <v>550.3536454071582</v>
       </c>
     </row>
     <row r="126">
@@ -1998,7 +1998,7 @@
         <v>2028</v>
       </c>
       <c r="D126">
-        <v>517.3138647629517</v>
+        <v>591.1380113638962</v>
       </c>
     </row>
     <row r="127">
@@ -2011,7 +2011,7 @@
         <v>2024</v>
       </c>
       <c r="D127">
-        <v>1567.928694920326</v>
+        <v>1580.480628691744</v>
       </c>
     </row>
     <row r="128">
@@ -2024,7 +2024,7 @@
         <v>2025</v>
       </c>
       <c r="D128">
-        <v>1672.071835941488</v>
+        <v>1715.722457254926</v>
       </c>
     </row>
     <row r="129">
@@ -2037,7 +2037,7 @@
         <v>2026</v>
       </c>
       <c r="D129">
-        <v>1758.432306222344</v>
+        <v>1854.825336237524</v>
       </c>
     </row>
     <row r="130">
@@ -2050,7 +2050,7 @@
         <v>2027</v>
       </c>
       <c r="D130">
-        <v>1826.704450249382</v>
+        <v>1998.185483823784</v>
       </c>
     </row>
     <row r="131">
@@ -2063,7 +2063,7 @@
         <v>2028</v>
       </c>
       <c r="D131">
-        <v>1878.299766579584</v>
+        <v>2146.253166782889</v>
       </c>
     </row>
     <row r="132">
@@ -2076,7 +2076,7 @@
         <v>2024</v>
       </c>
       <c r="D132">
-        <v>1567.928694920326</v>
+        <v>1580.480628691744</v>
       </c>
     </row>
     <row r="133">
@@ -2089,7 +2089,7 @@
         <v>2025</v>
       </c>
       <c r="D133">
-        <v>1672.071835941488</v>
+        <v>1715.722457254926</v>
       </c>
     </row>
     <row r="134">
@@ -2102,7 +2102,7 @@
         <v>2026</v>
       </c>
       <c r="D134">
-        <v>1758.432306222344</v>
+        <v>1854.825336237524</v>
       </c>
     </row>
     <row r="135">
@@ -2115,7 +2115,7 @@
         <v>2027</v>
       </c>
       <c r="D135">
-        <v>1826.704450249382</v>
+        <v>1998.185483823784</v>
       </c>
     </row>
     <row r="136">
@@ -2128,7 +2128,7 @@
         <v>2028</v>
       </c>
       <c r="D136">
-        <v>1878.299766579584</v>
+        <v>2146.253166782889</v>
       </c>
     </row>
     <row r="137">
@@ -2141,7 +2141,7 @@
         <v>2024</v>
       </c>
       <c r="D137">
-        <v>189.9535629033933</v>
+        <v>191.4751058566193</v>
       </c>
     </row>
     <row r="138">
@@ -2154,7 +2154,7 @@
         <v>2025</v>
       </c>
       <c r="D138">
-        <v>202.5692491947704</v>
+        <v>207.8604829510099</v>
       </c>
     </row>
     <row r="139">
@@ -2167,7 +2167,7 @@
         <v>2026</v>
       </c>
       <c r="D139">
-        <v>213.0296576767257</v>
+        <v>224.7140627032163</v>
       </c>
     </row>
     <row r="140">
@@ -2180,7 +2180,7 @@
         <v>2027</v>
       </c>
       <c r="D140">
-        <v>221.2978178729912</v>
+        <v>242.0838425469961</v>
       </c>
     </row>
     <row r="141">
@@ -2193,7 +2193,7 @@
         <v>2028</v>
       </c>
       <c r="D141">
-        <v>227.5449367111854</v>
+        <v>260.0243679157559</v>
       </c>
     </row>
     <row r="142">
@@ -2206,7 +2206,7 @@
         <v>2024</v>
       </c>
       <c r="D142">
-        <v>1567.928694920326</v>
+        <v>1580.480628691744</v>
       </c>
     </row>
     <row r="143">
@@ -2219,7 +2219,7 @@
         <v>2025</v>
       </c>
       <c r="D143">
-        <v>1672.071835941488</v>
+        <v>1715.722457254926</v>
       </c>
     </row>
     <row r="144">
@@ -2232,7 +2232,7 @@
         <v>2026</v>
       </c>
       <c r="D144">
-        <v>1758.432306222344</v>
+        <v>1854.825336237524</v>
       </c>
     </row>
     <row r="145">
@@ -2245,7 +2245,7 @@
         <v>2027</v>
       </c>
       <c r="D145">
-        <v>1826.704450249382</v>
+        <v>1998.185483823784</v>
       </c>
     </row>
     <row r="146">
@@ -2258,7 +2258,7 @@
         <v>2028</v>
       </c>
       <c r="D146">
-        <v>1878.299766579584</v>
+        <v>2146.253166782889</v>
       </c>
     </row>
     <row r="147">
@@ -2271,7 +2271,7 @@
         <v>2024</v>
       </c>
       <c r="D147">
-        <v>1418.684782750858</v>
+        <v>1423.43870265197</v>
       </c>
     </row>
     <row r="148">
@@ -2284,7 +2284,7 @@
         <v>2025</v>
       </c>
       <c r="D148">
-        <v>1483.830626214999</v>
+        <v>1499.675355721979</v>
       </c>
     </row>
     <row r="149">
@@ -2297,7 +2297,7 @@
         <v>2026</v>
       </c>
       <c r="D149">
-        <v>1544.675801774838</v>
+        <v>1578.890946554981</v>
       </c>
     </row>
     <row r="150">
@@ -2310,7 +2310,7 @@
         <v>2027</v>
       </c>
       <c r="D150">
-        <v>1601.25136708791</v>
+        <v>1661.680473703892</v>
       </c>
     </row>
     <row r="151">
@@ -2323,7 +2323,7 @@
         <v>2028</v>
       </c>
       <c r="D151">
-        <v>1653.647350681857</v>
+        <v>1748.473711909423</v>
       </c>
     </row>
     <row r="152">
@@ -2336,7 +2336,7 @@
         <v>2024</v>
       </c>
       <c r="D152">
-        <v>1418.684782750858</v>
+        <v>1423.43870265197</v>
       </c>
     </row>
     <row r="153">
@@ -2349,7 +2349,7 @@
         <v>2025</v>
       </c>
       <c r="D153">
-        <v>1483.830626214999</v>
+        <v>1499.675355721979</v>
       </c>
     </row>
     <row r="154">
@@ -2362,7 +2362,7 @@
         <v>2026</v>
       </c>
       <c r="D154">
-        <v>1544.675801774838</v>
+        <v>1578.890946554981</v>
       </c>
     </row>
     <row r="155">
@@ -2375,7 +2375,7 @@
         <v>2027</v>
       </c>
       <c r="D155">
-        <v>1601.25136708791</v>
+        <v>1661.680473703892</v>
       </c>
     </row>
     <row r="156">
@@ -2388,7 +2388,7 @@
         <v>2028</v>
       </c>
       <c r="D156">
-        <v>1653.647350681857</v>
+        <v>1748.473711909423</v>
       </c>
     </row>
     <row r="157">
@@ -2401,7 +2401,7 @@
         <v>2024</v>
       </c>
       <c r="D157">
-        <v>1418.684782750858</v>
+        <v>1423.43870265197</v>
       </c>
     </row>
     <row r="158">
@@ -2414,7 +2414,7 @@
         <v>2025</v>
       </c>
       <c r="D158">
-        <v>1483.830626214999</v>
+        <v>1499.675355721979</v>
       </c>
     </row>
     <row r="159">
@@ -2427,7 +2427,7 @@
         <v>2026</v>
       </c>
       <c r="D159">
-        <v>1544.675801774838</v>
+        <v>1578.890946554981</v>
       </c>
     </row>
     <row r="160">
@@ -2440,7 +2440,7 @@
         <v>2027</v>
       </c>
       <c r="D160">
-        <v>1601.25136708791</v>
+        <v>1661.680473703892</v>
       </c>
     </row>
     <row r="161">
@@ -2453,7 +2453,7 @@
         <v>2028</v>
       </c>
       <c r="D161">
-        <v>1653.647350681857</v>
+        <v>1748.473711909423</v>
       </c>
     </row>
     <row r="162">
@@ -2466,7 +2466,7 @@
         <v>2024</v>
       </c>
       <c r="D162">
-        <v>1418.684782750858</v>
+        <v>1423.43870265197</v>
       </c>
     </row>
     <row r="163">
@@ -2479,7 +2479,7 @@
         <v>2025</v>
       </c>
       <c r="D163">
-        <v>1483.830626214999</v>
+        <v>1499.675355721979</v>
       </c>
     </row>
     <row r="164">
@@ -2492,7 +2492,7 @@
         <v>2026</v>
       </c>
       <c r="D164">
-        <v>1544.675801774838</v>
+        <v>1578.890946554981</v>
       </c>
     </row>
     <row r="165">
@@ -2505,7 +2505,7 @@
         <v>2027</v>
       </c>
       <c r="D165">
-        <v>1601.25136708791</v>
+        <v>1661.680473703892</v>
       </c>
     </row>
     <row r="166">
@@ -2518,7 +2518,7 @@
         <v>2028</v>
       </c>
       <c r="D166">
-        <v>1653.647350681857</v>
+        <v>1748.473711909423</v>
       </c>
     </row>
     <row r="167">
@@ -2531,7 +2531,7 @@
         <v>2024</v>
       </c>
       <c r="D167">
-        <v>1418.684782750858</v>
+        <v>1423.43870265197</v>
       </c>
     </row>
     <row r="168">
@@ -2544,7 +2544,7 @@
         <v>2025</v>
       </c>
       <c r="D168">
-        <v>1483.830626214999</v>
+        <v>1499.675355721979</v>
       </c>
     </row>
     <row r="169">
@@ -2557,7 +2557,7 @@
         <v>2026</v>
       </c>
       <c r="D169">
-        <v>1544.675801774838</v>
+        <v>1578.890946554981</v>
       </c>
     </row>
     <row r="170">
@@ -2570,7 +2570,7 @@
         <v>2027</v>
       </c>
       <c r="D170">
-        <v>1601.25136708791</v>
+        <v>1661.680473703892</v>
       </c>
     </row>
     <row r="171">
@@ -2583,7 +2583,7 @@
         <v>2028</v>
       </c>
       <c r="D171">
-        <v>1653.647350681857</v>
+        <v>1748.473711909423</v>
       </c>
     </row>
     <row r="172">
@@ -2596,7 +2596,7 @@
         <v>2024</v>
       </c>
       <c r="D172">
-        <v>1418.684782750858</v>
+        <v>1423.43870265197</v>
       </c>
     </row>
     <row r="173">
@@ -2609,7 +2609,7 @@
         <v>2025</v>
       </c>
       <c r="D173">
-        <v>1483.830626214999</v>
+        <v>1499.675355721979</v>
       </c>
     </row>
     <row r="174">
@@ -2622,7 +2622,7 @@
         <v>2026</v>
       </c>
       <c r="D174">
-        <v>1544.675801774838</v>
+        <v>1578.890946554981</v>
       </c>
     </row>
     <row r="175">
@@ -2635,7 +2635,7 @@
         <v>2027</v>
       </c>
       <c r="D175">
-        <v>1601.25136708791</v>
+        <v>1661.680473703892</v>
       </c>
     </row>
     <row r="176">
@@ -2648,7 +2648,7 @@
         <v>2028</v>
       </c>
       <c r="D176">
-        <v>1653.647350681857</v>
+        <v>1748.473711909423</v>
       </c>
     </row>
     <row r="177">
@@ -2661,7 +2661,7 @@
         <v>2024</v>
       </c>
       <c r="D177">
-        <v>1418.684782750858</v>
+        <v>1423.43870265197</v>
       </c>
     </row>
     <row r="178">
@@ -2674,7 +2674,7 @@
         <v>2025</v>
       </c>
       <c r="D178">
-        <v>1483.830626214999</v>
+        <v>1499.675355721979</v>
       </c>
     </row>
     <row r="179">
@@ -2687,7 +2687,7 @@
         <v>2026</v>
       </c>
       <c r="D179">
-        <v>1544.675801774838</v>
+        <v>1578.890946554981</v>
       </c>
     </row>
     <row r="180">
@@ -2700,7 +2700,7 @@
         <v>2027</v>
       </c>
       <c r="D180">
-        <v>1601.25136708791</v>
+        <v>1661.680473703892</v>
       </c>
     </row>
     <row r="181">
@@ -2713,7 +2713,7 @@
         <v>2028</v>
       </c>
       <c r="D181">
-        <v>1653.647350681857</v>
+        <v>1748.473711909423</v>
       </c>
     </row>
     <row r="182">
@@ -2726,7 +2726,7 @@
         <v>2024</v>
       </c>
       <c r="D182">
-        <v>1419.719844958258</v>
+        <v>1424.043776903807</v>
       </c>
     </row>
     <row r="183">
@@ -2739,7 +2739,7 @@
         <v>2025</v>
       </c>
       <c r="D183">
-        <v>1486.121309674693</v>
+        <v>1500.789972374102</v>
       </c>
     </row>
     <row r="184">
@@ -2752,7 +2752,7 @@
         <v>2026</v>
       </c>
       <c r="D184">
-        <v>1548.360178351089</v>
+        <v>1580.426970497163</v>
       </c>
     </row>
     <row r="185">
@@ -2765,7 +2765,7 @@
         <v>2027</v>
       </c>
       <c r="D185">
-        <v>1606.438955237667</v>
+        <v>1663.591221850225</v>
       </c>
     </row>
     <row r="186">
@@ -2778,7 +2778,7 @@
         <v>2028</v>
       </c>
       <c r="D186">
-        <v>1660.420138686616</v>
+        <v>1750.739884965813</v>
       </c>
     </row>
     <row r="187">
@@ -2921,7 +2921,7 @@
         <v>2024</v>
       </c>
       <c r="D197">
-        <v>47.08745940929278</v>
+        <v>36.44487223840751</v>
       </c>
     </row>
     <row r="198">
@@ -2934,7 +2934,7 @@
         <v>2025</v>
       </c>
       <c r="D198">
-        <v>58.59975551524154</v>
+        <v>47.58415943539487</v>
       </c>
     </row>
     <row r="199">
@@ -2947,7 +2947,7 @@
         <v>2026</v>
       </c>
       <c r="D199">
-        <v>64.70136842090439</v>
+        <v>62.01032375857496</v>
       </c>
     </row>
     <row r="200">
@@ -2960,7 +2960,7 @@
         <v>2027</v>
       </c>
       <c r="D200">
-        <v>67.66974729910237</v>
+        <v>80.81738427187824</v>
       </c>
     </row>
     <row r="201">
@@ -2973,7 +2973,7 @@
         <v>2028</v>
       </c>
       <c r="D201">
-        <v>69.05844745196963</v>
+        <v>105.3279708854244</v>
       </c>
     </row>
     <row r="202">
@@ -3116,7 +3116,7 @@
         <v>2024</v>
       </c>
       <c r="D212">
-        <v>1315.379818890941</v>
+        <v>1947.899985060439</v>
       </c>
     </row>
     <row r="213">
@@ -3129,7 +3129,7 @@
         <v>2025</v>
       </c>
       <c r="D213">
-        <v>1315.460858441167</v>
+        <v>2736.397571587979</v>
       </c>
     </row>
     <row r="214">
@@ -3142,7 +3142,7 @@
         <v>2026</v>
       </c>
       <c r="D214">
-        <v>1315.463176395507</v>
+        <v>3880.498523917504</v>
       </c>
     </row>
     <row r="215">
@@ -3155,7 +3155,7 @@
         <v>2027</v>
       </c>
       <c r="D215">
-        <v>1315.463242693345</v>
+        <v>5494.044000185818</v>
       </c>
     </row>
     <row r="216">
@@ -3168,7 +3168,7 @@
         <v>2028</v>
       </c>
       <c r="D216">
-        <v>1315.463244589586</v>
+        <v>7780.681760846879</v>
       </c>
     </row>
     <row r="217">
@@ -3181,7 +3181,7 @@
         <v>2024</v>
       </c>
       <c r="D217">
-        <v>1418.684782750858</v>
+        <v>1423.43870265197</v>
       </c>
     </row>
     <row r="218">
@@ -3194,7 +3194,7 @@
         <v>2025</v>
       </c>
       <c r="D218">
-        <v>1483.830626214999</v>
+        <v>1499.675355721979</v>
       </c>
     </row>
     <row r="219">
@@ -3207,7 +3207,7 @@
         <v>2026</v>
       </c>
       <c r="D219">
-        <v>1544.675801774838</v>
+        <v>1578.890946554981</v>
       </c>
     </row>
     <row r="220">
@@ -3220,7 +3220,7 @@
         <v>2027</v>
       </c>
       <c r="D220">
-        <v>1601.25136708791</v>
+        <v>1661.680473703892</v>
       </c>
     </row>
     <row r="221">
@@ -3233,7 +3233,7 @@
         <v>2028</v>
       </c>
       <c r="D221">
-        <v>1653.647350681857</v>
+        <v>1748.473711909423</v>
       </c>
     </row>
     <row r="222">
@@ -3246,7 +3246,7 @@
         <v>2024</v>
       </c>
       <c r="D222">
-        <v>1418.684782750858</v>
+        <v>1423.43870265197</v>
       </c>
     </row>
     <row r="223">
@@ -3259,7 +3259,7 @@
         <v>2025</v>
       </c>
       <c r="D223">
-        <v>1483.830626214999</v>
+        <v>1499.675355721979</v>
       </c>
     </row>
     <row r="224">
@@ -3272,7 +3272,7 @@
         <v>2026</v>
       </c>
       <c r="D224">
-        <v>1544.675801774838</v>
+        <v>1578.890946554981</v>
       </c>
     </row>
     <row r="225">
@@ -3285,7 +3285,7 @@
         <v>2027</v>
       </c>
       <c r="D225">
-        <v>1601.25136708791</v>
+        <v>1661.680473703892</v>
       </c>
     </row>
     <row r="226">
@@ -3298,7 +3298,7 @@
         <v>2028</v>
       </c>
       <c r="D226">
-        <v>1653.647350681857</v>
+        <v>1748.473711909423</v>
       </c>
     </row>
     <row r="227">
@@ -3311,7 +3311,7 @@
         <v>2024</v>
       </c>
       <c r="D227">
-        <v>1330.94788566909</v>
+        <v>1543.430641701233</v>
       </c>
     </row>
     <row r="228">
@@ -3324,7 +3324,7 @@
         <v>2025</v>
       </c>
       <c r="D228">
-        <v>1333.787818821797</v>
+        <v>1774.811610356136</v>
       </c>
     </row>
     <row r="229">
@@ -3337,7 +3337,7 @@
         <v>2026</v>
       </c>
       <c r="D229">
-        <v>1334.320846442302</v>
+        <v>2048.992111549262</v>
       </c>
     </row>
     <row r="230">
@@ -3350,7 +3350,7 @@
         <v>2027</v>
       </c>
       <c r="D230">
-        <v>1334.420787698188</v>
+        <v>2363.649770700197</v>
       </c>
     </row>
     <row r="231">
@@ -3363,7 +3363,7 @@
         <v>2028</v>
       </c>
       <c r="D231">
-        <v>1334.439522805302</v>
+        <v>2727.062711935329</v>
       </c>
     </row>
     <row r="232">
@@ -3376,7 +3376,7 @@
         <v>2024</v>
       </c>
       <c r="D232">
-        <v>1362.659095196588</v>
+        <v>1819.127837867806</v>
       </c>
     </row>
     <row r="233">
@@ -3389,7 +3389,7 @@
         <v>2025</v>
       </c>
       <c r="D233">
-        <v>1363.034824229595</v>
+        <v>2350.390766694378</v>
       </c>
     </row>
     <row r="234">
@@ -3402,7 +3402,7 @@
         <v>2026</v>
       </c>
       <c r="D234">
-        <v>1363.060496591462</v>
+        <v>3054.372971162071</v>
       </c>
     </row>
     <row r="235">
@@ -3415,7 +3415,7 @@
         <v>2027</v>
       </c>
       <c r="D235">
-        <v>1363.062250461106</v>
+        <v>3965.615864748611</v>
       </c>
     </row>
     <row r="236">
@@ -3428,7 +3428,7 @@
         <v>2028</v>
       </c>
       <c r="D236">
-        <v>1363.06237027984</v>
+        <v>5149.451871130931</v>
       </c>
     </row>
     <row r="237">
@@ -3441,7 +3441,7 @@
         <v>2024</v>
       </c>
       <c r="D237">
-        <v>1266.109816554233</v>
+        <v>1615.199252546589</v>
       </c>
     </row>
     <row r="238">
@@ -3454,7 +3454,7 @@
         <v>2025</v>
       </c>
       <c r="D238">
-        <v>1266.443980485981</v>
+        <v>1997.409290645931</v>
       </c>
     </row>
     <row r="239">
@@ -3467,7 +3467,7 @@
         <v>2026</v>
       </c>
       <c r="D239">
-        <v>1266.465244814638</v>
+        <v>2486.954509749516</v>
       </c>
     </row>
     <row r="240">
@@ -3480,7 +3480,7 @@
         <v>2027</v>
       </c>
       <c r="D240">
-        <v>1266.466597780097</v>
+        <v>3092.406647778571</v>
       </c>
     </row>
     <row r="241">
@@ -3493,7 +3493,7 @@
         <v>2028</v>
       </c>
       <c r="D241">
-        <v>1266.466683863239</v>
+        <v>3846.235786797926</v>
       </c>
     </row>
     <row r="242">
@@ -4091,7 +4091,7 @@
         <v>2024</v>
       </c>
       <c r="D287">
-        <v>1130.335021052196</v>
+        <v>1144.100961778938</v>
       </c>
     </row>
     <row r="288">
@@ -4104,7 +4104,7 @@
         <v>2025</v>
       </c>
       <c r="D288">
-        <v>1170.767819265624</v>
+        <v>1209.867792528788</v>
       </c>
     </row>
     <row r="289">
@@ -4117,7 +4117,7 @@
         <v>2026</v>
       </c>
       <c r="D289">
-        <v>1205.537225815556</v>
+        <v>1280.296023218029</v>
       </c>
     </row>
     <row r="290">
@@ -4130,7 +4130,7 @@
         <v>2027</v>
       </c>
       <c r="D290">
-        <v>1235.275978426678</v>
+        <v>1355.230404222168</v>
       </c>
     </row>
     <row r="291">
@@ -4143,7 +4143,7 @@
         <v>2028</v>
       </c>
       <c r="D291">
-        <v>1260.598158149584</v>
+        <v>1434.738126778079</v>
       </c>
     </row>
     <row r="292">
@@ -4156,7 +4156,7 @@
         <v>2024</v>
       </c>
       <c r="D292">
-        <v>1553.724075422119</v>
+        <v>1559.886312970241</v>
       </c>
     </row>
     <row r="293">
@@ -4169,7 +4169,7 @@
         <v>2025</v>
       </c>
       <c r="D293">
-        <v>1626.663848859009</v>
+        <v>1647.704885379283</v>
       </c>
     </row>
     <row r="294">
@@ -4182,7 +4182,7 @@
         <v>2026</v>
       </c>
       <c r="D294">
-        <v>1692.023886762983</v>
+        <v>1738.009603218948</v>
       </c>
     </row>
     <row r="295">
@@ -4195,7 +4195,7 @@
         <v>2027</v>
       </c>
       <c r="D295">
-        <v>1750.240436032337</v>
+        <v>1831.863192685846</v>
       </c>
     </row>
     <row r="296">
@@ -4208,7 +4208,7 @@
         <v>2028</v>
       </c>
       <c r="D296">
-        <v>1801.826916851154</v>
+        <v>1929.987248212925</v>
       </c>
     </row>
     <row r="297">
@@ -4221,7 +4221,7 @@
         <v>2024</v>
       </c>
       <c r="D297">
-        <v>1553.724075428329</v>
+        <v>1559.88631295132</v>
       </c>
     </row>
     <row r="298">
@@ -4234,7 +4234,7 @@
         <v>2025</v>
       </c>
       <c r="D298">
-        <v>1626.663848876674</v>
+        <v>1647.704885328476</v>
       </c>
     </row>
     <row r="299">
@@ -4247,7 +4247,7 @@
         <v>2026</v>
       </c>
       <c r="D299">
-        <v>1692.023886796315</v>
+        <v>1738.009603126662</v>
       </c>
     </row>
     <row r="300">
@@ -4260,7 +4260,7 @@
         <v>2027</v>
       </c>
       <c r="D300">
-        <v>1750.240436084532</v>
+        <v>1831.863192544255</v>
       </c>
     </row>
     <row r="301">
@@ -4273,7 +4273,7 @@
         <v>2028</v>
       </c>
       <c r="D301">
-        <v>1801.826916924461</v>
+        <v>1929.987248015037</v>
       </c>
     </row>
     <row r="302">
@@ -4286,7 +4286,7 @@
         <v>2024</v>
       </c>
       <c r="D302">
-        <v>1553.724075428329</v>
+        <v>1559.88631295132</v>
       </c>
     </row>
     <row r="303">
@@ -4299,7 +4299,7 @@
         <v>2025</v>
       </c>
       <c r="D303">
-        <v>1626.663848876674</v>
+        <v>1647.704885328476</v>
       </c>
     </row>
     <row r="304">
@@ -4312,7 +4312,7 @@
         <v>2026</v>
       </c>
       <c r="D304">
-        <v>1692.023886796315</v>
+        <v>1738.009603126662</v>
       </c>
     </row>
     <row r="305">
@@ -4325,7 +4325,7 @@
         <v>2027</v>
       </c>
       <c r="D305">
-        <v>1750.240436084532</v>
+        <v>1831.863192544255</v>
       </c>
     </row>
     <row r="306">
@@ -4338,7 +4338,7 @@
         <v>2028</v>
       </c>
       <c r="D306">
-        <v>1801.826916924461</v>
+        <v>1929.987248015037</v>
       </c>
     </row>
     <row r="307">
@@ -4351,7 +4351,7 @@
         <v>2024</v>
       </c>
       <c r="D307">
-        <v>1553.724075428329</v>
+        <v>1559.88631295132</v>
       </c>
     </row>
     <row r="308">
@@ -4364,7 +4364,7 @@
         <v>2025</v>
       </c>
       <c r="D308">
-        <v>1626.663848876674</v>
+        <v>1647.704885328476</v>
       </c>
     </row>
     <row r="309">
@@ -4377,7 +4377,7 @@
         <v>2026</v>
       </c>
       <c r="D309">
-        <v>1692.023886796315</v>
+        <v>1738.009603126662</v>
       </c>
     </row>
     <row r="310">
@@ -4390,7 +4390,7 @@
         <v>2027</v>
       </c>
       <c r="D310">
-        <v>1750.240436084532</v>
+        <v>1831.863192544255</v>
       </c>
     </row>
     <row r="311">
@@ -4403,7 +4403,7 @@
         <v>2028</v>
       </c>
       <c r="D311">
-        <v>1801.826916924461</v>
+        <v>1929.987248015037</v>
       </c>
     </row>
     <row r="312">
@@ -4481,7 +4481,7 @@
         <v>2024</v>
       </c>
       <c r="D317">
-        <v>1131.564292074821</v>
+        <v>1144.046329105066</v>
       </c>
     </row>
     <row r="318">
@@ -4494,7 +4494,7 @@
         <v>2025</v>
       </c>
       <c r="D318">
-        <v>1170.475776782679</v>
+        <v>1206.445798586448</v>
       </c>
     </row>
     <row r="319">
@@ -4507,7 +4507,7 @@
         <v>2026</v>
       </c>
       <c r="D319">
-        <v>1203.351146338615</v>
+        <v>1272.76502420194</v>
       </c>
     </row>
     <row r="320">
@@ -4520,7 +4520,7 @@
         <v>2027</v>
       </c>
       <c r="D320">
-        <v>1230.972959980861</v>
+        <v>1342.983735313944</v>
       </c>
     </row>
     <row r="321">
@@ -4533,7 +4533,7 @@
         <v>2028</v>
       </c>
       <c r="D321">
-        <v>1254.075399054271</v>
+        <v>1417.201256051554</v>
       </c>
     </row>
     <row r="322">
@@ -4546,7 +4546,7 @@
         <v>2024</v>
       </c>
       <c r="D322">
-        <v>1131.56429204882</v>
+        <v>1144.046329095645</v>
       </c>
     </row>
     <row r="323">
@@ -4559,7 +4559,7 @@
         <v>2025</v>
       </c>
       <c r="D323">
-        <v>1170.475776711716</v>
+        <v>1206.445798563422</v>
       </c>
     </row>
     <row r="324">
@@ -4572,7 +4572,7 @@
         <v>2026</v>
       </c>
       <c r="D324">
-        <v>1203.35114620998</v>
+        <v>1272.765024163008</v>
       </c>
     </row>
     <row r="325">
@@ -4585,7 +4585,7 @@
         <v>2027</v>
       </c>
       <c r="D325">
-        <v>1230.972959787055</v>
+        <v>1342.983735257364</v>
       </c>
     </row>
     <row r="326">
@@ -4598,7 +4598,7 @@
         <v>2028</v>
       </c>
       <c r="D326">
-        <v>1254.075398791911</v>
+        <v>1417.201255975641</v>
       </c>
     </row>
     <row r="327">
@@ -4611,7 +4611,7 @@
         <v>2024</v>
       </c>
       <c r="D327">
-        <v>1131.564292074821</v>
+        <v>1144.046329105066</v>
       </c>
     </row>
     <row r="328">
@@ -4624,7 +4624,7 @@
         <v>2025</v>
       </c>
       <c r="D328">
-        <v>1170.475776782679</v>
+        <v>1206.445798586448</v>
       </c>
     </row>
     <row r="329">
@@ -4637,7 +4637,7 @@
         <v>2026</v>
       </c>
       <c r="D329">
-        <v>1203.351146338615</v>
+        <v>1272.76502420194</v>
       </c>
     </row>
     <row r="330">
@@ -4650,7 +4650,7 @@
         <v>2027</v>
       </c>
       <c r="D330">
-        <v>1230.972959980861</v>
+        <v>1342.983735313944</v>
       </c>
     </row>
     <row r="331">
@@ -4663,7 +4663,7 @@
         <v>2028</v>
       </c>
       <c r="D331">
-        <v>1254.075399054271</v>
+        <v>1417.201256051554</v>
       </c>
     </row>
     <row r="332">
@@ -4676,7 +4676,7 @@
         <v>2024</v>
       </c>
       <c r="D332">
-        <v>1488.74635082702</v>
+        <v>1495.645656251703</v>
       </c>
     </row>
     <row r="333">
@@ -4689,7 +4689,7 @@
         <v>2025</v>
       </c>
       <c r="D333">
-        <v>1556.563900755836</v>
+        <v>1579.338953528001</v>
       </c>
     </row>
     <row r="334">
@@ -4702,7 +4702,7 @@
         <v>2026</v>
       </c>
       <c r="D334">
-        <v>1617.058452274469</v>
+        <v>1665.729464453318</v>
       </c>
     </row>
     <row r="335">
@@ -4715,7 +4715,7 @@
         <v>2027</v>
       </c>
       <c r="D335">
-        <v>1670.700621280482</v>
+        <v>1755.722459114588</v>
       </c>
     </row>
     <row r="336">
@@ -4728,7 +4728,7 @@
         <v>2028</v>
       </c>
       <c r="D336">
-        <v>1718.02493358736</v>
+        <v>1849.942459457763</v>
       </c>
     </row>
     <row r="337">
@@ -4741,7 +4741,7 @@
         <v>2024</v>
       </c>
       <c r="D337">
-        <v>1553.724075428329</v>
+        <v>1559.88631295132</v>
       </c>
     </row>
     <row r="338">
@@ -4754,7 +4754,7 @@
         <v>2025</v>
       </c>
       <c r="D338">
-        <v>1626.663848876674</v>
+        <v>1647.704885328476</v>
       </c>
     </row>
     <row r="339">
@@ -4767,7 +4767,7 @@
         <v>2026</v>
       </c>
       <c r="D339">
-        <v>1692.023886796315</v>
+        <v>1738.009603126662</v>
       </c>
     </row>
     <row r="340">
@@ -4780,7 +4780,7 @@
         <v>2027</v>
       </c>
       <c r="D340">
-        <v>1750.240436084532</v>
+        <v>1831.863192544255</v>
       </c>
     </row>
     <row r="341">
@@ -4793,7 +4793,7 @@
         <v>2028</v>
       </c>
       <c r="D341">
-        <v>1801.826916924461</v>
+        <v>1929.987248015037</v>
       </c>
     </row>
     <row r="342">
@@ -4806,7 +4806,7 @@
         <v>2024</v>
       </c>
       <c r="D342">
-        <v>1550.465422144235</v>
+        <v>1556.66301802536</v>
       </c>
     </row>
     <row r="343">
@@ -4819,7 +4819,7 @@
         <v>2025</v>
       </c>
       <c r="D343">
-        <v>1623.150569074524</v>
+        <v>1644.274032334431</v>
       </c>
     </row>
     <row r="344">
@@ -4832,7 +4832,7 @@
         <v>2026</v>
       </c>
       <c r="D344">
-        <v>1688.269647641768</v>
+        <v>1734.381529573017</v>
       </c>
     </row>
     <row r="345">
@@ -4845,7 +4845,7 @@
         <v>2027</v>
       </c>
       <c r="D345">
-        <v>1746.260391312783</v>
+        <v>1828.040364208928</v>
       </c>
     </row>
     <row r="346">
@@ -4858,7 +4858,7 @@
         <v>2028</v>
       </c>
       <c r="D346">
-        <v>1797.637072669319</v>
+        <v>1925.96728154081</v>
       </c>
     </row>
     <row r="347">
@@ -4871,7 +4871,7 @@
         <v>2024</v>
       </c>
       <c r="D347">
-        <v>1131.564292048522</v>
+        <v>1144.04632909548</v>
       </c>
     </row>
     <row r="348">
@@ -4884,7 +4884,7 @@
         <v>2025</v>
       </c>
       <c r="D348">
-        <v>1170.475776710902</v>
+        <v>1206.445798563024</v>
       </c>
     </row>
     <row r="349">
@@ -4897,7 +4897,7 @@
         <v>2026</v>
       </c>
       <c r="D349">
-        <v>1203.351146208502</v>
+        <v>1272.765024162345</v>
       </c>
     </row>
     <row r="350">
@@ -4910,7 +4910,7 @@
         <v>2027</v>
       </c>
       <c r="D350">
-        <v>1230.972959784828</v>
+        <v>1342.983735256412</v>
       </c>
     </row>
     <row r="351">
@@ -4923,7 +4923,7 @@
         <v>2028</v>
       </c>
       <c r="D351">
-        <v>1254.075398788897</v>
+        <v>1417.201255974376</v>
       </c>
     </row>
     <row r="352">
@@ -4936,7 +4936,7 @@
         <v>2024</v>
       </c>
       <c r="D352">
-        <v>1131.564292074821</v>
+        <v>1144.046329105066</v>
       </c>
     </row>
     <row r="353">
@@ -4949,7 +4949,7 @@
         <v>2025</v>
       </c>
       <c r="D353">
-        <v>1170.475776782679</v>
+        <v>1206.445798586448</v>
       </c>
     </row>
     <row r="354">
@@ -4962,7 +4962,7 @@
         <v>2026</v>
       </c>
       <c r="D354">
-        <v>1203.351146338615</v>
+        <v>1272.76502420194</v>
       </c>
     </row>
     <row r="355">
@@ -4975,7 +4975,7 @@
         <v>2027</v>
       </c>
       <c r="D355">
-        <v>1230.972959980861</v>
+        <v>1342.983735313944</v>
       </c>
     </row>
     <row r="356">
@@ -4988,7 +4988,7 @@
         <v>2028</v>
       </c>
       <c r="D356">
-        <v>1254.075399054271</v>
+        <v>1417.201256051554</v>
       </c>
     </row>
     <row r="357">
@@ -5001,7 +5001,7 @@
         <v>2024</v>
       </c>
       <c r="D357">
-        <v>1131.564292074821</v>
+        <v>1144.046329105066</v>
       </c>
     </row>
     <row r="358">
@@ -5014,7 +5014,7 @@
         <v>2025</v>
       </c>
       <c r="D358">
-        <v>1170.475776782679</v>
+        <v>1206.445798586448</v>
       </c>
     </row>
     <row r="359">
@@ -5027,7 +5027,7 @@
         <v>2026</v>
       </c>
       <c r="D359">
-        <v>1203.351146338615</v>
+        <v>1272.76502420194</v>
       </c>
     </row>
     <row r="360">
@@ -5040,7 +5040,7 @@
         <v>2027</v>
       </c>
       <c r="D360">
-        <v>1230.972959980861</v>
+        <v>1342.983735313944</v>
       </c>
     </row>
     <row r="361">
@@ -5053,7 +5053,7 @@
         <v>2028</v>
       </c>
       <c r="D361">
-        <v>1254.075399054271</v>
+        <v>1417.201256051554</v>
       </c>
     </row>
     <row r="362">
@@ -5066,7 +5066,7 @@
         <v>2024</v>
       </c>
       <c r="D362">
-        <v>1130.394068361416</v>
+        <v>1144.094155673381</v>
       </c>
     </row>
     <row r="363">
@@ -5079,7 +5079,7 @@
         <v>2025</v>
       </c>
       <c r="D363">
-        <v>1170.764184377795</v>
+        <v>1209.705503059768</v>
       </c>
     </row>
     <row r="364">
@@ -5092,7 +5092,7 @@
         <v>2026</v>
       </c>
       <c r="D364">
-        <v>1205.45521416578</v>
+        <v>1279.946069209597</v>
       </c>
     </row>
     <row r="365">
@@ -5105,7 +5105,7 @@
         <v>2027</v>
       </c>
       <c r="D365">
-        <v>1235.105798365109</v>
+        <v>1354.666236787851</v>
       </c>
     </row>
     <row r="366">
@@ -5118,7 +5118,7 @@
         <v>2028</v>
       </c>
       <c r="D366">
-        <v>1260.334845151303</v>
+        <v>1433.934086417447</v>
       </c>
     </row>
     <row r="367">
@@ -5131,7 +5131,7 @@
         <v>2024</v>
       </c>
       <c r="D367">
-        <v>1496.132703593285</v>
+        <v>1611.93763092943</v>
       </c>
     </row>
     <row r="368">
@@ -5144,7 +5144,7 @@
         <v>2025</v>
       </c>
       <c r="D368">
-        <v>1518.125707567538</v>
+        <v>1710.433823135432</v>
       </c>
     </row>
     <row r="369">
@@ -5157,7 +5157,7 @@
         <v>2026</v>
       </c>
       <c r="D369">
-        <v>1533.354162394696</v>
+        <v>1852.875819096253</v>
       </c>
     </row>
     <row r="370">
@@ -5170,7 +5170,7 @@
         <v>2027</v>
       </c>
       <c r="D370">
-        <v>1543.857850691018</v>
+        <v>1983.845757761813</v>
       </c>
     </row>
     <row r="371">
@@ -5183,7 +5183,7 @@
         <v>2028</v>
       </c>
       <c r="D371">
-        <v>1551.083466729474</v>
+        <v>2138.163260430416</v>
       </c>
     </row>
     <row r="372">
@@ -5261,7 +5261,7 @@
         <v>2024</v>
       </c>
       <c r="D377">
-        <v>1076.521020321186</v>
+        <v>1227.377196907752</v>
       </c>
     </row>
     <row r="378">
@@ -5274,7 +5274,7 @@
         <v>2025</v>
       </c>
       <c r="D378">
-        <v>1096.011637654854</v>
+        <v>1331.838651663923</v>
       </c>
     </row>
     <row r="379">
@@ -5287,7 +5287,7 @@
         <v>2026</v>
       </c>
       <c r="D379">
-        <v>1109.959771281288</v>
+        <v>1514.119954039392</v>
       </c>
     </row>
     <row r="380">
@@ -5300,7 +5300,7 @@
         <v>2027</v>
       </c>
       <c r="D380">
-        <v>1119.896583767315</v>
+        <v>1672.188597628708</v>
       </c>
     </row>
     <row r="381">
@@ -5313,7 +5313,7 @@
         <v>2028</v>
       </c>
       <c r="D381">
-        <v>1126.953204356331</v>
+        <v>1880.337076624478</v>
       </c>
     </row>
     <row r="382">
@@ -5456,7 +5456,7 @@
         <v>2024</v>
       </c>
       <c r="D392">
-        <v>1801.975747967165</v>
+        <v>1960.537333882409</v>
       </c>
     </row>
     <row r="393">
@@ -5469,7 +5469,7 @@
         <v>2025</v>
       </c>
       <c r="D393">
-        <v>1834.660158308001</v>
+        <v>2075.089186160109</v>
       </c>
     </row>
     <row r="394">
@@ -5482,7 +5482,7 @@
         <v>2026</v>
       </c>
       <c r="D394">
-        <v>1859.61829990823</v>
+        <v>2273.769769049492</v>
       </c>
     </row>
     <row r="395">
@@ -5495,7 +5495,7 @@
         <v>2027</v>
       </c>
       <c r="D395">
-        <v>1878.602273134409</v>
+        <v>2434.022048679896</v>
       </c>
     </row>
     <row r="396">
@@ -5508,7 +5508,7 @@
         <v>2028</v>
       </c>
       <c r="D396">
-        <v>1892.999749421106</v>
+        <v>2646.818070695215</v>
       </c>
     </row>
     <row r="397">
@@ -5521,7 +5521,7 @@
         <v>2024</v>
       </c>
       <c r="D397">
-        <v>1815.415514895232</v>
+        <v>1959.317906174222</v>
       </c>
     </row>
     <row r="398">
@@ -5534,7 +5534,7 @@
         <v>2025</v>
       </c>
       <c r="D398">
-        <v>1843.224597359337</v>
+        <v>2078.42977857815</v>
       </c>
     </row>
     <row r="399">
@@ -5547,7 +5547,7 @@
         <v>2026</v>
       </c>
       <c r="D399">
-        <v>1862.855079419576</v>
+        <v>2255.779990253262</v>
       </c>
     </row>
     <row r="400">
@@ -5560,7 +5560,7 @@
         <v>2027</v>
       </c>
       <c r="D400">
-        <v>1876.658233232797</v>
+        <v>2415.724472601367</v>
       </c>
     </row>
     <row r="401">
@@ -5573,7 +5573,7 @@
         <v>2028</v>
       </c>
       <c r="D401">
-        <v>1886.337510430844</v>
+        <v>2607.341948271045</v>
       </c>
     </row>
     <row r="402">
@@ -5651,7 +5651,7 @@
         <v>2024</v>
       </c>
       <c r="D407">
-        <v>1076.521020321186</v>
+        <v>1227.377196907752</v>
       </c>
     </row>
     <row r="408">
@@ -5664,7 +5664,7 @@
         <v>2025</v>
       </c>
       <c r="D408">
-        <v>1096.011637654854</v>
+        <v>1331.838651663923</v>
       </c>
     </row>
     <row r="409">
@@ -5677,7 +5677,7 @@
         <v>2026</v>
       </c>
       <c r="D409">
-        <v>1109.959771281288</v>
+        <v>1514.119954039392</v>
       </c>
     </row>
     <row r="410">
@@ -5690,7 +5690,7 @@
         <v>2027</v>
       </c>
       <c r="D410">
-        <v>1119.896583767315</v>
+        <v>1672.188597628708</v>
       </c>
     </row>
     <row r="411">
@@ -5703,7 +5703,7 @@
         <v>2028</v>
       </c>
       <c r="D411">
-        <v>1126.953204356331</v>
+        <v>1880.337076624478</v>
       </c>
     </row>
     <row r="412">
@@ -5716,7 +5716,7 @@
         <v>2024</v>
       </c>
       <c r="D412">
-        <v>1076.521016387893</v>
+        <v>1227.377198518076</v>
       </c>
     </row>
     <row r="413">
@@ -5729,7 +5729,7 @@
         <v>2025</v>
       </c>
       <c r="D413">
-        <v>1096.011628005791</v>
+        <v>1331.838652810111</v>
       </c>
     </row>
     <row r="414">
@@ -5742,7 +5742,7 @@
         <v>2026</v>
       </c>
       <c r="D414">
-        <v>1109.959755466266</v>
+        <v>1514.119957211546</v>
       </c>
     </row>
     <row r="415">
@@ -5755,7 +5755,7 @@
         <v>2027</v>
       </c>
       <c r="D415">
-        <v>1119.896562081105</v>
+        <v>1672.188600830423</v>
       </c>
     </row>
     <row r="416">
@@ -5768,7 +5768,7 @@
         <v>2028</v>
       </c>
       <c r="D416">
-        <v>1126.953177454057</v>
+        <v>1880.33708196844</v>
       </c>
     </row>
     <row r="417">
@@ -5781,7 +5781,7 @@
         <v>2024</v>
       </c>
       <c r="D417">
-        <v>1076.521020321186</v>
+        <v>1227.377196907752</v>
       </c>
     </row>
     <row r="418">
@@ -5794,7 +5794,7 @@
         <v>2025</v>
       </c>
       <c r="D418">
-        <v>1096.011637654854</v>
+        <v>1331.838651663923</v>
       </c>
     </row>
     <row r="419">
@@ -5807,7 +5807,7 @@
         <v>2026</v>
       </c>
       <c r="D419">
-        <v>1109.959771281288</v>
+        <v>1514.119954039392</v>
       </c>
     </row>
     <row r="420">
@@ -5820,7 +5820,7 @@
         <v>2027</v>
       </c>
       <c r="D420">
-        <v>1119.896583767315</v>
+        <v>1672.188597628708</v>
       </c>
     </row>
     <row r="421">
@@ -5833,7 +5833,7 @@
         <v>2028</v>
       </c>
       <c r="D421">
-        <v>1126.953204356331</v>
+        <v>1880.337076624478</v>
       </c>
     </row>
     <row r="422">
@@ -5846,7 +5846,7 @@
         <v>2024</v>
       </c>
       <c r="D422">
-        <v>1076.521020321186</v>
+        <v>1227.377196907752</v>
       </c>
     </row>
     <row r="423">
@@ -5859,7 +5859,7 @@
         <v>2025</v>
       </c>
       <c r="D423">
-        <v>1096.011637654854</v>
+        <v>1331.838651663923</v>
       </c>
     </row>
     <row r="424">
@@ -5872,7 +5872,7 @@
         <v>2026</v>
       </c>
       <c r="D424">
-        <v>1109.959771281288</v>
+        <v>1514.119954039392</v>
       </c>
     </row>
     <row r="425">
@@ -5885,7 +5885,7 @@
         <v>2027</v>
       </c>
       <c r="D425">
-        <v>1119.896583767315</v>
+        <v>1672.188597628708</v>
       </c>
     </row>
     <row r="426">
@@ -5898,7 +5898,7 @@
         <v>2028</v>
       </c>
       <c r="D426">
-        <v>1126.953204356331</v>
+        <v>1880.337076624478</v>
       </c>
     </row>
     <row r="427">
@@ -5911,7 +5911,7 @@
         <v>2024</v>
       </c>
       <c r="D427">
-        <v>981.7379600813599</v>
+        <v>990.4504746360088</v>
       </c>
     </row>
     <row r="428">
@@ -5924,7 +5924,7 @@
         <v>2025</v>
       </c>
       <c r="D428">
-        <v>1035.702837653972</v>
+        <v>1062.844983696082</v>
       </c>
     </row>
     <row r="429">
@@ -5937,7 +5937,7 @@
         <v>2026</v>
       </c>
       <c r="D429">
-        <v>1084.328841112728</v>
+        <v>1140.167997526908</v>
       </c>
     </row>
     <row r="430">
@@ -5950,7 +5950,7 @@
         <v>2027</v>
       </c>
       <c r="D430">
-        <v>1127.8351366738</v>
+        <v>1222.939547142299</v>
       </c>
     </row>
     <row r="431">
@@ -5963,7 +5963,7 @@
         <v>2028</v>
       </c>
       <c r="D431">
-        <v>1166.52521786191</v>
+        <v>1311.633873087605</v>
       </c>
     </row>
     <row r="432">
@@ -5976,7 +5976,7 @@
         <v>2024</v>
       </c>
       <c r="D432">
-        <v>979.3362378402669</v>
+        <v>983.8910710947677</v>
       </c>
     </row>
     <row r="433">
@@ -5989,7 +5989,7 @@
         <v>2025</v>
       </c>
       <c r="D433">
-        <v>1036.526312042018</v>
+        <v>1052.199116217547</v>
       </c>
     </row>
     <row r="434">
@@ -6002,7 +6002,7 @@
         <v>2026</v>
       </c>
       <c r="D434">
-        <v>1089.226441072675</v>
+        <v>1123.802367228462</v>
       </c>
     </row>
     <row r="435">
@@ -6015,7 +6015,7 @@
         <v>2027</v>
       </c>
       <c r="D435">
-        <v>1137.464694892951</v>
+        <v>1199.47376645933</v>
       </c>
     </row>
     <row r="436">
@@ -6028,7 +6028,7 @@
         <v>2028</v>
       </c>
       <c r="D436">
-        <v>1181.360941368356</v>
+        <v>1279.793340480358</v>
       </c>
     </row>
     <row r="437">
@@ -6041,7 +6041,7 @@
         <v>2024</v>
       </c>
       <c r="D437">
-        <v>979.3362378402669</v>
+        <v>983.8910710947677</v>
       </c>
     </row>
     <row r="438">
@@ -6054,7 +6054,7 @@
         <v>2025</v>
       </c>
       <c r="D438">
-        <v>1036.526312042018</v>
+        <v>1052.199116217547</v>
       </c>
     </row>
     <row r="439">
@@ -6067,7 +6067,7 @@
         <v>2026</v>
       </c>
       <c r="D439">
-        <v>1089.226441072675</v>
+        <v>1123.802367228462</v>
       </c>
     </row>
     <row r="440">
@@ -6080,7 +6080,7 @@
         <v>2027</v>
       </c>
       <c r="D440">
-        <v>1137.464694892951</v>
+        <v>1199.47376645933</v>
       </c>
     </row>
     <row r="441">
@@ -6093,7 +6093,7 @@
         <v>2028</v>
       </c>
       <c r="D441">
-        <v>1181.360941368356</v>
+        <v>1279.793340480358</v>
       </c>
     </row>
     <row r="442">
@@ -6106,7 +6106,7 @@
         <v>2024</v>
       </c>
       <c r="D442">
-        <v>980.2082480520022</v>
+        <v>985.0250121428841</v>
       </c>
     </row>
     <row r="443">
@@ -6119,7 +6119,7 @@
         <v>2025</v>
       </c>
       <c r="D443">
-        <v>1037.612317341153</v>
+        <v>1053.899335224677</v>
       </c>
     </row>
     <row r="444">
@@ -6132,7 +6132,7 @@
         <v>2026</v>
       </c>
       <c r="D444">
-        <v>1090.69768009377</v>
+        <v>1126.260011203767</v>
       </c>
     </row>
     <row r="445">
@@ -6145,7 +6145,7 @@
         <v>2027</v>
       </c>
       <c r="D445">
-        <v>1139.46741721645</v>
+        <v>1202.83915579063</v>
       </c>
     </row>
     <row r="446">
@@ -6158,7 +6158,7 @@
         <v>2028</v>
       </c>
       <c r="D446">
-        <v>1184.014719775969</v>
+        <v>1284.202421974969</v>
       </c>
     </row>
     <row r="447">
@@ -6171,7 +6171,7 @@
         <v>2024</v>
       </c>
       <c r="D447">
-        <v>1076.521020321186</v>
+        <v>1227.377196907752</v>
       </c>
     </row>
     <row r="448">
@@ -6184,7 +6184,7 @@
         <v>2025</v>
       </c>
       <c r="D448">
-        <v>1096.011637654854</v>
+        <v>1331.838651663923</v>
       </c>
     </row>
     <row r="449">
@@ -6197,7 +6197,7 @@
         <v>2026</v>
       </c>
       <c r="D449">
-        <v>1109.959771281288</v>
+        <v>1514.119954039392</v>
       </c>
     </row>
     <row r="450">
@@ -6210,7 +6210,7 @@
         <v>2027</v>
       </c>
       <c r="D450">
-        <v>1119.896583767315</v>
+        <v>1672.188597628708</v>
       </c>
     </row>
     <row r="451">
@@ -6223,7 +6223,7 @@
         <v>2028</v>
       </c>
       <c r="D451">
-        <v>1126.953204356331</v>
+        <v>1880.337076624478</v>
       </c>
     </row>
     <row r="452">
@@ -6301,7 +6301,7 @@
         <v>2024</v>
       </c>
       <c r="D457">
-        <v>1076.521016387893</v>
+        <v>1227.377198518076</v>
       </c>
     </row>
     <row r="458">
@@ -6314,7 +6314,7 @@
         <v>2025</v>
       </c>
       <c r="D458">
-        <v>1096.011628005791</v>
+        <v>1331.838652810111</v>
       </c>
     </row>
     <row r="459">
@@ -6327,7 +6327,7 @@
         <v>2026</v>
       </c>
       <c r="D459">
-        <v>1109.959755466266</v>
+        <v>1514.119957211546</v>
       </c>
     </row>
     <row r="460">
@@ -6340,7 +6340,7 @@
         <v>2027</v>
       </c>
       <c r="D460">
-        <v>1119.896562081105</v>
+        <v>1672.188600830423</v>
       </c>
     </row>
     <row r="461">
@@ -6353,7 +6353,7 @@
         <v>2028</v>
       </c>
       <c r="D461">
-        <v>1126.953177454057</v>
+        <v>1880.33708196844</v>
       </c>
     </row>
     <row r="462">
@@ -6366,7 +6366,7 @@
         <v>2024</v>
       </c>
       <c r="D462">
-        <v>1076.521020321186</v>
+        <v>1227.377196907752</v>
       </c>
     </row>
     <row r="463">
@@ -6379,7 +6379,7 @@
         <v>2025</v>
       </c>
       <c r="D463">
-        <v>1096.011637654854</v>
+        <v>1331.838651663923</v>
       </c>
     </row>
     <row r="464">
@@ -6392,7 +6392,7 @@
         <v>2026</v>
       </c>
       <c r="D464">
-        <v>1109.959771281288</v>
+        <v>1514.119954039392</v>
       </c>
     </row>
     <row r="465">
@@ -6405,7 +6405,7 @@
         <v>2027</v>
       </c>
       <c r="D465">
-        <v>1119.896583767315</v>
+        <v>1672.188597628708</v>
       </c>
     </row>
     <row r="466">
@@ -6418,7 +6418,7 @@
         <v>2028</v>
       </c>
       <c r="D466">
-        <v>1126.953204356331</v>
+        <v>1880.337076624478</v>
       </c>
     </row>
     <row r="467">
@@ -6496,7 +6496,7 @@
         <v>2024</v>
       </c>
       <c r="D472">
-        <v>979.3362378402669</v>
+        <v>983.8910710947677</v>
       </c>
     </row>
     <row r="473">
@@ -6509,7 +6509,7 @@
         <v>2025</v>
       </c>
       <c r="D473">
-        <v>1036.526312042018</v>
+        <v>1052.199116217547</v>
       </c>
     </row>
     <row r="474">
@@ -6522,7 +6522,7 @@
         <v>2026</v>
       </c>
       <c r="D474">
-        <v>1089.226441072675</v>
+        <v>1123.802367228462</v>
       </c>
     </row>
     <row r="475">
@@ -6535,7 +6535,7 @@
         <v>2027</v>
       </c>
       <c r="D475">
-        <v>1137.464694892951</v>
+        <v>1199.47376645933</v>
       </c>
     </row>
     <row r="476">
@@ -6548,7 +6548,7 @@
         <v>2028</v>
       </c>
       <c r="D476">
-        <v>1181.360941368356</v>
+        <v>1279.793340480358</v>
       </c>
     </row>
     <row r="477">
@@ -6561,7 +6561,7 @@
         <v>2024</v>
       </c>
       <c r="D477">
-        <v>979.3362378402669</v>
+        <v>983.8910710947677</v>
       </c>
     </row>
     <row r="478">
@@ -6574,7 +6574,7 @@
         <v>2025</v>
       </c>
       <c r="D478">
-        <v>1036.526312042018</v>
+        <v>1052.199116217547</v>
       </c>
     </row>
     <row r="479">
@@ -6587,7 +6587,7 @@
         <v>2026</v>
       </c>
       <c r="D479">
-        <v>1089.226441072675</v>
+        <v>1123.802367228462</v>
       </c>
     </row>
     <row r="480">
@@ -6600,7 +6600,7 @@
         <v>2027</v>
       </c>
       <c r="D480">
-        <v>1137.464694892951</v>
+        <v>1199.47376645933</v>
       </c>
     </row>
     <row r="481">
@@ -6613,7 +6613,7 @@
         <v>2028</v>
       </c>
       <c r="D481">
-        <v>1181.360941368356</v>
+        <v>1279.793340480358</v>
       </c>
     </row>
     <row r="482">
@@ -6626,7 +6626,7 @@
         <v>2024</v>
       </c>
       <c r="D482">
-        <v>979.3362378402669</v>
+        <v>983.8910710947677</v>
       </c>
     </row>
     <row r="483">
@@ -6639,7 +6639,7 @@
         <v>2025</v>
       </c>
       <c r="D483">
-        <v>1036.526312042018</v>
+        <v>1052.199116217547</v>
       </c>
     </row>
     <row r="484">
@@ -6652,7 +6652,7 @@
         <v>2026</v>
       </c>
       <c r="D484">
-        <v>1089.226441072675</v>
+        <v>1123.802367228462</v>
       </c>
     </row>
     <row r="485">
@@ -6665,7 +6665,7 @@
         <v>2027</v>
       </c>
       <c r="D485">
-        <v>1137.464694892951</v>
+        <v>1199.47376645933</v>
       </c>
     </row>
     <row r="486">
@@ -6678,7 +6678,7 @@
         <v>2028</v>
       </c>
       <c r="D486">
-        <v>1181.360941368356</v>
+        <v>1279.793340480358</v>
       </c>
     </row>
     <row r="487">
@@ -6691,7 +6691,7 @@
         <v>2024</v>
       </c>
       <c r="D487">
-        <v>979.3362378402669</v>
+        <v>983.8910710947677</v>
       </c>
     </row>
     <row r="488">
@@ -6704,7 +6704,7 @@
         <v>2025</v>
       </c>
       <c r="D488">
-        <v>1036.526312042018</v>
+        <v>1052.199116217547</v>
       </c>
     </row>
     <row r="489">
@@ -6717,7 +6717,7 @@
         <v>2026</v>
       </c>
       <c r="D489">
-        <v>1089.226441072675</v>
+        <v>1123.802367228462</v>
       </c>
     </row>
     <row r="490">
@@ -6730,7 +6730,7 @@
         <v>2027</v>
       </c>
       <c r="D490">
-        <v>1137.464694892951</v>
+        <v>1199.47376645933</v>
       </c>
     </row>
     <row r="491">
@@ -6743,7 +6743,7 @@
         <v>2028</v>
       </c>
       <c r="D491">
-        <v>1181.360941368356</v>
+        <v>1279.793340480358</v>
       </c>
     </row>
     <row r="492">
@@ -6756,7 +6756,7 @@
         <v>2024</v>
       </c>
       <c r="D492">
-        <v>1063.506369737125</v>
+        <v>1218.255982375965</v>
       </c>
     </row>
     <row r="493">
@@ -6769,7 +6769,7 @@
         <v>2025</v>
       </c>
       <c r="D493">
-        <v>1080.151401130009</v>
+        <v>1469.616057359019</v>
       </c>
     </row>
     <row r="494">
@@ -6782,7 +6782,7 @@
         <v>2026</v>
       </c>
       <c r="D494">
-        <v>1088.644396219331</v>
+        <v>1780.215329238226</v>
       </c>
     </row>
     <row r="495">
@@ -6795,7 +6795,7 @@
         <v>2027</v>
       </c>
       <c r="D495">
-        <v>1092.952885181722</v>
+        <v>2158.235344782728</v>
       </c>
     </row>
     <row r="496">
@@ -6808,7 +6808,7 @@
         <v>2028</v>
       </c>
       <c r="D496">
-        <v>1095.132207994648</v>
+        <v>2616.953368214005</v>
       </c>
     </row>
     <row r="497">
@@ -6821,7 +6821,7 @@
         <v>2024</v>
       </c>
       <c r="D497">
-        <v>1203.099981216072</v>
+        <v>1430.297806238465</v>
       </c>
     </row>
     <row r="498">
@@ -6834,7 +6834,7 @@
         <v>2025</v>
       </c>
       <c r="D498">
-        <v>1228.363779213326</v>
+        <v>1683.777972086963</v>
       </c>
     </row>
     <row r="499">
@@ -6847,7 +6847,7 @@
         <v>2026</v>
       </c>
       <c r="D499">
-        <v>1242.927788643585</v>
+        <v>2011.910060511746</v>
       </c>
     </row>
     <row r="500">
@@ -6860,7 +6860,7 @@
         <v>2027</v>
       </c>
       <c r="D500">
-        <v>1251.264713119204</v>
+        <v>2392.548745925043</v>
       </c>
     </row>
     <row r="501">
@@ -6873,7 +6873,7 @@
         <v>2028</v>
       </c>
       <c r="D501">
-        <v>1256.018019718452</v>
+        <v>2849.552985014239</v>
       </c>
     </row>
     <row r="502">
@@ -6886,7 +6886,7 @@
         <v>2024</v>
       </c>
       <c r="D502">
-        <v>1092.634562137395</v>
+        <v>1211.975729617488</v>
       </c>
     </row>
     <row r="503">
@@ -6899,7 +6899,7 @@
         <v>2025</v>
       </c>
       <c r="D503">
-        <v>1121.296840835209</v>
+        <v>1368.984002233626</v>
       </c>
     </row>
     <row r="504">
@@ -6912,7 +6912,7 @@
         <v>2026</v>
       </c>
       <c r="D504">
-        <v>1145.40165272564</v>
+        <v>1549.189170348304</v>
       </c>
     </row>
     <row r="505">
@@ -6925,7 +6925,7 @@
         <v>2027</v>
       </c>
       <c r="D505">
-        <v>1165.588521442926</v>
+        <v>1752.668734002168</v>
       </c>
     </row>
     <row r="506">
@@ -6938,7 +6938,7 @@
         <v>2028</v>
       </c>
       <c r="D506">
-        <v>1182.435910606352</v>
+        <v>1982.944281233758</v>
       </c>
     </row>
     <row r="507">
@@ -6951,7 +6951,7 @@
         <v>2024</v>
       </c>
       <c r="D507">
-        <v>1076.521020321186</v>
+        <v>1227.377196907752</v>
       </c>
     </row>
     <row r="508">
@@ -6964,7 +6964,7 @@
         <v>2025</v>
       </c>
       <c r="D508">
-        <v>1096.011637654854</v>
+        <v>1331.838651663923</v>
       </c>
     </row>
     <row r="509">
@@ -6977,7 +6977,7 @@
         <v>2026</v>
       </c>
       <c r="D509">
-        <v>1109.959771281288</v>
+        <v>1514.119954039392</v>
       </c>
     </row>
     <row r="510">
@@ -6990,7 +6990,7 @@
         <v>2027</v>
       </c>
       <c r="D510">
-        <v>1119.896583767315</v>
+        <v>1672.188597628708</v>
       </c>
     </row>
     <row r="511">
@@ -7003,7 +7003,7 @@
         <v>2028</v>
       </c>
       <c r="D511">
-        <v>1126.953204356331</v>
+        <v>1880.337076624478</v>
       </c>
     </row>
     <row r="512">
@@ -7341,7 +7341,7 @@
         <v>2024</v>
       </c>
       <c r="D537">
-        <v>1022.589007068391</v>
+        <v>1025.579969215592</v>
       </c>
     </row>
     <row r="538">
@@ -7354,7 +7354,7 @@
         <v>2025</v>
       </c>
       <c r="D538">
-        <v>1085.042195003126</v>
+        <v>1095.47715099675</v>
       </c>
     </row>
     <row r="539">
@@ -7367,7 +7367,7 @@
         <v>2026</v>
       </c>
       <c r="D539">
-        <v>1145.160958455216</v>
+        <v>1168.606123721413</v>
       </c>
     </row>
     <row r="540">
@@ -7380,7 +7380,7 @@
         <v>2027</v>
       </c>
       <c r="D540">
-        <v>1202.737661593499</v>
+        <v>1245.625199618813</v>
       </c>
     </row>
     <row r="541">
@@ -7393,7 +7393,7 @@
         <v>2028</v>
       </c>
       <c r="D541">
-        <v>1257.624110398745</v>
+        <v>1327.078704141171</v>
       </c>
     </row>
     <row r="542">
@@ -7406,7 +7406,7 @@
         <v>2024</v>
       </c>
       <c r="D542">
-        <v>1022.589007068391</v>
+        <v>1025.579969215592</v>
       </c>
     </row>
     <row r="543">
@@ -7419,7 +7419,7 @@
         <v>2025</v>
       </c>
       <c r="D543">
-        <v>1085.042195003126</v>
+        <v>1095.47715099675</v>
       </c>
     </row>
     <row r="544">
@@ -7432,7 +7432,7 @@
         <v>2026</v>
       </c>
       <c r="D544">
-        <v>1145.160958455216</v>
+        <v>1168.606123721413</v>
       </c>
     </row>
     <row r="545">
@@ -7445,7 +7445,7 @@
         <v>2027</v>
       </c>
       <c r="D545">
-        <v>1202.737661593499</v>
+        <v>1245.625199618813</v>
       </c>
     </row>
     <row r="546">
@@ -7458,7 +7458,7 @@
         <v>2028</v>
       </c>
       <c r="D546">
-        <v>1257.624110398745</v>
+        <v>1327.078704141171</v>
       </c>
     </row>
     <row r="547">
@@ -7471,7 +7471,7 @@
         <v>2024</v>
       </c>
       <c r="D547">
-        <v>1022.589007068391</v>
+        <v>1025.579969215592</v>
       </c>
     </row>
     <row r="548">
@@ -7484,7 +7484,7 @@
         <v>2025</v>
       </c>
       <c r="D548">
-        <v>1085.042195003126</v>
+        <v>1095.47715099675</v>
       </c>
     </row>
     <row r="549">
@@ -7497,7 +7497,7 @@
         <v>2026</v>
       </c>
       <c r="D549">
-        <v>1145.160958455216</v>
+        <v>1168.606123721413</v>
       </c>
     </row>
     <row r="550">
@@ -7510,7 +7510,7 @@
         <v>2027</v>
       </c>
       <c r="D550">
-        <v>1202.737661593499</v>
+        <v>1245.625199618813</v>
       </c>
     </row>
     <row r="551">
@@ -7523,7 +7523,7 @@
         <v>2028</v>
       </c>
       <c r="D551">
-        <v>1257.624110398745</v>
+        <v>1327.078704141171</v>
       </c>
     </row>
     <row r="552">
@@ -7536,7 +7536,7 @@
         <v>2024</v>
       </c>
       <c r="D552">
-        <v>1074.026788357517</v>
+        <v>1340.242902741399</v>
       </c>
     </row>
     <row r="553">
@@ -7549,7 +7549,7 @@
         <v>2025</v>
       </c>
       <c r="D553">
-        <v>1080.984511059051</v>
+        <v>1628.268605123396</v>
       </c>
     </row>
     <row r="554">
@@ -7562,7 +7562,7 @@
         <v>2026</v>
       </c>
       <c r="D554">
-        <v>1083.095502315212</v>
+        <v>2005.017819731981</v>
       </c>
     </row>
     <row r="555">
@@ -7575,7 +7575,7 @@
         <v>2027</v>
       </c>
       <c r="D555">
-        <v>1083.734107134651</v>
+        <v>2459.652701736671</v>
       </c>
     </row>
     <row r="556">
@@ -7588,7 +7588,7 @@
         <v>2028</v>
       </c>
       <c r="D556">
-        <v>1083.927123012523</v>
+        <v>3020.558460911682</v>
       </c>
     </row>
     <row r="557">
@@ -7861,7 +7861,7 @@
         <v>2024</v>
       </c>
       <c r="D577">
-        <v>1296.297481973512</v>
+        <v>1442.340500912743</v>
       </c>
     </row>
     <row r="578">
@@ -7874,7 +7874,7 @@
         <v>2025</v>
       </c>
       <c r="D578">
-        <v>1306.82473805714</v>
+        <v>1620.808004426156</v>
       </c>
     </row>
     <row r="579">
@@ -7887,7 +7887,7 @@
         <v>2026</v>
       </c>
       <c r="D579">
-        <v>1310.436228934804</v>
+        <v>1827.056311072357</v>
       </c>
     </row>
     <row r="580">
@@ -7900,7 +7900,7 @@
         <v>2027</v>
       </c>
       <c r="D580">
-        <v>1311.670773925188</v>
+        <v>2058.094327258214</v>
       </c>
     </row>
     <row r="581">
@@ -7913,7 +7913,7 @@
         <v>2028</v>
       </c>
       <c r="D581">
-        <v>1312.092274260531</v>
+        <v>2318.718896563441</v>
       </c>
     </row>
     <row r="582">
@@ -7926,7 +7926,7 @@
         <v>2024</v>
       </c>
       <c r="D582">
-        <v>1395.428867274248</v>
+        <v>1469.381234964764</v>
       </c>
     </row>
     <row r="583">
@@ -7939,7 +7939,7 @@
         <v>2025</v>
       </c>
       <c r="D583">
-        <v>1452.083660336854</v>
+        <v>1642.23003275649</v>
       </c>
     </row>
     <row r="584">
@@ -7952,7 +7952,7 @@
         <v>2026</v>
       </c>
       <c r="D584">
-        <v>1497.518300576078</v>
+        <v>1838.75517483274</v>
       </c>
     </row>
     <row r="585">
@@ -7965,7 +7965,7 @@
         <v>2027</v>
       </c>
       <c r="D585">
-        <v>1533.665901141179</v>
+        <v>2059.633667861199</v>
       </c>
     </row>
     <row r="586">
@@ -7978,7 +7978,7 @@
         <v>2028</v>
       </c>
       <c r="D586">
-        <v>1562.247990311802</v>
+        <v>2307.253513910122</v>
       </c>
     </row>
     <row r="587">
@@ -7991,7 +7991,7 @@
         <v>2024</v>
       </c>
       <c r="D587">
-        <v>1022.589007068391</v>
+        <v>1025.579969215592</v>
       </c>
     </row>
     <row r="588">
@@ -8004,7 +8004,7 @@
         <v>2025</v>
       </c>
       <c r="D588">
-        <v>1085.042195003126</v>
+        <v>1095.47715099675</v>
       </c>
     </row>
     <row r="589">
@@ -8017,7 +8017,7 @@
         <v>2026</v>
       </c>
       <c r="D589">
-        <v>1145.160958455216</v>
+        <v>1168.606123721413</v>
       </c>
     </row>
     <row r="590">
@@ -8030,7 +8030,7 @@
         <v>2027</v>
       </c>
       <c r="D590">
-        <v>1202.737661593499</v>
+        <v>1245.625199618813</v>
       </c>
     </row>
     <row r="591">
@@ -8043,7 +8043,7 @@
         <v>2028</v>
       </c>
       <c r="D591">
-        <v>1257.624110398745</v>
+        <v>1327.078704141171</v>
       </c>
     </row>
     <row r="592">
@@ -8056,7 +8056,7 @@
         <v>2024</v>
       </c>
       <c r="D592">
-        <v>1022.589007173523</v>
+        <v>1025.579969215633</v>
       </c>
     </row>
     <row r="593">
@@ -8069,7 +8069,7 @@
         <v>2025</v>
       </c>
       <c r="D593">
-        <v>1085.042195317632</v>
+        <v>1095.477150996861</v>
       </c>
     </row>
     <row r="594">
@@ -8082,7 +8082,7 @@
         <v>2026</v>
       </c>
       <c r="D594">
-        <v>1145.160959079422</v>
+        <v>1168.606123721621</v>
       </c>
     </row>
     <row r="595">
@@ -8095,7 +8095,7 @@
         <v>2027</v>
       </c>
       <c r="D595">
-        <v>1202.737662621409</v>
+        <v>1245.625199619138</v>
       </c>
     </row>
     <row r="596">
@@ -8108,7 +8108,7 @@
         <v>2028</v>
       </c>
       <c r="D596">
-        <v>1257.624111916242</v>
+        <v>1327.078704141632</v>
       </c>
     </row>
     <row r="597">
@@ -8121,7 +8121,7 @@
         <v>2024</v>
       </c>
       <c r="D597">
-        <v>1022.589007068391</v>
+        <v>1025.579969215592</v>
       </c>
     </row>
     <row r="598">
@@ -8134,7 +8134,7 @@
         <v>2025</v>
       </c>
       <c r="D598">
-        <v>1085.042195003126</v>
+        <v>1095.47715099675</v>
       </c>
     </row>
     <row r="599">
@@ -8147,7 +8147,7 @@
         <v>2026</v>
       </c>
       <c r="D599">
-        <v>1145.160958455216</v>
+        <v>1168.606123721413</v>
       </c>
     </row>
     <row r="600">
@@ -8160,7 +8160,7 @@
         <v>2027</v>
       </c>
       <c r="D600">
-        <v>1202.737661593499</v>
+        <v>1245.625199618813</v>
       </c>
     </row>
     <row r="601">
@@ -8173,7 +8173,7 @@
         <v>2028</v>
       </c>
       <c r="D601">
-        <v>1257.624110398745</v>
+        <v>1327.078704141171</v>
       </c>
     </row>
     <row r="602">
@@ -8316,7 +8316,7 @@
         <v>2024</v>
       </c>
       <c r="D612">
-        <v>1056.901839569395</v>
+        <v>1127.137679589519</v>
       </c>
     </row>
     <row r="613">
@@ -8329,7 +8329,7 @@
         <v>2025</v>
       </c>
       <c r="D613">
-        <v>1105.742753261487</v>
+        <v>1256.708494465722</v>
       </c>
     </row>
     <row r="614">
@@ -8342,7 +8342,7 @@
         <v>2026</v>
       </c>
       <c r="D614">
-        <v>1142.782662143885</v>
+        <v>1411.545682910177</v>
       </c>
     </row>
     <row r="615">
@@ -8355,7 +8355,7 @@
         <v>2027</v>
       </c>
       <c r="D615">
-        <v>1170.578052149085</v>
+        <v>1580.530307866091</v>
       </c>
     </row>
     <row r="616">
@@ -8368,7 +8368,7 @@
         <v>2028</v>
       </c>
       <c r="D616">
-        <v>1191.276186865329</v>
+        <v>1772.074017809487</v>
       </c>
     </row>
     <row r="617">
@@ -8381,7 +8381,7 @@
         <v>2024</v>
       </c>
       <c r="D617">
-        <v>1083.643704608855</v>
+        <v>1125.561607850815</v>
       </c>
     </row>
     <row r="618">
@@ -8394,7 +8394,7 @@
         <v>2025</v>
       </c>
       <c r="D618">
-        <v>1158.323410863892</v>
+        <v>1264.926930379847</v>
       </c>
     </row>
     <row r="619">
@@ -8407,7 +8407,7 @@
         <v>2026</v>
       </c>
       <c r="D619">
-        <v>1228.443660923988</v>
+        <v>1422.074923318761</v>
       </c>
     </row>
     <row r="620">
@@ -8420,7 +8420,7 @@
         <v>2027</v>
       </c>
       <c r="D620">
-        <v>1293.797661649736</v>
+        <v>1598.814490967251</v>
       </c>
     </row>
     <row r="621">
@@ -8433,7 +8433,7 @@
         <v>2028</v>
       </c>
       <c r="D621">
-        <v>1354.313307860891</v>
+        <v>1797.528622256543</v>
       </c>
     </row>
     <row r="622">
@@ -8511,7 +8511,7 @@
         <v>2024</v>
       </c>
       <c r="D627">
-        <v>1354.00766510743</v>
+        <v>1369.919474612975</v>
       </c>
     </row>
     <row r="628">
@@ -8524,7 +8524,7 @@
         <v>2025</v>
       </c>
       <c r="D628">
-        <v>1393.313720727085</v>
+        <v>1442.374640650092</v>
       </c>
     </row>
     <row r="629">
@@ -8537,7 +8537,7 @@
         <v>2026</v>
       </c>
       <c r="D629">
-        <v>1422.419900534414</v>
+        <v>1518.635516410832</v>
       </c>
     </row>
     <row r="630">
@@ -8550,7 +8550,7 @@
         <v>2027</v>
       </c>
       <c r="D630">
-        <v>1443.826318903595</v>
+        <v>1598.930394378692</v>
       </c>
     </row>
     <row r="631">
@@ -8563,7 +8563,7 @@
         <v>2028</v>
       </c>
       <c r="D631">
-        <v>1459.49233457964</v>
+        <v>1683.470562075094</v>
       </c>
     </row>
     <row r="632">
@@ -8576,7 +8576,7 @@
         <v>2024</v>
       </c>
       <c r="D632">
-        <v>1354.00766510743</v>
+        <v>1369.919474612975</v>
       </c>
     </row>
     <row r="633">
@@ -8589,7 +8589,7 @@
         <v>2025</v>
       </c>
       <c r="D633">
-        <v>1393.313720727085</v>
+        <v>1442.374640650092</v>
       </c>
     </row>
     <row r="634">
@@ -8602,7 +8602,7 @@
         <v>2026</v>
       </c>
       <c r="D634">
-        <v>1422.419900534414</v>
+        <v>1518.635516410832</v>
       </c>
     </row>
     <row r="635">
@@ -8615,7 +8615,7 @@
         <v>2027</v>
       </c>
       <c r="D635">
-        <v>1443.826318903595</v>
+        <v>1598.930394378692</v>
       </c>
     </row>
     <row r="636">
@@ -8628,7 +8628,7 @@
         <v>2028</v>
       </c>
       <c r="D636">
-        <v>1459.49233457964</v>
+        <v>1683.470562075094</v>
       </c>
     </row>
     <row r="637">
@@ -8641,7 +8641,7 @@
         <v>2024</v>
       </c>
       <c r="D637">
-        <v>1262.565282741099</v>
+        <v>1682.748779769556</v>
       </c>
     </row>
     <row r="638">
@@ -8654,7 +8654,7 @@
         <v>2025</v>
       </c>
       <c r="D638">
-        <v>1275.087074377264</v>
+        <v>2428.770314935244</v>
       </c>
     </row>
     <row r="639">
@@ -8667,7 +8667,7 @@
         <v>2026</v>
       </c>
       <c r="D639">
-        <v>1280.232640509344</v>
+        <v>3548.590152347321</v>
       </c>
     </row>
     <row r="640">
@@ -8680,7 +8680,7 @@
         <v>2027</v>
       </c>
       <c r="D640">
-        <v>1282.338430033865</v>
+        <v>5198.664984704765</v>
       </c>
     </row>
     <row r="641">
@@ -8693,7 +8693,7 @@
         <v>2028</v>
       </c>
       <c r="D641">
-        <v>1283.198765988564</v>
+        <v>7620.517971847721</v>
       </c>
     </row>
     <row r="642">
@@ -8771,7 +8771,7 @@
         <v>2024</v>
       </c>
       <c r="D647">
-        <v>1506.270976366209</v>
+        <v>1957.299940924639</v>
       </c>
     </row>
     <row r="648">
@@ -8784,7 +8784,7 @@
         <v>2025</v>
       </c>
       <c r="D648">
-        <v>1506.344880544357</v>
+        <v>2389.118684486613</v>
       </c>
     </row>
     <row r="649">
@@ -8797,7 +8797,7 @@
         <v>2026</v>
       </c>
       <c r="D649">
-        <v>1506.34754244627</v>
+        <v>2969.552675852105</v>
       </c>
     </row>
     <row r="650">
@@ -8810,7 +8810,7 @@
         <v>2027</v>
       </c>
       <c r="D650">
-        <v>1506.347638321069</v>
+        <v>3672.078427258901</v>
       </c>
     </row>
     <row r="651">
@@ -8823,7 +8823,7 @@
         <v>2028</v>
       </c>
       <c r="D651">
-        <v>1506.347641774227</v>
+        <v>4547.428321183291</v>
       </c>
     </row>
     <row r="652">
@@ -8836,7 +8836,7 @@
         <v>2024</v>
       </c>
       <c r="D652">
-        <v>1225.870036857259</v>
+        <v>1658.023270557558</v>
       </c>
     </row>
     <row r="653">
@@ -8849,7 +8849,7 @@
         <v>2025</v>
       </c>
       <c r="D653">
-        <v>1226.088724553985</v>
+        <v>2163.540639627483</v>
       </c>
     </row>
     <row r="654">
@@ -8862,7 +8862,7 @@
         <v>2026</v>
       </c>
       <c r="D654">
-        <v>1226.100369402411</v>
+        <v>2841.14462061613</v>
       </c>
     </row>
     <row r="655">
@@ -8875,7 +8875,7 @@
         <v>2027</v>
       </c>
       <c r="D655">
-        <v>1226.100989420993</v>
+        <v>3727.144462326798</v>
       </c>
     </row>
     <row r="656">
@@ -8888,7 +8888,7 @@
         <v>2028</v>
       </c>
       <c r="D656">
-        <v>1226.10102243312</v>
+        <v>4890.250978403921</v>
       </c>
     </row>
     <row r="657">
@@ -9681,7 +9681,7 @@
         <v>2024</v>
       </c>
       <c r="D717">
-        <v>1432.692632815597</v>
+        <v>2081.814081165859</v>
       </c>
     </row>
     <row r="718">
@@ -9694,7 +9694,7 @@
         <v>2025</v>
       </c>
       <c r="D718">
-        <v>1433.164087406016</v>
+        <v>2656.261865297889</v>
       </c>
     </row>
     <row r="719">
@@ -9707,7 +9707,7 @@
         <v>2026</v>
       </c>
       <c r="D719">
-        <v>1433.20598366691</v>
+        <v>3574.598793428233</v>
       </c>
     </row>
     <row r="720">
@@ -9720,7 +9720,7 @@
         <v>2027</v>
       </c>
       <c r="D720">
-        <v>1433.209706210426</v>
+        <v>4709.474839323306</v>
       </c>
     </row>
     <row r="721">
@@ -9733,7 +9733,7 @@
         <v>2028</v>
       </c>
       <c r="D721">
-        <v>1433.210036959017</v>
+        <v>6257.290570819521</v>
       </c>
     </row>
     <row r="722">
@@ -9746,7 +9746,7 @@
         <v>2024</v>
       </c>
       <c r="D722">
-        <v>1148.658610804667</v>
+        <v>1286.032936737007</v>
       </c>
     </row>
     <row r="723">
@@ -9759,7 +9759,7 @@
         <v>2025</v>
       </c>
       <c r="D723">
-        <v>1164.40777590775</v>
+        <v>1434.523881767622</v>
       </c>
     </row>
     <row r="724">
@@ -9772,7 +9772,7 @@
         <v>2026</v>
       </c>
       <c r="D724">
-        <v>1171.467963154553</v>
+        <v>1625.72782552845</v>
       </c>
     </row>
     <row r="725">
@@ -9785,7 +9785,7 @@
         <v>2027</v>
       </c>
       <c r="D725">
-        <v>1174.615731056085</v>
+        <v>1828.997423645414</v>
       </c>
     </row>
     <row r="726">
@@ -9798,7 +9798,7 @@
         <v>2028</v>
       </c>
       <c r="D726">
-        <v>1176.01575549232</v>
+        <v>2064.630998389611</v>
       </c>
     </row>
     <row r="727">
@@ -9811,7 +9811,7 @@
         <v>2024</v>
       </c>
       <c r="D727">
-        <v>949.7366108501675</v>
+        <v>955.0791805721416</v>
       </c>
     </row>
     <row r="728">
@@ -9824,7 +9824,7 @@
         <v>2025</v>
       </c>
       <c r="D728">
-        <v>1011.908426280464</v>
+        <v>1027.890858476301</v>
       </c>
     </row>
     <row r="729">
@@ -9837,7 +9837,7 @@
         <v>2026</v>
       </c>
       <c r="D729">
-        <v>1074.078511069307</v>
+        <v>1106.405791844594</v>
       </c>
     </row>
     <row r="730">
@@ -9850,7 +9850,7 @@
         <v>2027</v>
       </c>
       <c r="D730">
-        <v>1136.019217529818</v>
+        <v>1190.970819519613</v>
       </c>
     </row>
     <row r="731">
@@ -9863,7 +9863,7 @@
         <v>2028</v>
       </c>
       <c r="D731">
-        <v>1197.518867921696</v>
+        <v>1282.017614342297</v>
       </c>
     </row>
     <row r="732">
@@ -9876,7 +9876,7 @@
         <v>2024</v>
       </c>
       <c r="D732">
-        <v>1309.794431009556</v>
+        <v>1317.162412681181</v>
       </c>
     </row>
     <row r="733">
@@ -9889,7 +9889,7 @@
         <v>2025</v>
       </c>
       <c r="D733">
-        <v>1395.5364862068</v>
+        <v>1417.577974895148</v>
       </c>
     </row>
     <row r="734">
@@ -9902,7 +9902,7 @@
         <v>2026</v>
       </c>
       <c r="D734">
-        <v>1481.276196585163</v>
+        <v>1525.858970521967</v>
       </c>
     </row>
     <row r="735">
@@ -9915,7 +9915,7 @@
         <v>2027</v>
       </c>
       <c r="D735">
-        <v>1566.699611361541</v>
+        <v>1642.483730646015</v>
       </c>
     </row>
     <row r="736">
@@ -9928,7 +9928,7 @@
         <v>2028</v>
       </c>
       <c r="D736">
-        <v>1651.514803444124</v>
+        <v>1768.047581822121</v>
       </c>
     </row>
     <row r="737">
@@ -9941,7 +9941,7 @@
         <v>2024</v>
       </c>
       <c r="D737">
-        <v>1309.794431009556</v>
+        <v>1317.162412681181</v>
       </c>
     </row>
     <row r="738">
@@ -9954,7 +9954,7 @@
         <v>2025</v>
       </c>
       <c r="D738">
-        <v>1395.5364862068</v>
+        <v>1417.577974895148</v>
       </c>
     </row>
     <row r="739">
@@ -9967,7 +9967,7 @@
         <v>2026</v>
       </c>
       <c r="D739">
-        <v>1481.276196585163</v>
+        <v>1525.858970521967</v>
       </c>
     </row>
     <row r="740">
@@ -9980,7 +9980,7 @@
         <v>2027</v>
       </c>
       <c r="D740">
-        <v>1566.699611361541</v>
+        <v>1642.483730646015</v>
       </c>
     </row>
     <row r="741">
@@ -9993,7 +9993,7 @@
         <v>2028</v>
       </c>
       <c r="D741">
-        <v>1651.514803444124</v>
+        <v>1768.047581822121</v>
       </c>
     </row>
     <row r="742">
@@ -10006,7 +10006,7 @@
         <v>2024</v>
       </c>
       <c r="D742">
-        <v>1309.794431009556</v>
+        <v>1317.162412681181</v>
       </c>
     </row>
     <row r="743">
@@ -10019,7 +10019,7 @@
         <v>2025</v>
       </c>
       <c r="D743">
-        <v>1395.5364862068</v>
+        <v>1417.577974895148</v>
       </c>
     </row>
     <row r="744">
@@ -10032,7 +10032,7 @@
         <v>2026</v>
       </c>
       <c r="D744">
-        <v>1481.276196585163</v>
+        <v>1525.858970521967</v>
       </c>
     </row>
     <row r="745">
@@ -10045,7 +10045,7 @@
         <v>2027</v>
       </c>
       <c r="D745">
-        <v>1566.699611361541</v>
+        <v>1642.483730646015</v>
       </c>
     </row>
     <row r="746">
@@ -10058,7 +10058,7 @@
         <v>2028</v>
       </c>
       <c r="D746">
-        <v>1651.514803444124</v>
+        <v>1768.047581822121</v>
       </c>
     </row>
     <row r="747">
@@ -10071,7 +10071,7 @@
         <v>2024</v>
       </c>
       <c r="D747">
-        <v>1309.794430983976</v>
+        <v>1317.16241268131</v>
       </c>
     </row>
     <row r="748">
@@ -10084,7 +10084,7 @@
         <v>2025</v>
       </c>
       <c r="D748">
-        <v>1395.536486128286</v>
+        <v>1417.577974895471</v>
       </c>
     </row>
     <row r="749">
@@ -10097,7 +10097,7 @@
         <v>2026</v>
       </c>
       <c r="D749">
-        <v>1481.276196425082</v>
+        <v>1525.858970522532</v>
       </c>
     </row>
     <row r="750">
@@ -10110,7 +10110,7 @@
         <v>2027</v>
       </c>
       <c r="D750">
-        <v>1566.69961109046</v>
+        <v>1642.483730646861</v>
       </c>
     </row>
     <row r="751">
@@ -10123,7 +10123,7 @@
         <v>2028</v>
       </c>
       <c r="D751">
-        <v>1651.514803032274</v>
+        <v>1768.047581823294</v>
       </c>
     </row>
     <row r="752">
@@ -10136,7 +10136,7 @@
         <v>2024</v>
       </c>
       <c r="D752">
-        <v>1309.794431009556</v>
+        <v>1317.162412681181</v>
       </c>
     </row>
     <row r="753">
@@ -10149,7 +10149,7 @@
         <v>2025</v>
       </c>
       <c r="D753">
-        <v>1395.5364862068</v>
+        <v>1417.577974895148</v>
       </c>
     </row>
     <row r="754">
@@ -10162,7 +10162,7 @@
         <v>2026</v>
       </c>
       <c r="D754">
-        <v>1481.276196585163</v>
+        <v>1525.858970521967</v>
       </c>
     </row>
     <row r="755">
@@ -10175,7 +10175,7 @@
         <v>2027</v>
       </c>
       <c r="D755">
-        <v>1566.699611361541</v>
+        <v>1642.483730646015</v>
       </c>
     </row>
     <row r="756">
@@ -10188,7 +10188,7 @@
         <v>2028</v>
       </c>
       <c r="D756">
-        <v>1651.514803444124</v>
+        <v>1768.047581822121</v>
       </c>
     </row>
     <row r="757">
@@ -10201,7 +10201,7 @@
         <v>2024</v>
       </c>
       <c r="D757">
-        <v>1309.794431009556</v>
+        <v>1317.162412681181</v>
       </c>
     </row>
     <row r="758">
@@ -10214,7 +10214,7 @@
         <v>2025</v>
       </c>
       <c r="D758">
-        <v>1395.5364862068</v>
+        <v>1417.577974895148</v>
       </c>
     </row>
     <row r="759">
@@ -10227,7 +10227,7 @@
         <v>2026</v>
       </c>
       <c r="D759">
-        <v>1481.276196585163</v>
+        <v>1525.858970521967</v>
       </c>
     </row>
     <row r="760">
@@ -10240,7 +10240,7 @@
         <v>2027</v>
       </c>
       <c r="D760">
-        <v>1566.699611361541</v>
+        <v>1642.483730646015</v>
       </c>
     </row>
     <row r="761">
@@ -10253,7 +10253,7 @@
         <v>2028</v>
       </c>
       <c r="D761">
-        <v>1651.514803444124</v>
+        <v>1768.047581822121</v>
       </c>
     </row>
     <row r="762">
@@ -10266,7 +10266,7 @@
         <v>2024</v>
       </c>
       <c r="D762">
-        <v>1309.794431009556</v>
+        <v>1317.162412681181</v>
       </c>
     </row>
     <row r="763">
@@ -10279,7 +10279,7 @@
         <v>2025</v>
       </c>
       <c r="D763">
-        <v>1395.5364862068</v>
+        <v>1417.577974895148</v>
       </c>
     </row>
     <row r="764">
@@ -10292,7 +10292,7 @@
         <v>2026</v>
       </c>
       <c r="D764">
-        <v>1481.276196585163</v>
+        <v>1525.858970521967</v>
       </c>
     </row>
     <row r="765">
@@ -10305,7 +10305,7 @@
         <v>2027</v>
       </c>
       <c r="D765">
-        <v>1566.699611361541</v>
+        <v>1642.483730646015</v>
       </c>
     </row>
     <row r="766">
@@ -10318,7 +10318,7 @@
         <v>2028</v>
       </c>
       <c r="D766">
-        <v>1651.514803444124</v>
+        <v>1768.047581822121</v>
       </c>
     </row>
     <row r="767">
@@ -10331,7 +10331,7 @@
         <v>2024</v>
       </c>
       <c r="D767">
-        <v>437.9596669814744</v>
+        <v>440.4233513349223</v>
       </c>
     </row>
     <row r="768">
@@ -10344,7 +10344,7 @@
         <v>2025</v>
       </c>
       <c r="D768">
-        <v>466.6293947710244</v>
+        <v>473.9995803082409</v>
       </c>
     </row>
     <row r="769">
@@ -10357,7 +10357,7 @@
         <v>2026</v>
       </c>
       <c r="D769">
-        <v>495.2982906909704</v>
+        <v>510.2057991176965</v>
       </c>
     </row>
     <row r="770">
@@ -10370,7 +10370,7 @@
         <v>2027</v>
       </c>
       <c r="D770">
-        <v>523.8613767856416</v>
+        <v>549.2019475304099</v>
       </c>
     </row>
     <row r="771">
@@ -10383,7 +10383,7 @@
         <v>2028</v>
       </c>
       <c r="D771">
-        <v>552.221039993291</v>
+        <v>591.1870856828357</v>
       </c>
     </row>
     <row r="772">
@@ -10396,7 +10396,7 @@
         <v>2024</v>
       </c>
       <c r="D772">
-        <v>223.1146664821797</v>
+        <v>224.3697784915646</v>
       </c>
     </row>
     <row r="773">
@@ -10409,7 +10409,7 @@
         <v>2025</v>
       </c>
       <c r="D773">
-        <v>237.7201780773961</v>
+        <v>241.4748884044309</v>
       </c>
     </row>
     <row r="774">
@@ -10422,7 +10422,7 @@
         <v>2026</v>
       </c>
       <c r="D774">
-        <v>252.3252508854947</v>
+        <v>259.9198241286077</v>
       </c>
     </row>
     <row r="775">
@@ -10435,7 +10435,7 @@
         <v>2027</v>
       </c>
       <c r="D775">
-        <v>266.8764043967276</v>
+        <v>279.786065198734</v>
       </c>
     </row>
     <row r="776">
@@ -10448,7 +10448,7 @@
         <v>2028</v>
       </c>
       <c r="D776">
-        <v>281.3239103226919</v>
+        <v>301.1750207569866</v>
       </c>
     </row>
     <row r="777">
@@ -10526,7 +10526,7 @@
         <v>2024</v>
       </c>
       <c r="D782">
-        <v>1022.589007068391</v>
+        <v>1025.579969215592</v>
       </c>
     </row>
     <row r="783">
@@ -10539,7 +10539,7 @@
         <v>2025</v>
       </c>
       <c r="D783">
-        <v>1085.042195003126</v>
+        <v>1095.47715099675</v>
       </c>
     </row>
     <row r="784">
@@ -10552,7 +10552,7 @@
         <v>2026</v>
       </c>
       <c r="D784">
-        <v>1145.160958455216</v>
+        <v>1168.606123721413</v>
       </c>
     </row>
     <row r="785">
@@ -10565,7 +10565,7 @@
         <v>2027</v>
       </c>
       <c r="D785">
-        <v>1202.737661593499</v>
+        <v>1245.625199618813</v>
       </c>
     </row>
     <row r="786">
@@ -10578,7 +10578,7 @@
         <v>2028</v>
       </c>
       <c r="D786">
-        <v>1257.624110398745</v>
+        <v>1327.078704141171</v>
       </c>
     </row>
     <row r="787">
@@ -10591,7 +10591,7 @@
         <v>2024</v>
       </c>
       <c r="D787">
-        <v>1022.589007078032</v>
+        <v>1025.57996922379</v>
       </c>
     </row>
     <row r="788">
@@ -10604,7 +10604,7 @@
         <v>2025</v>
       </c>
       <c r="D788">
-        <v>1085.042195031968</v>
+        <v>1095.477150998819</v>
       </c>
     </row>
     <row r="789">
@@ -10617,7 +10617,7 @@
         <v>2026</v>
       </c>
       <c r="D789">
-        <v>1145.16095851246</v>
+        <v>1168.606123693026</v>
       </c>
     </row>
     <row r="790">
@@ -10630,7 +10630,7 @@
         <v>2027</v>
       </c>
       <c r="D790">
-        <v>1202.737661687765</v>
+        <v>1245.625199532044</v>
       </c>
     </row>
     <row r="791">
@@ -10643,7 +10643,7 @@
         <v>2028</v>
       </c>
       <c r="D791">
-        <v>1257.624110537909</v>
+        <v>1327.078703967416</v>
       </c>
     </row>
     <row r="792">
@@ -10656,7 +10656,7 @@
         <v>2024</v>
       </c>
       <c r="D792">
-        <v>1127.232957260337</v>
+        <v>1142.324985386801</v>
       </c>
     </row>
     <row r="793">
@@ -10669,7 +10669,7 @@
         <v>2025</v>
       </c>
       <c r="D793">
-        <v>1168.239105590234</v>
+        <v>1210.478237967179</v>
       </c>
     </row>
     <row r="794">
@@ -10682,7 +10682,7 @@
         <v>2026</v>
       </c>
       <c r="D794">
-        <v>1203.826670487417</v>
+        <v>1283.792229960093</v>
       </c>
     </row>
     <row r="795">
@@ -10695,7 +10695,7 @@
         <v>2027</v>
       </c>
       <c r="D795">
-        <v>1234.54961493092</v>
+        <v>1362.017747306137</v>
       </c>
     </row>
     <row r="796">
@@ -10708,7 +10708,7 @@
         <v>2028</v>
       </c>
       <c r="D796">
-        <v>1260.955965817003</v>
+        <v>1445.212616156559</v>
       </c>
     </row>
     <row r="797">
@@ -10721,7 +10721,7 @@
         <v>2024</v>
       </c>
       <c r="D797">
-        <v>1131.564292074821</v>
+        <v>1144.046329105066</v>
       </c>
     </row>
     <row r="798">
@@ -10734,7 +10734,7 @@
         <v>2025</v>
       </c>
       <c r="D798">
-        <v>1170.475776782679</v>
+        <v>1206.445798586448</v>
       </c>
     </row>
     <row r="799">
@@ -10747,7 +10747,7 @@
         <v>2026</v>
       </c>
       <c r="D799">
-        <v>1203.351146338615</v>
+        <v>1272.76502420194</v>
       </c>
     </row>
     <row r="800">
@@ -10760,7 +10760,7 @@
         <v>2027</v>
       </c>
       <c r="D800">
-        <v>1230.972959980861</v>
+        <v>1342.983735313944</v>
       </c>
     </row>
     <row r="801">
@@ -10773,7 +10773,7 @@
         <v>2028</v>
       </c>
       <c r="D801">
-        <v>1254.075399054271</v>
+        <v>1417.201256051554</v>
       </c>
     </row>
     <row r="802">
@@ -10786,7 +10786,7 @@
         <v>2024</v>
       </c>
       <c r="D802">
-        <v>912.816652366281</v>
+        <v>924.7026485909397</v>
       </c>
     </row>
     <row r="803">
@@ -10799,7 +10799,7 @@
         <v>2025</v>
       </c>
       <c r="D803">
-        <v>950.1793506100319</v>
+        <v>982.9856548336689</v>
       </c>
     </row>
     <row r="804">
@@ -10812,7 +10812,7 @@
         <v>2026</v>
       </c>
       <c r="D804">
-        <v>983.5393785968025</v>
+        <v>1045.410288437349</v>
       </c>
     </row>
     <row r="805">
@@ -10825,7 +10825,7 @@
         <v>2027</v>
       </c>
       <c r="D805">
-        <v>1013.170696430061</v>
+        <v>1111.943199035313</v>
       </c>
     </row>
     <row r="806">
@@ -10838,7 +10838,7 @@
         <v>2028</v>
       </c>
       <c r="D806">
-        <v>1039.372317724288</v>
+        <v>1182.754743991404</v>
       </c>
     </row>
     <row r="807">
@@ -10851,7 +10851,7 @@
         <v>2024</v>
       </c>
       <c r="D807">
-        <v>918.7187988588282</v>
+        <v>929.7678542637816</v>
       </c>
     </row>
     <row r="808">
@@ -10864,7 +10864,7 @@
         <v>2025</v>
       </c>
       <c r="D808">
-        <v>957.4698240295137</v>
+        <v>988.383677284402</v>
       </c>
     </row>
     <row r="809">
@@ -10877,7 +10877,7 @@
         <v>2026</v>
       </c>
       <c r="D809">
-        <v>992.301951262788</v>
+        <v>1051.162717978329</v>
       </c>
     </row>
     <row r="810">
@@ -10890,7 +10890,7 @@
         <v>2027</v>
       </c>
       <c r="D810">
-        <v>1023.449130470372</v>
+        <v>1118.085936594954</v>
       </c>
     </row>
     <row r="811">
@@ -10903,7 +10903,7 @@
         <v>2028</v>
       </c>
       <c r="D811">
-        <v>1051.176212555335</v>
+        <v>1189.322327282559</v>
       </c>
     </row>
     <row r="812">
@@ -10916,7 +10916,7 @@
         <v>2024</v>
       </c>
       <c r="D812">
-        <v>1625.579610788247</v>
+        <v>1642.560928364055</v>
       </c>
     </row>
     <row r="813">
@@ -10929,7 +10929,7 @@
         <v>2025</v>
       </c>
       <c r="D813">
-        <v>1681.078033445736</v>
+        <v>1728.855200753731</v>
       </c>
     </row>
     <row r="814">
@@ -10942,7 +10942,7 @@
         <v>2026</v>
       </c>
       <c r="D814">
-        <v>1730.652737593273</v>
+        <v>1821.402371608616</v>
       </c>
     </row>
     <row r="815">
@@ -10955,7 +10955,7 @@
         <v>2027</v>
       </c>
       <c r="D815">
-        <v>1774.750317039305</v>
+        <v>1919.745524281756</v>
       </c>
     </row>
     <row r="816">
@@ -10968,7 +10968,7 @@
         <v>2028</v>
       </c>
       <c r="D816">
-        <v>1813.833450232213</v>
+        <v>2023.810762868771</v>
       </c>
     </row>
     <row r="817">
@@ -10981,7 +10981,7 @@
         <v>2024</v>
       </c>
       <c r="D817">
-        <v>1553.724075428329</v>
+        <v>1559.88631295132</v>
       </c>
     </row>
     <row r="818">
@@ -10994,7 +10994,7 @@
         <v>2025</v>
       </c>
       <c r="D818">
-        <v>1626.663848876674</v>
+        <v>1647.704885328476</v>
       </c>
     </row>
     <row r="819">
@@ -11007,7 +11007,7 @@
         <v>2026</v>
       </c>
       <c r="D819">
-        <v>1692.023886796315</v>
+        <v>1738.009603126662</v>
       </c>
     </row>
     <row r="820">
@@ -11020,7 +11020,7 @@
         <v>2027</v>
       </c>
       <c r="D820">
-        <v>1750.240436084532</v>
+        <v>1831.863192544255</v>
       </c>
     </row>
     <row r="821">
@@ -11033,7 +11033,7 @@
         <v>2028</v>
       </c>
       <c r="D821">
-        <v>1801.826916924461</v>
+        <v>1929.987248015037</v>
       </c>
     </row>
     <row r="822">
@@ -11046,7 +11046,7 @@
         <v>2024</v>
       </c>
       <c r="D822">
-        <v>1627.498912533883</v>
+        <v>1644.498802468367</v>
       </c>
     </row>
     <row r="823">
@@ -11059,7 +11059,7 @@
         <v>2025</v>
       </c>
       <c r="D823">
-        <v>1683.041745242904</v>
+        <v>1730.871181668455</v>
       </c>
     </row>
     <row r="824">
@@ -11072,7 +11072,7 @@
         <v>2026</v>
       </c>
       <c r="D824">
-        <v>1732.654040772479</v>
+        <v>1823.502283141811</v>
       </c>
     </row>
     <row r="825">
@@ -11085,7 +11085,7 @@
         <v>2027</v>
       </c>
       <c r="D825">
-        <v>1776.78324590902</v>
+        <v>1921.93427335516</v>
       </c>
     </row>
     <row r="826">
@@ -11098,7 +11098,7 @@
         <v>2028</v>
       </c>
       <c r="D826">
-        <v>1815.892834275332</v>
+        <v>2026.092773112435</v>
       </c>
     </row>
     <row r="827">
@@ -11111,7 +11111,7 @@
         <v>2024</v>
       </c>
       <c r="D827">
-        <v>1553.724075428329</v>
+        <v>1559.88631295132</v>
       </c>
     </row>
     <row r="828">
@@ -11124,7 +11124,7 @@
         <v>2025</v>
       </c>
       <c r="D828">
-        <v>1626.663848876674</v>
+        <v>1647.704885328476</v>
       </c>
     </row>
     <row r="829">
@@ -11137,7 +11137,7 @@
         <v>2026</v>
       </c>
       <c r="D829">
-        <v>1692.023886796315</v>
+        <v>1738.009603126662</v>
       </c>
     </row>
     <row r="830">
@@ -11150,7 +11150,7 @@
         <v>2027</v>
       </c>
       <c r="D830">
-        <v>1750.240436084532</v>
+        <v>1831.863192544255</v>
       </c>
     </row>
     <row r="831">
@@ -11163,7 +11163,7 @@
         <v>2028</v>
       </c>
       <c r="D831">
-        <v>1801.826916924461</v>
+        <v>1929.987248015037</v>
       </c>
     </row>
     <row r="832">
@@ -11176,7 +11176,7 @@
         <v>2024</v>
       </c>
       <c r="D832">
-        <v>1557.59693904545</v>
+        <v>1564.181525802859</v>
       </c>
     </row>
     <row r="833">
@@ -11189,7 +11189,7 @@
         <v>2025</v>
       </c>
       <c r="D833">
-        <v>1635.07635707799</v>
+        <v>1656.793180654984</v>
       </c>
     </row>
     <row r="834">
@@ -11202,7 +11202,7 @@
         <v>2026</v>
       </c>
       <c r="D834">
-        <v>1706.908626293422</v>
+        <v>1753.488580504545</v>
       </c>
     </row>
     <row r="835">
@@ -11215,7 +11215,7 @@
         <v>2027</v>
       </c>
       <c r="D835">
-        <v>1773.158020571782</v>
+        <v>1855.045281085703</v>
       </c>
     </row>
     <row r="836">
@@ -11228,7 +11228,7 @@
         <v>2028</v>
       </c>
       <c r="D836">
-        <v>1833.97611270785</v>
+        <v>1962.046813468321</v>
       </c>
     </row>
     <row r="837">
@@ -11241,7 +11241,7 @@
         <v>2024</v>
       </c>
       <c r="D837">
-        <v>1627.498912533883</v>
+        <v>1644.498802468367</v>
       </c>
     </row>
     <row r="838">
@@ -11254,7 +11254,7 @@
         <v>2025</v>
       </c>
       <c r="D838">
-        <v>1683.041745242904</v>
+        <v>1730.871181668455</v>
       </c>
     </row>
     <row r="839">
@@ -11267,7 +11267,7 @@
         <v>2026</v>
       </c>
       <c r="D839">
-        <v>1732.654040772479</v>
+        <v>1823.502283141811</v>
       </c>
     </row>
     <row r="840">
@@ -11280,7 +11280,7 @@
         <v>2027</v>
       </c>
       <c r="D840">
-        <v>1776.78324590902</v>
+        <v>1921.93427335516</v>
       </c>
     </row>
     <row r="841">
@@ -11293,7 +11293,7 @@
         <v>2028</v>
       </c>
       <c r="D841">
-        <v>1815.892834275332</v>
+        <v>2026.092773112435</v>
       </c>
     </row>
     <row r="842">
@@ -11306,7 +11306,7 @@
         <v>2024</v>
       </c>
       <c r="D842">
-        <v>1619.174453393392</v>
+        <v>1636.093866597869</v>
       </c>
     </row>
     <row r="843">
@@ -11319,7 +11319,7 @@
         <v>2025</v>
       </c>
       <c r="D843">
-        <v>1674.524650807719</v>
+        <v>1722.127561978306</v>
       </c>
     </row>
     <row r="844">
@@ -11332,7 +11332,7 @@
         <v>2026</v>
       </c>
       <c r="D844">
-        <v>1723.973879936788</v>
+        <v>1814.394728214262</v>
       </c>
     </row>
     <row r="845">
@@ -11345,7 +11345,7 @@
         <v>2027</v>
       </c>
       <c r="D845">
-        <v>1767.965890176224</v>
+        <v>1912.441508700872</v>
       </c>
     </row>
     <row r="846">
@@ -11358,7 +11358,7 @@
         <v>2028</v>
       </c>
       <c r="D846">
-        <v>1806.960708013164</v>
+        <v>2016.195623053721</v>
       </c>
     </row>
     <row r="847">
@@ -11371,7 +11371,7 @@
         <v>2024</v>
       </c>
       <c r="D847">
-        <v>912.816652366281</v>
+        <v>924.7026485909397</v>
       </c>
     </row>
     <row r="848">
@@ -11384,7 +11384,7 @@
         <v>2025</v>
       </c>
       <c r="D848">
-        <v>950.1793506100319</v>
+        <v>982.9856548336689</v>
       </c>
     </row>
     <row r="849">
@@ -11397,7 +11397,7 @@
         <v>2026</v>
       </c>
       <c r="D849">
-        <v>983.5393785968025</v>
+        <v>1045.410288437349</v>
       </c>
     </row>
     <row r="850">
@@ -11410,7 +11410,7 @@
         <v>2027</v>
       </c>
       <c r="D850">
-        <v>1013.170696430061</v>
+        <v>1111.943199035313</v>
       </c>
     </row>
     <row r="851">
@@ -11423,7 +11423,7 @@
         <v>2028</v>
       </c>
       <c r="D851">
-        <v>1039.372317724288</v>
+        <v>1182.754743991404</v>
       </c>
     </row>
     <row r="852">
@@ -11436,7 +11436,7 @@
         <v>2024</v>
       </c>
       <c r="D852">
-        <v>912.816652366281</v>
+        <v>924.7026485909397</v>
       </c>
     </row>
     <row r="853">
@@ -11449,7 +11449,7 @@
         <v>2025</v>
       </c>
       <c r="D853">
-        <v>950.1793506100319</v>
+        <v>982.9856548336689</v>
       </c>
     </row>
     <row r="854">
@@ -11462,7 +11462,7 @@
         <v>2026</v>
       </c>
       <c r="D854">
-        <v>983.5393785968025</v>
+        <v>1045.410288437349</v>
       </c>
     </row>
     <row r="855">
@@ -11475,7 +11475,7 @@
         <v>2027</v>
       </c>
       <c r="D855">
-        <v>1013.170696430061</v>
+        <v>1111.943199035313</v>
       </c>
     </row>
     <row r="856">
@@ -11488,7 +11488,7 @@
         <v>2028</v>
       </c>
       <c r="D856">
-        <v>1039.372317724288</v>
+        <v>1182.754743991404</v>
       </c>
     </row>
     <row r="857">
@@ -11501,7 +11501,7 @@
         <v>2024</v>
       </c>
       <c r="D857">
-        <v>912.816652366281</v>
+        <v>924.7026485909397</v>
       </c>
     </row>
     <row r="858">
@@ -11514,7 +11514,7 @@
         <v>2025</v>
       </c>
       <c r="D858">
-        <v>950.1793506100319</v>
+        <v>982.9856548336689</v>
       </c>
     </row>
     <row r="859">
@@ -11527,7 +11527,7 @@
         <v>2026</v>
       </c>
       <c r="D859">
-        <v>983.5393785968025</v>
+        <v>1045.410288437349</v>
       </c>
     </row>
     <row r="860">
@@ -11540,7 +11540,7 @@
         <v>2027</v>
       </c>
       <c r="D860">
-        <v>1013.170696430061</v>
+        <v>1111.943199035313</v>
       </c>
     </row>
     <row r="861">
@@ -11553,7 +11553,7 @@
         <v>2028</v>
       </c>
       <c r="D861">
-        <v>1039.372317724288</v>
+        <v>1182.754743991404</v>
       </c>
     </row>
     <row r="862">
@@ -11566,7 +11566,7 @@
         <v>2024</v>
       </c>
       <c r="D862">
-        <v>912.816652366281</v>
+        <v>924.7026485909397</v>
       </c>
     </row>
     <row r="863">
@@ -11579,7 +11579,7 @@
         <v>2025</v>
       </c>
       <c r="D863">
-        <v>950.1793506100319</v>
+        <v>982.9856548336689</v>
       </c>
     </row>
     <row r="864">
@@ -11592,7 +11592,7 @@
         <v>2026</v>
       </c>
       <c r="D864">
-        <v>983.5393785968025</v>
+        <v>1045.410288437349</v>
       </c>
     </row>
     <row r="865">
@@ -11605,7 +11605,7 @@
         <v>2027</v>
       </c>
       <c r="D865">
-        <v>1013.170696430061</v>
+        <v>1111.943199035313</v>
       </c>
     </row>
     <row r="866">
@@ -11618,7 +11618,7 @@
         <v>2028</v>
       </c>
       <c r="D866">
-        <v>1039.372317724288</v>
+        <v>1182.754743991404</v>
       </c>
     </row>
     <row r="867">
@@ -11631,7 +11631,7 @@
         <v>2024</v>
       </c>
       <c r="D867">
-        <v>965.9698493816027</v>
+        <v>971.9527426721593</v>
       </c>
     </row>
     <row r="868">
@@ -11644,7 +11644,7 @@
         <v>2025</v>
       </c>
       <c r="D868">
-        <v>1015.82907990739</v>
+        <v>1034.358080007895</v>
       </c>
     </row>
     <row r="869">
@@ -11657,7 +11657,7 @@
         <v>2026</v>
       </c>
       <c r="D869">
-        <v>1062.570531042529</v>
+        <v>1100.636313179543</v>
       </c>
     </row>
     <row r="870">
@@ -11670,7 +11670,7 @@
         <v>2027</v>
       </c>
       <c r="D870">
-        <v>1106.16825729746</v>
+        <v>1171.091934352098</v>
       </c>
     </row>
     <row r="871">
@@ -11683,7 +11683,7 @@
         <v>2028</v>
       </c>
       <c r="D871">
-        <v>1146.650384032747</v>
+        <v>1246.021597276651</v>
       </c>
     </row>
     <row r="872">
@@ -11696,7 +11696,7 @@
         <v>2024</v>
       </c>
       <c r="D872">
-        <v>912.816652366281</v>
+        <v>924.7026485909397</v>
       </c>
     </row>
     <row r="873">
@@ -11709,7 +11709,7 @@
         <v>2025</v>
       </c>
       <c r="D873">
-        <v>950.1793506100319</v>
+        <v>982.9856548336689</v>
       </c>
     </row>
     <row r="874">
@@ -11722,7 +11722,7 @@
         <v>2026</v>
       </c>
       <c r="D874">
-        <v>983.5393785968025</v>
+        <v>1045.410288437349</v>
       </c>
     </row>
     <row r="875">
@@ -11735,7 +11735,7 @@
         <v>2027</v>
       </c>
       <c r="D875">
-        <v>1013.170696430061</v>
+        <v>1111.943199035313</v>
       </c>
     </row>
     <row r="876">
@@ -11748,7 +11748,7 @@
         <v>2028</v>
       </c>
       <c r="D876">
-        <v>1039.372317724288</v>
+        <v>1182.754743991404</v>
       </c>
     </row>
     <row r="877">
@@ -11891,7 +11891,7 @@
         <v>2024</v>
       </c>
       <c r="D887">
-        <v>912.816652366281</v>
+        <v>924.7026485909397</v>
       </c>
     </row>
     <row r="888">
@@ -11904,7 +11904,7 @@
         <v>2025</v>
       </c>
       <c r="D888">
-        <v>950.1793506100319</v>
+        <v>982.9856548336689</v>
       </c>
     </row>
     <row r="889">
@@ -11917,7 +11917,7 @@
         <v>2026</v>
       </c>
       <c r="D889">
-        <v>983.5393785968025</v>
+        <v>1045.410288437349</v>
       </c>
     </row>
     <row r="890">
@@ -11930,7 +11930,7 @@
         <v>2027</v>
       </c>
       <c r="D890">
-        <v>1013.170696430061</v>
+        <v>1111.943199035313</v>
       </c>
     </row>
     <row r="891">
@@ -11943,7 +11943,7 @@
         <v>2028</v>
       </c>
       <c r="D891">
-        <v>1039.372317724288</v>
+        <v>1182.754743991404</v>
       </c>
     </row>
     <row r="892">
@@ -11956,7 +11956,7 @@
         <v>2024</v>
       </c>
       <c r="D892">
-        <v>1804.981459917957</v>
+        <v>1812.640779517384</v>
       </c>
     </row>
     <row r="893">
@@ -11969,7 +11969,7 @@
         <v>2025</v>
       </c>
       <c r="D893">
-        <v>1877.027039101772</v>
+        <v>1900.790688883108</v>
       </c>
     </row>
     <row r="894">
@@ -11982,7 +11982,7 @@
         <v>2026</v>
       </c>
       <c r="D894">
-        <v>1943.050493828501</v>
+        <v>1991.844896203598</v>
       </c>
     </row>
     <row r="895">
@@ -11995,7 +11995,7 @@
         <v>2027</v>
       </c>
       <c r="D895">
-        <v>2003.295642639186</v>
+        <v>2086.313890340407</v>
       </c>
     </row>
     <row r="896">
@@ -12008,7 +12008,7 @@
         <v>2028</v>
       </c>
       <c r="D896">
-        <v>2058.059831399085</v>
+        <v>2184.614805712344</v>
       </c>
     </row>
     <row r="897">
@@ -12086,7 +12086,7 @@
         <v>2024</v>
       </c>
       <c r="D902">
-        <v>1696.488618445461</v>
+        <v>1878.151204244292</v>
       </c>
     </row>
     <row r="903">
@@ -12099,7 +12099,7 @@
         <v>2025</v>
       </c>
       <c r="D903">
-        <v>1715.565556751788</v>
+        <v>2054.122876564645</v>
       </c>
     </row>
     <row r="904">
@@ -12112,7 +12112,7 @@
         <v>2026</v>
       </c>
       <c r="D904">
-        <v>1724.853127170532</v>
+        <v>2283.326816559544</v>
       </c>
     </row>
     <row r="905">
@@ -12125,7 +12125,7 @@
         <v>2027</v>
       </c>
       <c r="D905">
-        <v>1729.355430816947</v>
+        <v>2519.265481007933</v>
       </c>
     </row>
     <row r="906">
@@ -12138,7 +12138,7 @@
         <v>2028</v>
       </c>
       <c r="D906">
-        <v>1731.533484947021</v>
+        <v>2789.111294971774</v>
       </c>
     </row>
     <row r="907">
@@ -12151,7 +12151,7 @@
         <v>2024</v>
       </c>
       <c r="D907">
-        <v>1806.806288361841</v>
+        <v>1814.329901781613</v>
       </c>
     </row>
     <row r="908">
@@ -12164,7 +12164,7 @@
         <v>2025</v>
       </c>
       <c r="D908">
-        <v>1878.89808010262</v>
+        <v>1902.273283930449</v>
       </c>
     </row>
     <row r="909">
@@ -12177,7 +12177,7 @@
         <v>2026</v>
       </c>
       <c r="D909">
-        <v>1944.95364576163</v>
+        <v>1993.00451414605</v>
       </c>
     </row>
     <row r="910">
@@ -12190,7 +12190,7 @@
         <v>2027</v>
       </c>
       <c r="D910">
-        <v>2005.218591915781</v>
+        <v>2087.046528694405</v>
       </c>
     </row>
     <row r="911">
@@ -12203,7 +12203,7 @@
         <v>2028</v>
       </c>
       <c r="D911">
-        <v>2059.99203847562</v>
+        <v>2184.825292974867</v>
       </c>
     </row>
     <row r="912">
@@ -12216,7 +12216,7 @@
         <v>2024</v>
       </c>
       <c r="D912">
-        <v>1498.150577355568</v>
+        <v>1517.421791641794</v>
       </c>
     </row>
     <row r="913">
@@ -12229,7 +12229,7 @@
         <v>2025</v>
       </c>
       <c r="D913">
-        <v>1549.374577598185</v>
+        <v>1606.596990501886</v>
       </c>
     </row>
     <row r="914">
@@ -12242,7 +12242,7 @@
         <v>2026</v>
       </c>
       <c r="D914">
-        <v>1585.087951846063</v>
+        <v>1696.871873470263</v>
       </c>
     </row>
     <row r="915">
@@ -12255,7 +12255,7 @@
         <v>2027</v>
       </c>
       <c r="D915">
-        <v>1608.396785333981</v>
+        <v>1788.66460301438</v>
       </c>
     </row>
     <row r="916">
@@ -12268,7 +12268,7 @@
         <v>2028</v>
       </c>
       <c r="D916">
-        <v>1622.393389786368</v>
+        <v>1882.376204711294</v>
       </c>
     </row>
     <row r="917">
@@ -12411,7 +12411,7 @@
         <v>2024</v>
       </c>
       <c r="D927">
-        <v>1229.238213254048</v>
+        <v>1715.471899247876</v>
       </c>
     </row>
     <row r="928">
@@ -12424,7 +12424,7 @@
         <v>2025</v>
       </c>
       <c r="D928">
-        <v>1229.674445111318</v>
+        <v>2332.086930581588</v>
       </c>
     </row>
     <row r="929">
@@ -12437,7 +12437,7 @@
         <v>2026</v>
       </c>
       <c r="D929">
-        <v>1229.704725281392</v>
+        <v>3182.117351261611</v>
       </c>
     </row>
     <row r="930">
@@ -12450,7 +12450,7 @@
         <v>2027</v>
       </c>
       <c r="D930">
-        <v>1229.70682674836</v>
+        <v>4340.073357396316</v>
       </c>
     </row>
     <row r="931">
@@ -12463,7 +12463,7 @@
         <v>2028</v>
       </c>
       <c r="D931">
-        <v>1229.706972589988</v>
+        <v>5919.71097336293</v>
       </c>
     </row>
     <row r="932">
@@ -13126,7 +13126,7 @@
         <v>2024</v>
       </c>
       <c r="D982">
-        <v>1309.794431009556</v>
+        <v>1317.162412681181</v>
       </c>
     </row>
     <row r="983">
@@ -13139,7 +13139,7 @@
         <v>2025</v>
       </c>
       <c r="D983">
-        <v>1395.5364862068</v>
+        <v>1417.577974895148</v>
       </c>
     </row>
     <row r="984">
@@ -13152,7 +13152,7 @@
         <v>2026</v>
       </c>
       <c r="D984">
-        <v>1481.276196585163</v>
+        <v>1525.858970521967</v>
       </c>
     </row>
     <row r="985">
@@ -13165,7 +13165,7 @@
         <v>2027</v>
       </c>
       <c r="D985">
-        <v>1566.699611361541</v>
+        <v>1642.483730646015</v>
       </c>
     </row>
     <row r="986">
@@ -13178,7 +13178,7 @@
         <v>2028</v>
       </c>
       <c r="D986">
-        <v>1651.514803444124</v>
+        <v>1768.047581822121</v>
       </c>
     </row>
     <row r="987">
@@ -13906,7 +13906,7 @@
         <v>2024</v>
       </c>
       <c r="D1042">
-        <v>1372.924758331353</v>
+        <v>1562.890979512805</v>
       </c>
     </row>
     <row r="1043">
@@ -13919,7 +13919,7 @@
         <v>2025</v>
       </c>
       <c r="D1043">
-        <v>1379.740475537615</v>
+        <v>1796.535800183672</v>
       </c>
     </row>
     <row r="1044">
@@ -13932,7 +13932,7 @@
         <v>2026</v>
       </c>
       <c r="D1044">
-        <v>1381.710391504684</v>
+        <v>2066.428809305717</v>
       </c>
     </row>
     <row r="1045">
@@ -13945,7 +13945,7 @@
         <v>2027</v>
       </c>
       <c r="D1045">
-        <v>1382.27845663943</v>
+        <v>2376.737783348324</v>
       </c>
     </row>
     <row r="1046">
@@ -13958,7 +13958,7 @@
         <v>2028</v>
       </c>
       <c r="D1046">
-        <v>1382.44216260544</v>
+        <v>2733.657658543623</v>
       </c>
     </row>
     <row r="1047">
@@ -13971,7 +13971,7 @@
         <v>2024</v>
       </c>
       <c r="D1047">
-        <v>1547.553690129967</v>
+        <v>1917.362008019356</v>
       </c>
     </row>
     <row r="1048">
@@ -13984,7 +13984,7 @@
         <v>2025</v>
       </c>
       <c r="D1048">
-        <v>1548.743478459931</v>
+        <v>2347.932756726164</v>
       </c>
     </row>
     <row r="1049">
@@ -13997,7 +13997,7 @@
         <v>2026</v>
       </c>
       <c r="D1049">
-        <v>1548.894164018122</v>
+        <v>2880.460092873612</v>
       </c>
     </row>
     <row r="1050">
@@ -14010,7 +14010,7 @@
         <v>2027</v>
       </c>
       <c r="D1050">
-        <v>1548.913240986495</v>
+        <v>3533.102193144961</v>
       </c>
     </row>
     <row r="1051">
@@ -14023,7 +14023,7 @@
         <v>2028</v>
       </c>
       <c r="D1051">
-        <v>1548.915656037462</v>
+        <v>4333.701265249378</v>
       </c>
     </row>
     <row r="1052">
@@ -14036,7 +14036,7 @@
         <v>2024</v>
       </c>
       <c r="D1052">
-        <v>1802.991869082179</v>
+        <v>1810.45044671235</v>
       </c>
     </row>
     <row r="1053">
@@ -14049,7 +14049,7 @@
         <v>2025</v>
       </c>
       <c r="D1053">
-        <v>1875.243815223126</v>
+        <v>1898.43181406109</v>
       </c>
     </row>
     <row r="1054">
@@ -14062,7 +14062,7 @@
         <v>2026</v>
       </c>
       <c r="D1054">
-        <v>1941.521094370854</v>
+        <v>1989.215710463475</v>
       </c>
     </row>
     <row r="1055">
@@ -14075,7 +14075,7 @@
         <v>2027</v>
       </c>
       <c r="D1055">
-        <v>2002.057461228879</v>
+        <v>2083.324497712939</v>
       </c>
     </row>
     <row r="1056">
@@ -14088,7 +14088,7 @@
         <v>2028</v>
       </c>
       <c r="D1056">
-        <v>2057.140848207387</v>
+        <v>2181.184353762357</v>
       </c>
     </row>
     <row r="1057">
@@ -14101,7 +14101,7 @@
         <v>2024</v>
       </c>
       <c r="D1057">
-        <v>1806.806288361841</v>
+        <v>1814.329901781613</v>
       </c>
     </row>
     <row r="1058">
@@ -14114,7 +14114,7 @@
         <v>2025</v>
       </c>
       <c r="D1058">
-        <v>1878.89808010262</v>
+        <v>1902.273283930449</v>
       </c>
     </row>
     <row r="1059">
@@ -14127,7 +14127,7 @@
         <v>2026</v>
       </c>
       <c r="D1059">
-        <v>1944.95364576163</v>
+        <v>1993.00451414605</v>
       </c>
     </row>
     <row r="1060">
@@ -14140,7 +14140,7 @@
         <v>2027</v>
       </c>
       <c r="D1060">
-        <v>2005.218591915781</v>
+        <v>2087.046528694405</v>
       </c>
     </row>
     <row r="1061">
@@ -14153,7 +14153,7 @@
         <v>2028</v>
       </c>
       <c r="D1061">
-        <v>2059.99203847562</v>
+        <v>2184.825292974867</v>
       </c>
     </row>
     <row r="1062">
@@ -14166,7 +14166,7 @@
         <v>2024</v>
       </c>
       <c r="D1062">
-        <v>1806.806288361841</v>
+        <v>1814.329901781613</v>
       </c>
     </row>
     <row r="1063">
@@ -14179,7 +14179,7 @@
         <v>2025</v>
       </c>
       <c r="D1063">
-        <v>1878.89808010262</v>
+        <v>1902.273283930449</v>
       </c>
     </row>
     <row r="1064">
@@ -14192,7 +14192,7 @@
         <v>2026</v>
       </c>
       <c r="D1064">
-        <v>1944.95364576163</v>
+        <v>1993.00451414605</v>
       </c>
     </row>
     <row r="1065">
@@ -14205,7 +14205,7 @@
         <v>2027</v>
       </c>
       <c r="D1065">
-        <v>2005.218591915781</v>
+        <v>2087.046528694405</v>
       </c>
     </row>
     <row r="1066">
@@ -14218,7 +14218,7 @@
         <v>2028</v>
       </c>
       <c r="D1066">
-        <v>2059.99203847562</v>
+        <v>2184.825292974867</v>
       </c>
     </row>
     <row r="1067">
@@ -14296,7 +14296,7 @@
         <v>2024</v>
       </c>
       <c r="D1072">
-        <v>1806.806313878234</v>
+        <v>1814.329901778909</v>
       </c>
     </row>
     <row r="1073">
@@ -14309,7 +14309,7 @@
         <v>2025</v>
       </c>
       <c r="D1073">
-        <v>1878.898153504626</v>
+        <v>1902.273283917962</v>
       </c>
     </row>
     <row r="1074">
@@ -14322,7 +14322,7 @@
         <v>2026</v>
       </c>
       <c r="D1074">
-        <v>1944.95378601298</v>
+        <v>1993.004514114733</v>
       </c>
     </row>
     <row r="1075">
@@ -14335,7 +14335,7 @@
         <v>2027</v>
       </c>
       <c r="D1075">
-        <v>2005.218814535784</v>
+        <v>2087.046528634562</v>
       </c>
     </row>
     <row r="1076">
@@ -14348,7 +14348,7 @@
         <v>2028</v>
       </c>
       <c r="D1076">
-        <v>2059.992355661048</v>
+        <v>2184.825292876801</v>
       </c>
     </row>
     <row r="1077">
@@ -14686,7 +14686,7 @@
         <v>2024</v>
       </c>
       <c r="D1102">
-        <v>1131.564292048428</v>
+        <v>1144.046329095667</v>
       </c>
     </row>
     <row r="1103">
@@ -14699,7 +14699,7 @@
         <v>2025</v>
       </c>
       <c r="D1103">
-        <v>1170.475776710648</v>
+        <v>1206.44579856347</v>
       </c>
     </row>
     <row r="1104">
@@ -14712,7 +14712,7 @@
         <v>2026</v>
       </c>
       <c r="D1104">
-        <v>1203.351146208043</v>
+        <v>1272.765024163082</v>
       </c>
     </row>
     <row r="1105">
@@ -14725,7 +14725,7 @@
         <v>2027</v>
       </c>
       <c r="D1105">
-        <v>1230.972959784135</v>
+        <v>1342.983735257462</v>
       </c>
     </row>
     <row r="1106">
@@ -14738,7 +14738,7 @@
         <v>2028</v>
       </c>
       <c r="D1106">
-        <v>1254.075398787958</v>
+        <v>1417.201255975761</v>
       </c>
     </row>
     <row r="1107">
@@ -14751,7 +14751,7 @@
         <v>2024</v>
       </c>
       <c r="D1107">
-        <v>1131.276358178686</v>
+        <v>1144.868045095115</v>
       </c>
     </row>
     <row r="1108">
@@ -14764,7 +14764,7 @@
         <v>2025</v>
       </c>
       <c r="D1108">
-        <v>1169.106176035959</v>
+        <v>1207.965219212263</v>
       </c>
     </row>
     <row r="1109">
@@ -14777,7 +14777,7 @@
         <v>2026</v>
       </c>
       <c r="D1109">
-        <v>1200.660235161811</v>
+        <v>1275.160662789741</v>
       </c>
     </row>
     <row r="1110">
@@ -14790,7 +14790,7 @@
         <v>2027</v>
       </c>
       <c r="D1110">
-        <v>1226.831110413052</v>
+        <v>1346.389753044363</v>
       </c>
     </row>
     <row r="1111">
@@ -14803,7 +14803,7 @@
         <v>2028</v>
       </c>
       <c r="D1111">
-        <v>1248.437926870973</v>
+        <v>1421.738541223259</v>
       </c>
     </row>
     <row r="1112">
@@ -14816,7 +14816,7 @@
         <v>2024</v>
       </c>
       <c r="D1112">
-        <v>979.3362378402669</v>
+        <v>983.8910710947677</v>
       </c>
     </row>
     <row r="1113">
@@ -14829,7 +14829,7 @@
         <v>2025</v>
       </c>
       <c r="D1113">
-        <v>1036.526312042018</v>
+        <v>1052.199116217547</v>
       </c>
     </row>
     <row r="1114">
@@ -14842,7 +14842,7 @@
         <v>2026</v>
       </c>
       <c r="D1114">
-        <v>1089.226441072675</v>
+        <v>1123.802367228462</v>
       </c>
     </row>
     <row r="1115">
@@ -14855,7 +14855,7 @@
         <v>2027</v>
       </c>
       <c r="D1115">
-        <v>1137.464694892951</v>
+        <v>1199.47376645933</v>
       </c>
     </row>
     <row r="1116">
@@ -14868,7 +14868,7 @@
         <v>2028</v>
       </c>
       <c r="D1116">
-        <v>1181.360941368356</v>
+        <v>1279.793340480358</v>
       </c>
     </row>
     <row r="1117">
@@ -14881,7 +14881,7 @@
         <v>2024</v>
       </c>
       <c r="D1117">
-        <v>1319.658808627316</v>
+        <v>1554.968618981151</v>
       </c>
     </row>
     <row r="1118">
@@ -14894,7 +14894,7 @@
         <v>2025</v>
       </c>
       <c r="D1118">
-        <v>1321.767457202602</v>
+        <v>1836.269027888605</v>
       </c>
     </row>
     <row r="1119">
@@ -14907,7 +14907,7 @@
         <v>2026</v>
       </c>
       <c r="D1119">
-        <v>1322.084958004255</v>
+        <v>2169.93284778616</v>
       </c>
     </row>
     <row r="1120">
@@ -14920,7 +14920,7 @@
         <v>2027</v>
       </c>
       <c r="D1120">
-        <v>1322.132727057986</v>
+        <v>2564.084997011766</v>
       </c>
     </row>
     <row r="1121">
@@ -14933,7 +14933,7 @@
         <v>2028</v>
       </c>
       <c r="D1121">
-        <v>1322.139913227826</v>
+        <v>3029.845401365175</v>
       </c>
     </row>
     <row r="1122">
@@ -14946,7 +14946,7 @@
         <v>2024</v>
       </c>
       <c r="D1122">
-        <v>1354.00766510743</v>
+        <v>1369.919474612975</v>
       </c>
     </row>
     <row r="1123">
@@ -14959,7 +14959,7 @@
         <v>2025</v>
       </c>
       <c r="D1123">
-        <v>1393.313720727085</v>
+        <v>1442.374640650092</v>
       </c>
     </row>
     <row r="1124">
@@ -14972,7 +14972,7 @@
         <v>2026</v>
       </c>
       <c r="D1124">
-        <v>1422.419900534414</v>
+        <v>1518.635516410832</v>
       </c>
     </row>
     <row r="1125">
@@ -14985,7 +14985,7 @@
         <v>2027</v>
       </c>
       <c r="D1125">
-        <v>1443.826318903595</v>
+        <v>1598.930394378692</v>
       </c>
     </row>
     <row r="1126">
@@ -14998,7 +14998,7 @@
         <v>2028</v>
       </c>
       <c r="D1126">
-        <v>1459.49233457964</v>
+        <v>1683.470562075094</v>
       </c>
     </row>
     <row r="1127">
@@ -15011,7 +15011,7 @@
         <v>2024</v>
       </c>
       <c r="D1127">
-        <v>914.0690075130477</v>
+        <v>1064.643706052665</v>
       </c>
     </row>
     <row r="1128">
@@ -15024,7 +15024,7 @@
         <v>2025</v>
       </c>
       <c r="D1128">
-        <v>914.4905565606427</v>
+        <v>1196.878515939718</v>
       </c>
     </row>
     <row r="1129">
@@ -15037,7 +15037,7 @@
         <v>2026</v>
       </c>
       <c r="D1129">
-        <v>914.5332204240725</v>
+        <v>1364.866197102979</v>
       </c>
     </row>
     <row r="1130">
@@ -15050,7 +15050,7 @@
         <v>2027</v>
       </c>
       <c r="D1130">
-        <v>914.5375373356848</v>
+        <v>1548.530404118716</v>
       </c>
     </row>
     <row r="1131">
@@ -15063,7 +15063,7 @@
         <v>2028</v>
       </c>
       <c r="D1131">
-        <v>914.5379741291235</v>
+        <v>1760.10321459814</v>
       </c>
     </row>
     <row r="1132">
@@ -15076,7 +15076,7 @@
         <v>2024</v>
       </c>
       <c r="D1132">
-        <v>1606.917639801334</v>
+        <v>2540.840330400773</v>
       </c>
     </row>
     <row r="1133">
@@ -15089,7 +15089,7 @@
         <v>2025</v>
       </c>
       <c r="D1133">
-        <v>1606.927085302508</v>
+        <v>3610.159963227204</v>
       </c>
     </row>
     <row r="1134">
@@ -15102,7 +15102,7 @@
         <v>2026</v>
       </c>
       <c r="D1134">
-        <v>1606.927215422329</v>
+        <v>5269.608852529263</v>
       </c>
     </row>
     <row r="1135">
@@ -15115,7 +15115,7 @@
         <v>2027</v>
       </c>
       <c r="D1135">
-        <v>1606.927217214835</v>
+        <v>7639.986362698792</v>
       </c>
     </row>
     <row r="1136">
@@ -15128,7 +15128,7 @@
         <v>2028</v>
       </c>
       <c r="D1136">
-        <v>1606.927217239527</v>
+        <v>11095.43249882344</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/forecast_zori_by_tract.xlsx
+++ b/outputs/forecast_zori_by_tract.xlsx
@@ -386,7 +386,7 @@
         <v>2024</v>
       </c>
       <c r="D2">
-        <v>1669.201997988329</v>
+        <v>1669.201997988326</v>
       </c>
     </row>
     <row r="3">
@@ -412,7 +412,7 @@
         <v>2026</v>
       </c>
       <c r="D4">
-        <v>1804.045958805935</v>
+        <v>1951.897533280797</v>
       </c>
     </row>
     <row r="5">
@@ -425,7 +425,7 @@
         <v>2027</v>
       </c>
       <c r="D5">
-        <v>1951.023804986376</v>
+        <v>2111.318773896303</v>
       </c>
     </row>
     <row r="6">
@@ -438,7 +438,7 @@
         <v>2028</v>
       </c>
       <c r="D6">
-        <v>2111.709301589578</v>
+        <v>2285.028251675553</v>
       </c>
     </row>
     <row r="7">
@@ -451,7 +451,7 @@
         <v>2024</v>
       </c>
       <c r="D7">
-        <v>898.2417585204241</v>
+        <v>898.2417585204249</v>
       </c>
     </row>
     <row r="8">
@@ -477,7 +477,7 @@
         <v>2026</v>
       </c>
       <c r="D9">
-        <v>972.932329858666</v>
+        <v>1053.928254093772</v>
       </c>
     </row>
     <row r="10">
@@ -490,7 +490,7 @@
         <v>2027</v>
       </c>
       <c r="D10">
-        <v>1053.90901929606</v>
+        <v>1141.707095116924</v>
       </c>
     </row>
     <row r="11">
@@ -503,7 +503,7 @@
         <v>2028</v>
       </c>
       <c r="D11">
-        <v>1141.711327918655</v>
+        <v>1236.810555073517</v>
       </c>
     </row>
     <row r="12">
@@ -516,7 +516,7 @@
         <v>2024</v>
       </c>
       <c r="D12">
-        <v>1814.329901781613</v>
+        <v>1814.32990178161</v>
       </c>
     </row>
     <row r="13">
@@ -542,7 +542,7 @@
         <v>2026</v>
       </c>
       <c r="D14">
-        <v>1901.804262248687</v>
+        <v>1993.00451414605</v>
       </c>
     </row>
     <row r="15">
@@ -555,7 +555,7 @@
         <v>2027</v>
       </c>
       <c r="D15">
-        <v>1992.680973555916</v>
+        <v>2087.046528694405</v>
       </c>
     </row>
     <row r="16">
@@ -568,7 +568,7 @@
         <v>2028</v>
       </c>
       <c r="D16">
-        <v>2086.823455773566</v>
+        <v>2184.825292974873</v>
       </c>
     </row>
     <row r="17">
@@ -581,7 +581,7 @@
         <v>2024</v>
       </c>
       <c r="D17">
-        <v>1592.952952253476</v>
+        <v>1592.952952253474</v>
       </c>
     </row>
     <row r="18">
@@ -607,7 +607,7 @@
         <v>2026</v>
       </c>
       <c r="D19">
-        <v>1690.037040620934</v>
+        <v>1821.368712397048</v>
       </c>
     </row>
     <row r="20">
@@ -620,7 +620,7 @@
         <v>2027</v>
       </c>
       <c r="D20">
-        <v>1828.06052090495</v>
+        <v>2015.978929207843</v>
       </c>
     </row>
     <row r="21">
@@ -633,7 +633,7 @@
         <v>2028</v>
       </c>
       <c r="D21">
-        <v>1991.111608447058</v>
+        <v>2149.824225822761</v>
       </c>
     </row>
     <row r="22">
@@ -646,7 +646,7 @@
         <v>2024</v>
       </c>
       <c r="D22">
-        <v>1998.840165327557</v>
+        <v>1998.840165327559</v>
       </c>
     </row>
     <row r="23">
@@ -672,7 +672,7 @@
         <v>2026</v>
       </c>
       <c r="D24">
-        <v>2145.603452555335</v>
+        <v>2334.482894863905</v>
       </c>
     </row>
     <row r="25">
@@ -685,7 +685,7 @@
         <v>2027</v>
       </c>
       <c r="D25">
-        <v>2312.762980074878</v>
+        <v>2503.358629706541</v>
       </c>
     </row>
     <row r="26">
@@ -698,7 +698,7 @@
         <v>2028</v>
       </c>
       <c r="D26">
-        <v>2519.594535999485</v>
+        <v>2737.021485562927</v>
       </c>
     </row>
     <row r="27">
@@ -711,7 +711,7 @@
         <v>2024</v>
       </c>
       <c r="D27">
-        <v>1998.84026273542</v>
+        <v>1998.840262735416</v>
       </c>
     </row>
     <row r="28">
@@ -737,7 +737,7 @@
         <v>2026</v>
       </c>
       <c r="D29">
-        <v>2145.603460524413</v>
+        <v>2334.482952021144</v>
       </c>
     </row>
     <row r="30">
@@ -750,7 +750,7 @@
         <v>2027</v>
       </c>
       <c r="D30">
-        <v>2312.762885072513</v>
+        <v>2503.358415312564</v>
       </c>
     </row>
     <row r="31">
@@ -763,7 +763,7 @@
         <v>2028</v>
       </c>
       <c r="D31">
-        <v>2519.594469418731</v>
+        <v>2737.021435976542</v>
       </c>
     </row>
     <row r="32">
@@ -776,7 +776,7 @@
         <v>2024</v>
       </c>
       <c r="D32">
-        <v>1998.84026273542</v>
+        <v>1998.840262735416</v>
       </c>
     </row>
     <row r="33">
@@ -802,7 +802,7 @@
         <v>2026</v>
       </c>
       <c r="D34">
-        <v>2145.603460524413</v>
+        <v>2334.482952021144</v>
       </c>
     </row>
     <row r="35">
@@ -815,7 +815,7 @@
         <v>2027</v>
       </c>
       <c r="D35">
-        <v>2312.762885072513</v>
+        <v>2503.358415312564</v>
       </c>
     </row>
     <row r="36">
@@ -828,7 +828,7 @@
         <v>2028</v>
       </c>
       <c r="D36">
-        <v>2519.594469418731</v>
+        <v>2737.021435976542</v>
       </c>
     </row>
     <row r="37">
@@ -841,7 +841,7 @@
         <v>2024</v>
       </c>
       <c r="D37">
-        <v>1998.84026273542</v>
+        <v>1998.840262735416</v>
       </c>
     </row>
     <row r="38">
@@ -867,7 +867,7 @@
         <v>2026</v>
       </c>
       <c r="D39">
-        <v>2145.603460524413</v>
+        <v>2334.482952021144</v>
       </c>
     </row>
     <row r="40">
@@ -880,7 +880,7 @@
         <v>2027</v>
       </c>
       <c r="D40">
-        <v>2312.762885072513</v>
+        <v>2503.358415312564</v>
       </c>
     </row>
     <row r="41">
@@ -893,7 +893,7 @@
         <v>2028</v>
       </c>
       <c r="D41">
-        <v>2519.594469418731</v>
+        <v>2737.021435976542</v>
       </c>
     </row>
     <row r="42">
@@ -906,7 +906,7 @@
         <v>2024</v>
       </c>
       <c r="D42">
-        <v>1998.84026273542</v>
+        <v>1998.840262735416</v>
       </c>
     </row>
     <row r="43">
@@ -932,7 +932,7 @@
         <v>2026</v>
       </c>
       <c r="D44">
-        <v>2145.603460524413</v>
+        <v>2334.482952021144</v>
       </c>
     </row>
     <row r="45">
@@ -945,7 +945,7 @@
         <v>2027</v>
       </c>
       <c r="D45">
-        <v>2312.762885072513</v>
+        <v>2503.358415312564</v>
       </c>
     </row>
     <row r="46">
@@ -958,7 +958,7 @@
         <v>2028</v>
       </c>
       <c r="D46">
-        <v>2519.594469418731</v>
+        <v>2737.021435976542</v>
       </c>
     </row>
     <row r="47">
@@ -971,7 +971,7 @@
         <v>2024</v>
       </c>
       <c r="D47">
-        <v>1998.84026273542</v>
+        <v>1998.840262735416</v>
       </c>
     </row>
     <row r="48">
@@ -997,7 +997,7 @@
         <v>2026</v>
       </c>
       <c r="D49">
-        <v>2145.603460524413</v>
+        <v>2334.482952021144</v>
       </c>
     </row>
     <row r="50">
@@ -1010,7 +1010,7 @@
         <v>2027</v>
       </c>
       <c r="D50">
-        <v>2312.762885072513</v>
+        <v>2503.358415312564</v>
       </c>
     </row>
     <row r="51">
@@ -1023,7 +1023,7 @@
         <v>2028</v>
       </c>
       <c r="D51">
-        <v>2519.594469418731</v>
+        <v>2737.021435976542</v>
       </c>
     </row>
     <row r="52">
@@ -1036,7 +1036,7 @@
         <v>2024</v>
       </c>
       <c r="D52">
-        <v>1669.201997988329</v>
+        <v>1669.201997988326</v>
       </c>
     </row>
     <row r="53">
@@ -1062,7 +1062,7 @@
         <v>2026</v>
       </c>
       <c r="D54">
-        <v>1804.045958805935</v>
+        <v>1951.897533280797</v>
       </c>
     </row>
     <row r="55">
@@ -1075,7 +1075,7 @@
         <v>2027</v>
       </c>
       <c r="D55">
-        <v>1951.023804986376</v>
+        <v>2111.318773896303</v>
       </c>
     </row>
     <row r="56">
@@ -1088,7 +1088,7 @@
         <v>2028</v>
       </c>
       <c r="D56">
-        <v>2111.709301589578</v>
+        <v>2285.028251675553</v>
       </c>
     </row>
     <row r="57">
@@ -1101,7 +1101,7 @@
         <v>2024</v>
       </c>
       <c r="D57">
-        <v>1669.201997988329</v>
+        <v>1669.201997988326</v>
       </c>
     </row>
     <row r="58">
@@ -1127,7 +1127,7 @@
         <v>2026</v>
       </c>
       <c r="D59">
-        <v>1804.045958805935</v>
+        <v>1951.897533280797</v>
       </c>
     </row>
     <row r="60">
@@ -1140,7 +1140,7 @@
         <v>2027</v>
       </c>
       <c r="D60">
-        <v>1951.023804986376</v>
+        <v>2111.318773896303</v>
       </c>
     </row>
     <row r="61">
@@ -1153,7 +1153,7 @@
         <v>2028</v>
       </c>
       <c r="D61">
-        <v>2111.709301589578</v>
+        <v>2285.028251675553</v>
       </c>
     </row>
     <row r="62">
@@ -1166,7 +1166,7 @@
         <v>2024</v>
       </c>
       <c r="D62">
-        <v>1723.755293397485</v>
+        <v>1723.755293397482</v>
       </c>
     </row>
     <row r="63">
@@ -1192,7 +1192,7 @@
         <v>2026</v>
       </c>
       <c r="D64">
-        <v>1940.228623794669</v>
+        <v>2178.499530308049</v>
       </c>
     </row>
     <row r="65">
@@ -1205,7 +1205,7 @@
         <v>2027</v>
       </c>
       <c r="D65">
-        <v>2175.810332231829</v>
+        <v>2430.972214794591</v>
       </c>
     </row>
     <row r="66">
@@ -1218,7 +1218,7 @@
         <v>2028</v>
       </c>
       <c r="D66">
-        <v>2429.471126339123</v>
+        <v>2707.682637735501</v>
       </c>
     </row>
     <row r="67">
@@ -1231,7 +1231,7 @@
         <v>2024</v>
       </c>
       <c r="D67">
-        <v>2075.805322336766</v>
+        <v>2075.805322336764</v>
       </c>
     </row>
     <row r="68">
@@ -1257,7 +1257,7 @@
         <v>2026</v>
       </c>
       <c r="D69">
-        <v>2627.666906379354</v>
+        <v>3326.264926085004</v>
       </c>
     </row>
     <row r="70">
@@ -1270,7 +1270,7 @@
         <v>2027</v>
       </c>
       <c r="D70">
-        <v>3326.265152131413</v>
+        <v>4210.62228311325</v>
       </c>
     </row>
     <row r="71">
@@ -1283,7 +1283,7 @@
         <v>2028</v>
       </c>
       <c r="D71">
-        <v>4210.622286092579</v>
+        <v>5330.104619643668</v>
       </c>
     </row>
     <row r="72">
@@ -1296,7 +1296,7 @@
         <v>2024</v>
       </c>
       <c r="D72">
-        <v>1580.051228093173</v>
+        <v>1580.051228093175</v>
       </c>
     </row>
     <row r="73">
@@ -1322,7 +1322,7 @@
         <v>2026</v>
       </c>
       <c r="D74">
-        <v>1713.137076498763</v>
+        <v>1855.208140528486</v>
       </c>
     </row>
     <row r="75">
@@ -1335,7 +1335,7 @@
         <v>2027</v>
       </c>
       <c r="D75">
-        <v>1853.499155203014</v>
+        <v>2001.114790426912</v>
       </c>
     </row>
     <row r="76">
@@ -1348,7 +1348,7 @@
         <v>2028</v>
       </c>
       <c r="D76">
-        <v>1999.696907783845</v>
+        <v>2153.911633490219</v>
       </c>
     </row>
     <row r="77">
@@ -1361,7 +1361,7 @@
         <v>2024</v>
       </c>
       <c r="D77">
-        <v>1580.051228093173</v>
+        <v>1580.051228093175</v>
       </c>
     </row>
     <row r="78">
@@ -1387,7 +1387,7 @@
         <v>2026</v>
       </c>
       <c r="D79">
-        <v>1713.137076498763</v>
+        <v>1855.208140528486</v>
       </c>
     </row>
     <row r="80">
@@ -1400,7 +1400,7 @@
         <v>2027</v>
       </c>
       <c r="D80">
-        <v>1853.499155203014</v>
+        <v>2001.114790426912</v>
       </c>
     </row>
     <row r="81">
@@ -1413,7 +1413,7 @@
         <v>2028</v>
       </c>
       <c r="D81">
-        <v>1999.696907783845</v>
+        <v>2153.911633490219</v>
       </c>
     </row>
     <row r="82">
@@ -1426,7 +1426,7 @@
         <v>2024</v>
       </c>
       <c r="D82">
-        <v>1998.840194479362</v>
+        <v>1998.840194479361</v>
       </c>
     </row>
     <row r="83">
@@ -1452,7 +1452,7 @@
         <v>2026</v>
       </c>
       <c r="D84">
-        <v>2145.603470188169</v>
+        <v>2334.482930956876</v>
       </c>
     </row>
     <row r="85">
@@ -1465,7 +1465,7 @@
         <v>2027</v>
       </c>
       <c r="D85">
-        <v>2312.762985040472</v>
+        <v>2503.358620622129</v>
       </c>
     </row>
     <row r="86">
@@ -1478,7 +1478,7 @@
         <v>2028</v>
       </c>
       <c r="D86">
-        <v>2519.594556855159</v>
+        <v>2737.021521144961</v>
       </c>
     </row>
     <row r="87">
@@ -1491,7 +1491,7 @@
         <v>2024</v>
       </c>
       <c r="D87">
-        <v>1669.201997988329</v>
+        <v>1669.201997988326</v>
       </c>
     </row>
     <row r="88">
@@ -1517,7 +1517,7 @@
         <v>2026</v>
       </c>
       <c r="D89">
-        <v>1804.045958805935</v>
+        <v>1951.897533280797</v>
       </c>
     </row>
     <row r="90">
@@ -1530,7 +1530,7 @@
         <v>2027</v>
       </c>
       <c r="D90">
-        <v>1951.023804986376</v>
+        <v>2111.318773896303</v>
       </c>
     </row>
     <row r="91">
@@ -1543,7 +1543,7 @@
         <v>2028</v>
       </c>
       <c r="D91">
-        <v>2111.709301589578</v>
+        <v>2285.028251675553</v>
       </c>
     </row>
     <row r="92">
@@ -1556,7 +1556,7 @@
         <v>2024</v>
       </c>
       <c r="D92">
-        <v>1669.201997988329</v>
+        <v>1669.201997988326</v>
       </c>
     </row>
     <row r="93">
@@ -1582,7 +1582,7 @@
         <v>2026</v>
       </c>
       <c r="D94">
-        <v>1804.045958805935</v>
+        <v>1951.897533280797</v>
       </c>
     </row>
     <row r="95">
@@ -1595,7 +1595,7 @@
         <v>2027</v>
       </c>
       <c r="D95">
-        <v>1951.023804986376</v>
+        <v>2111.318773896303</v>
       </c>
     </row>
     <row r="96">
@@ -1608,7 +1608,7 @@
         <v>2028</v>
       </c>
       <c r="D96">
-        <v>2111.709301589578</v>
+        <v>2285.028251675553</v>
       </c>
     </row>
     <row r="97">
@@ -1621,7 +1621,7 @@
         <v>2024</v>
       </c>
       <c r="D97">
-        <v>1658.266021474097</v>
+        <v>1658.266021474094</v>
       </c>
     </row>
     <row r="98">
@@ -1647,7 +1647,7 @@
         <v>2026</v>
       </c>
       <c r="D99">
-        <v>1799.74943863595</v>
+        <v>1953.298799339549</v>
       </c>
     </row>
     <row r="100">
@@ -1660,7 +1660,7 @@
         <v>2027</v>
       </c>
       <c r="D100">
-        <v>1953.298559647899</v>
+        <v>2119.941863203625</v>
       </c>
     </row>
     <row r="101">
@@ -1673,7 +1673,7 @@
         <v>2028</v>
       </c>
       <c r="D101">
-        <v>2119.941851731608</v>
+        <v>2300.801818914132</v>
       </c>
     </row>
     <row r="102">
@@ -1686,7 +1686,7 @@
         <v>2024</v>
       </c>
       <c r="D102">
-        <v>1580.051228093173</v>
+        <v>1580.051228093175</v>
       </c>
     </row>
     <row r="103">
@@ -1712,7 +1712,7 @@
         <v>2026</v>
       </c>
       <c r="D104">
-        <v>1713.137076498763</v>
+        <v>1855.208140528486</v>
       </c>
     </row>
     <row r="105">
@@ -1725,7 +1725,7 @@
         <v>2027</v>
       </c>
       <c r="D105">
-        <v>1853.499155203014</v>
+        <v>2001.114790426912</v>
       </c>
     </row>
     <row r="106">
@@ -1738,7 +1738,7 @@
         <v>2028</v>
       </c>
       <c r="D106">
-        <v>1999.696907783845</v>
+        <v>2153.911633490219</v>
       </c>
     </row>
     <row r="107">
@@ -1751,7 +1751,7 @@
         <v>2024</v>
       </c>
       <c r="D107">
-        <v>1580.051228093173</v>
+        <v>1580.051228093175</v>
       </c>
     </row>
     <row r="108">
@@ -1777,7 +1777,7 @@
         <v>2026</v>
       </c>
       <c r="D109">
-        <v>1713.137076498763</v>
+        <v>1855.208140528486</v>
       </c>
     </row>
     <row r="110">
@@ -1790,7 +1790,7 @@
         <v>2027</v>
       </c>
       <c r="D110">
-        <v>1853.499155203014</v>
+        <v>2001.114790426912</v>
       </c>
     </row>
     <row r="111">
@@ -1803,7 +1803,7 @@
         <v>2028</v>
       </c>
       <c r="D111">
-        <v>1999.696907783845</v>
+        <v>2153.911633490219</v>
       </c>
     </row>
     <row r="112">
@@ -1816,7 +1816,7 @@
         <v>2024</v>
       </c>
       <c r="D112">
-        <v>435.184254902883</v>
+        <v>435.1842549028822</v>
       </c>
     </row>
     <row r="113">
@@ -1842,7 +1842,7 @@
         <v>2026</v>
       </c>
       <c r="D114">
-        <v>471.8407592037427</v>
+        <v>510.9723647785924</v>
       </c>
     </row>
     <row r="115">
@@ -1855,7 +1855,7 @@
         <v>2027</v>
       </c>
       <c r="D115">
-        <v>510.5017321549581</v>
+        <v>551.1609906852589</v>
       </c>
     </row>
     <row r="116">
@@ -1868,7 +1868,7 @@
         <v>2028</v>
       </c>
       <c r="D116">
-        <v>550.7705036417668</v>
+        <v>593.2478000833707</v>
       </c>
     </row>
     <row r="117">
@@ -1881,7 +1881,7 @@
         <v>2024</v>
       </c>
       <c r="D117">
-        <v>1580.051228093173</v>
+        <v>1580.051228093175</v>
       </c>
     </row>
     <row r="118">
@@ -1907,7 +1907,7 @@
         <v>2026</v>
       </c>
       <c r="D119">
-        <v>1713.137076498763</v>
+        <v>1855.208140528486</v>
       </c>
     </row>
     <row r="120">
@@ -1920,7 +1920,7 @@
         <v>2027</v>
       </c>
       <c r="D120">
-        <v>1853.499155203014</v>
+        <v>2001.114790426912</v>
       </c>
     </row>
     <row r="121">
@@ -1933,7 +1933,7 @@
         <v>2028</v>
       </c>
       <c r="D121">
-        <v>1999.696907783845</v>
+        <v>2153.911633490219</v>
       </c>
     </row>
     <row r="122">
@@ -1946,7 +1946,7 @@
         <v>2024</v>
       </c>
       <c r="D122">
-        <v>1580.051228093173</v>
+        <v>1580.051228093175</v>
       </c>
     </row>
     <row r="123">
@@ -1972,7 +1972,7 @@
         <v>2026</v>
       </c>
       <c r="D124">
-        <v>1713.137076498763</v>
+        <v>1855.208140528486</v>
       </c>
     </row>
     <row r="125">
@@ -1985,7 +1985,7 @@
         <v>2027</v>
       </c>
       <c r="D125">
-        <v>1853.499155203014</v>
+        <v>2001.114790426912</v>
       </c>
     </row>
     <row r="126">
@@ -1998,7 +1998,7 @@
         <v>2028</v>
       </c>
       <c r="D126">
-        <v>1999.696907783845</v>
+        <v>2153.911633490219</v>
       </c>
     </row>
     <row r="127">
@@ -2037,7 +2037,7 @@
         <v>2026</v>
       </c>
       <c r="D129">
-        <v>207.547584368597</v>
+        <v>224.7607930635742</v>
       </c>
     </row>
     <row r="130">
@@ -2050,7 +2050,7 @@
         <v>2027</v>
       </c>
       <c r="D130">
-        <v>224.553794977977</v>
+        <v>242.4391204166636</v>
       </c>
     </row>
     <row r="131">
@@ -2063,7 +2063,7 @@
         <v>2028</v>
       </c>
       <c r="D131">
-        <v>242.2673669677604</v>
+        <v>260.9525243284623</v>
       </c>
     </row>
     <row r="132">
@@ -2076,7 +2076,7 @@
         <v>2024</v>
       </c>
       <c r="D132">
-        <v>1580.051228093173</v>
+        <v>1580.051228093175</v>
       </c>
     </row>
     <row r="133">
@@ -2102,7 +2102,7 @@
         <v>2026</v>
       </c>
       <c r="D134">
-        <v>1713.137076498763</v>
+        <v>1855.208140528486</v>
       </c>
     </row>
     <row r="135">
@@ -2115,7 +2115,7 @@
         <v>2027</v>
       </c>
       <c r="D135">
-        <v>1853.499155203014</v>
+        <v>2001.114790426912</v>
       </c>
     </row>
     <row r="136">
@@ -2128,7 +2128,7 @@
         <v>2028</v>
       </c>
       <c r="D136">
-        <v>1999.696907783845</v>
+        <v>2153.911633490219</v>
       </c>
     </row>
     <row r="137">
@@ -2141,7 +2141,7 @@
         <v>2024</v>
       </c>
       <c r="D137">
-        <v>1427.486392065094</v>
+        <v>1427.486392065089</v>
       </c>
     </row>
     <row r="138">
@@ -2167,7 +2167,7 @@
         <v>2026</v>
       </c>
       <c r="D139">
-        <v>1510.404480062146</v>
+        <v>1598.158772724461</v>
       </c>
     </row>
     <row r="140">
@@ -2180,7 +2180,7 @@
         <v>2027</v>
       </c>
       <c r="D140">
-        <v>1598.165646071762</v>
+        <v>1691.054304392527</v>
       </c>
     </row>
     <row r="141">
@@ -2193,7 +2193,7 @@
         <v>2028</v>
       </c>
       <c r="D141">
-        <v>1691.056834183095</v>
+        <v>1789.357567764276</v>
       </c>
     </row>
     <row r="142">
@@ -2206,7 +2206,7 @@
         <v>2024</v>
       </c>
       <c r="D142">
-        <v>1427.486392065094</v>
+        <v>1427.486392065089</v>
       </c>
     </row>
     <row r="143">
@@ -2232,7 +2232,7 @@
         <v>2026</v>
       </c>
       <c r="D144">
-        <v>1510.404480062146</v>
+        <v>1598.158772724461</v>
       </c>
     </row>
     <row r="145">
@@ -2245,7 +2245,7 @@
         <v>2027</v>
       </c>
       <c r="D145">
-        <v>1598.165646071762</v>
+        <v>1691.054304392527</v>
       </c>
     </row>
     <row r="146">
@@ -2258,7 +2258,7 @@
         <v>2028</v>
       </c>
       <c r="D146">
-        <v>1691.056834183095</v>
+        <v>1789.357567764276</v>
       </c>
     </row>
     <row r="147">
@@ -2271,7 +2271,7 @@
         <v>2024</v>
       </c>
       <c r="D147">
-        <v>1427.486392065094</v>
+        <v>1427.486392065089</v>
       </c>
     </row>
     <row r="148">
@@ -2297,7 +2297,7 @@
         <v>2026</v>
       </c>
       <c r="D149">
-        <v>1510.404480062146</v>
+        <v>1598.158772724461</v>
       </c>
     </row>
     <row r="150">
@@ -2310,7 +2310,7 @@
         <v>2027</v>
       </c>
       <c r="D150">
-        <v>1598.165646071762</v>
+        <v>1691.054304392527</v>
       </c>
     </row>
     <row r="151">
@@ -2323,7 +2323,7 @@
         <v>2028</v>
       </c>
       <c r="D151">
-        <v>1691.056834183095</v>
+        <v>1789.357567764276</v>
       </c>
     </row>
     <row r="152">
@@ -2336,7 +2336,7 @@
         <v>2024</v>
       </c>
       <c r="D152">
-        <v>1427.486392065094</v>
+        <v>1427.486392065089</v>
       </c>
     </row>
     <row r="153">
@@ -2362,7 +2362,7 @@
         <v>2026</v>
       </c>
       <c r="D154">
-        <v>1510.404480062146</v>
+        <v>1598.158772724461</v>
       </c>
     </row>
     <row r="155">
@@ -2375,7 +2375,7 @@
         <v>2027</v>
       </c>
       <c r="D155">
-        <v>1598.165646071762</v>
+        <v>1691.054304392527</v>
       </c>
     </row>
     <row r="156">
@@ -2388,7 +2388,7 @@
         <v>2028</v>
       </c>
       <c r="D156">
-        <v>1691.056834183095</v>
+        <v>1789.357567764276</v>
       </c>
     </row>
     <row r="157">
@@ -2401,7 +2401,7 @@
         <v>2024</v>
       </c>
       <c r="D157">
-        <v>1427.486392065094</v>
+        <v>1427.486392065089</v>
       </c>
     </row>
     <row r="158">
@@ -2427,7 +2427,7 @@
         <v>2026</v>
       </c>
       <c r="D159">
-        <v>1510.404480062146</v>
+        <v>1598.158772724461</v>
       </c>
     </row>
     <row r="160">
@@ -2440,7 +2440,7 @@
         <v>2027</v>
       </c>
       <c r="D160">
-        <v>1598.165646071762</v>
+        <v>1691.054304392527</v>
       </c>
     </row>
     <row r="161">
@@ -2453,7 +2453,7 @@
         <v>2028</v>
       </c>
       <c r="D161">
-        <v>1691.056834183095</v>
+        <v>1789.357567764276</v>
       </c>
     </row>
     <row r="162">
@@ -2466,7 +2466,7 @@
         <v>2024</v>
       </c>
       <c r="D162">
-        <v>1427.486392065094</v>
+        <v>1427.486392065089</v>
       </c>
     </row>
     <row r="163">
@@ -2492,7 +2492,7 @@
         <v>2026</v>
       </c>
       <c r="D164">
-        <v>1510.404480062146</v>
+        <v>1598.158772724461</v>
       </c>
     </row>
     <row r="165">
@@ -2505,7 +2505,7 @@
         <v>2027</v>
       </c>
       <c r="D165">
-        <v>1598.165646071762</v>
+        <v>1691.054304392527</v>
       </c>
     </row>
     <row r="166">
@@ -2518,7 +2518,7 @@
         <v>2028</v>
       </c>
       <c r="D166">
-        <v>1691.056834183095</v>
+        <v>1789.357567764276</v>
       </c>
     </row>
     <row r="167">
@@ -2531,7 +2531,7 @@
         <v>2024</v>
       </c>
       <c r="D167">
-        <v>1427.486392065094</v>
+        <v>1427.486392065089</v>
       </c>
     </row>
     <row r="168">
@@ -2557,7 +2557,7 @@
         <v>2026</v>
       </c>
       <c r="D169">
-        <v>1510.404480062146</v>
+        <v>1598.158772724461</v>
       </c>
     </row>
     <row r="170">
@@ -2570,7 +2570,7 @@
         <v>2027</v>
       </c>
       <c r="D170">
-        <v>1598.165646071762</v>
+        <v>1691.054304392527</v>
       </c>
     </row>
     <row r="171">
@@ -2583,7 +2583,7 @@
         <v>2028</v>
       </c>
       <c r="D171">
-        <v>1691.056834183095</v>
+        <v>1789.357567764276</v>
       </c>
     </row>
     <row r="172">
@@ -2596,7 +2596,7 @@
         <v>2024</v>
       </c>
       <c r="D172">
-        <v>1427.842834671744</v>
+        <v>1427.842834671743</v>
       </c>
     </row>
     <row r="173">
@@ -2622,7 +2622,7 @@
         <v>2026</v>
       </c>
       <c r="D174">
-        <v>1510.974053461054</v>
+        <v>1598.937923463992</v>
       </c>
     </row>
     <row r="175">
@@ -2635,7 +2635,7 @@
         <v>2027</v>
       </c>
       <c r="D175">
-        <v>1598.935284037949</v>
+        <v>1692.006571022032</v>
       </c>
     </row>
     <row r="176">
@@ -2648,7 +2648,7 @@
         <v>2028</v>
       </c>
       <c r="D176">
-        <v>1692.005571680335</v>
+        <v>1790.4892502045</v>
       </c>
     </row>
     <row r="177">
@@ -2687,7 +2687,7 @@
         <v>2026</v>
       </c>
       <c r="D179">
-        <v>139.4360220358365</v>
+        <v>148.885649972629</v>
       </c>
     </row>
     <row r="180">
@@ -2700,7 +2700,7 @@
         <v>2027</v>
       </c>
       <c r="D180">
-        <v>148.7998718849638</v>
+        <v>158.5523281829821</v>
       </c>
     </row>
     <row r="181">
@@ -2713,7 +2713,7 @@
         <v>2028</v>
       </c>
       <c r="D181">
-        <v>158.4961787586064</v>
+        <v>168.6673119144455</v>
       </c>
     </row>
     <row r="182">
@@ -2752,7 +2752,7 @@
         <v>2026</v>
       </c>
       <c r="D184">
-        <v>4.566161902815475</v>
+        <v>4.946292726889488</v>
       </c>
     </row>
     <row r="185">
@@ -2765,7 +2765,7 @@
         <v>2027</v>
       </c>
       <c r="D185">
-        <v>4.946202721523941</v>
+        <v>5.358257073824114</v>
       </c>
     </row>
     <row r="186">
@@ -2778,7 +2778,7 @@
         <v>2028</v>
       </c>
       <c r="D186">
-        <v>5.358276866311702</v>
+        <v>5.80459722369212</v>
       </c>
     </row>
     <row r="187">
@@ -2791,7 +2791,7 @@
         <v>2024</v>
       </c>
       <c r="D187">
-        <v>11.68394067052617</v>
+        <v>11.68394067052616</v>
       </c>
     </row>
     <row r="188">
@@ -2817,7 +2817,7 @@
         <v>2026</v>
       </c>
       <c r="D189">
-        <v>12.6554876914405</v>
+        <v>13.70905049364123</v>
       </c>
     </row>
     <row r="190">
@@ -2830,7 +2830,7 @@
         <v>2027</v>
       </c>
       <c r="D190">
-        <v>13.70880089571329</v>
+        <v>14.85084250148937</v>
       </c>
     </row>
     <row r="191">
@@ -2843,7 +2843,7 @@
         <v>2028</v>
       </c>
       <c r="D191">
-        <v>14.85089739634021</v>
+        <v>16.08790986799083</v>
       </c>
     </row>
     <row r="192">
@@ -2882,7 +2882,7 @@
         <v>2026</v>
       </c>
       <c r="D194">
-        <v>0.3039344630836961</v>
+        <v>0.3278176765955487</v>
       </c>
     </row>
     <row r="195">
@@ -2895,7 +2895,7 @@
         <v>2027</v>
       </c>
       <c r="D195">
-        <v>0.3276981240279641</v>
+        <v>0.3529891126625025</v>
       </c>
     </row>
     <row r="196">
@@ -2908,7 +2908,7 @@
         <v>2028</v>
       </c>
       <c r="D196">
-        <v>0.3529069573972605</v>
+        <v>0.3798280051756933</v>
       </c>
     </row>
     <row r="197">
@@ -2921,7 +2921,7 @@
         <v>2024</v>
       </c>
       <c r="D197">
-        <v>148.9729882215053</v>
+        <v>148.9729882215052</v>
       </c>
     </row>
     <row r="198">
@@ -2947,7 +2947,7 @@
         <v>2026</v>
       </c>
       <c r="D199">
-        <v>165.7949949880863</v>
+        <v>184.2646399648482</v>
       </c>
     </row>
     <row r="200">
@@ -2960,7 +2960,7 @@
         <v>2027</v>
       </c>
       <c r="D200">
-        <v>184.0480141143568</v>
+        <v>203.791792230403</v>
       </c>
     </row>
     <row r="201">
@@ -2973,7 +2973,7 @@
         <v>2028</v>
       </c>
       <c r="D201">
-        <v>203.5854803067662</v>
+        <v>224.7044696643248</v>
       </c>
     </row>
     <row r="202">
@@ -2986,7 +2986,7 @@
         <v>2024</v>
       </c>
       <c r="D202">
-        <v>1427.486392065094</v>
+        <v>1427.486392065089</v>
       </c>
     </row>
     <row r="203">
@@ -3012,7 +3012,7 @@
         <v>2026</v>
       </c>
       <c r="D204">
-        <v>1510.404480062146</v>
+        <v>1598.158772724461</v>
       </c>
     </row>
     <row r="205">
@@ -3025,7 +3025,7 @@
         <v>2027</v>
       </c>
       <c r="D205">
-        <v>1598.165646071762</v>
+        <v>1691.054304392527</v>
       </c>
     </row>
     <row r="206">
@@ -3038,7 +3038,7 @@
         <v>2028</v>
       </c>
       <c r="D206">
-        <v>1691.056834183095</v>
+        <v>1789.357567764276</v>
       </c>
     </row>
     <row r="207">
@@ -3051,7 +3051,7 @@
         <v>2024</v>
       </c>
       <c r="D207">
-        <v>1427.486392065094</v>
+        <v>1427.486392065089</v>
       </c>
     </row>
     <row r="208">
@@ -3077,7 +3077,7 @@
         <v>2026</v>
       </c>
       <c r="D209">
-        <v>1510.404480062146</v>
+        <v>1598.158772724461</v>
       </c>
     </row>
     <row r="210">
@@ -3090,7 +3090,7 @@
         <v>2027</v>
       </c>
       <c r="D210">
-        <v>1598.165646071762</v>
+        <v>1691.054304392527</v>
       </c>
     </row>
     <row r="211">
@@ -3103,7 +3103,7 @@
         <v>2028</v>
       </c>
       <c r="D211">
-        <v>1691.056834183095</v>
+        <v>1789.357567764276</v>
       </c>
     </row>
     <row r="212">
@@ -3116,7 +3116,7 @@
         <v>2024</v>
       </c>
       <c r="D212">
-        <v>1494.538653121168</v>
+        <v>1494.538653121164</v>
       </c>
     </row>
     <row r="213">
@@ -3142,7 +3142,7 @@
         <v>2026</v>
       </c>
       <c r="D214">
-        <v>1712.154150178372</v>
+        <v>1962.131022471861</v>
       </c>
     </row>
     <row r="215">
@@ -3155,7 +3155,7 @@
         <v>2027</v>
       </c>
       <c r="D215">
-        <v>1962.215049689628</v>
+        <v>2249.66768460943</v>
       </c>
     </row>
     <row r="216">
@@ -3168,7 +3168,7 @@
         <v>2028</v>
       </c>
       <c r="D216">
-        <v>2249.679674934548</v>
+        <v>2579.382088344038</v>
       </c>
     </row>
     <row r="217">
@@ -3181,7 +3181,7 @@
         <v>2024</v>
       </c>
       <c r="D217">
-        <v>1672.213199336093</v>
+        <v>1672.21319933609</v>
       </c>
     </row>
     <row r="218">
@@ -3207,7 +3207,7 @@
         <v>2026</v>
       </c>
       <c r="D219">
-        <v>2123.963030272409</v>
+        <v>2702.662664317318</v>
       </c>
     </row>
     <row r="220">
@@ -3220,7 +3220,7 @@
         <v>2027</v>
       </c>
       <c r="D220">
-        <v>2703.60081787093</v>
+        <v>3448.883266624006</v>
       </c>
     </row>
     <row r="221">
@@ -3233,7 +3233,7 @@
         <v>2028</v>
       </c>
       <c r="D221">
-        <v>3449.111770111444</v>
+        <v>4402.014482266812</v>
       </c>
     </row>
     <row r="222">
@@ -3246,7 +3246,7 @@
         <v>2024</v>
       </c>
       <c r="D222">
-        <v>1515.84598566845</v>
+        <v>1515.845985668446</v>
       </c>
     </row>
     <row r="223">
@@ -3272,7 +3272,7 @@
         <v>2026</v>
       </c>
       <c r="D224">
-        <v>1856.179291523884</v>
+        <v>2274.877462643891</v>
       </c>
     </row>
     <row r="225">
@@ -3285,7 +3285,7 @@
         <v>2027</v>
       </c>
       <c r="D225">
-        <v>2275.165273432647</v>
+        <v>2791.4776786962</v>
       </c>
     </row>
     <row r="226">
@@ -3298,7 +3298,7 @@
         <v>2028</v>
       </c>
       <c r="D226">
-        <v>2791.52966366007</v>
+        <v>3425.583624319016</v>
       </c>
     </row>
     <row r="227">
@@ -3311,7 +3311,7 @@
         <v>2024</v>
       </c>
       <c r="D227">
-        <v>1217.630894094818</v>
+        <v>1217.630894094817</v>
       </c>
     </row>
     <row r="228">
@@ -3337,7 +3337,7 @@
         <v>2026</v>
       </c>
       <c r="D229">
-        <v>1313.803119948016</v>
+        <v>1416.855425842011</v>
       </c>
     </row>
     <row r="230">
@@ -3350,7 +3350,7 @@
         <v>2027</v>
       </c>
       <c r="D230">
-        <v>1416.397998536504</v>
+        <v>1525.740607820793</v>
       </c>
     </row>
     <row r="231">
@@ -3363,7 +3363,7 @@
         <v>2028</v>
       </c>
       <c r="D231">
-        <v>1525.425721678513</v>
+        <v>1641.976558538316</v>
       </c>
     </row>
     <row r="232">
@@ -3402,7 +3402,7 @@
         <v>2026</v>
       </c>
       <c r="D234">
-        <v>1312.548022096241</v>
+        <v>1415.515336131529</v>
       </c>
     </row>
     <row r="235">
@@ -3415,7 +3415,7 @@
         <v>2027</v>
       </c>
       <c r="D235">
-        <v>1415.054058230069</v>
+        <v>1524.290907434324</v>
       </c>
     </row>
     <row r="236">
@@ -3428,7 +3428,7 @@
         <v>2028</v>
       </c>
       <c r="D236">
-        <v>1523.973394305454</v>
+        <v>1640.399836380142</v>
       </c>
     </row>
     <row r="237">
@@ -3441,7 +3441,7 @@
         <v>2024</v>
       </c>
       <c r="D237">
-        <v>1489.165773263901</v>
+        <v>1489.165773263898</v>
       </c>
     </row>
     <row r="238">
@@ -3467,7 +3467,7 @@
         <v>2026</v>
       </c>
       <c r="D239">
-        <v>1607.937886216509</v>
+        <v>1736.56346334983</v>
       </c>
     </row>
     <row r="240">
@@ -3480,7 +3480,7 @@
         <v>2027</v>
       </c>
       <c r="D240">
-        <v>1736.689414623867</v>
+        <v>1876.297556606977</v>
       </c>
     </row>
     <row r="241">
@@ -3493,7 +3493,7 @@
         <v>2028</v>
       </c>
       <c r="D241">
-        <v>1876.342595556797</v>
+        <v>2027.421468166711</v>
       </c>
     </row>
     <row r="242">
@@ -3506,7 +3506,7 @@
         <v>2024</v>
       </c>
       <c r="D242">
-        <v>1489.165773263901</v>
+        <v>1489.165773263898</v>
       </c>
     </row>
     <row r="243">
@@ -3532,7 +3532,7 @@
         <v>2026</v>
       </c>
       <c r="D244">
-        <v>1607.937886216509</v>
+        <v>1736.56346334983</v>
       </c>
     </row>
     <row r="245">
@@ -3545,7 +3545,7 @@
         <v>2027</v>
       </c>
       <c r="D245">
-        <v>1736.689414623867</v>
+        <v>1876.297556606977</v>
       </c>
     </row>
     <row r="246">
@@ -3558,7 +3558,7 @@
         <v>2028</v>
       </c>
       <c r="D246">
-        <v>1876.342595556797</v>
+        <v>2027.421468166711</v>
       </c>
     </row>
     <row r="247">
@@ -3571,7 +3571,7 @@
         <v>2024</v>
       </c>
       <c r="D247">
-        <v>1489.165773263901</v>
+        <v>1489.165773263898</v>
       </c>
     </row>
     <row r="248">
@@ -3597,7 +3597,7 @@
         <v>2026</v>
       </c>
       <c r="D249">
-        <v>1607.937886216509</v>
+        <v>1736.56346334983</v>
       </c>
     </row>
     <row r="250">
@@ -3610,7 +3610,7 @@
         <v>2027</v>
       </c>
       <c r="D250">
-        <v>1736.689414623867</v>
+        <v>1876.297556606977</v>
       </c>
     </row>
     <row r="251">
@@ -3623,7 +3623,7 @@
         <v>2028</v>
       </c>
       <c r="D251">
-        <v>1876.342595556797</v>
+        <v>2027.421468166711</v>
       </c>
     </row>
     <row r="252">
@@ -3636,7 +3636,7 @@
         <v>2024</v>
       </c>
       <c r="D252">
-        <v>1489.165773263901</v>
+        <v>1489.165773263898</v>
       </c>
     </row>
     <row r="253">
@@ -3662,7 +3662,7 @@
         <v>2026</v>
       </c>
       <c r="D254">
-        <v>1607.937886216509</v>
+        <v>1736.56346334983</v>
       </c>
     </row>
     <row r="255">
@@ -3675,7 +3675,7 @@
         <v>2027</v>
       </c>
       <c r="D255">
-        <v>1736.689414623867</v>
+        <v>1876.297556606977</v>
       </c>
     </row>
     <row r="256">
@@ -3688,7 +3688,7 @@
         <v>2028</v>
       </c>
       <c r="D256">
-        <v>1876.342595556797</v>
+        <v>2027.421468166711</v>
       </c>
     </row>
     <row r="257">
@@ -3701,7 +3701,7 @@
         <v>2024</v>
       </c>
       <c r="D257">
-        <v>1489.165773263901</v>
+        <v>1489.165773263898</v>
       </c>
     </row>
     <row r="258">
@@ -3727,7 +3727,7 @@
         <v>2026</v>
       </c>
       <c r="D259">
-        <v>1607.937886216509</v>
+        <v>1736.56346334983</v>
       </c>
     </row>
     <row r="260">
@@ -3740,7 +3740,7 @@
         <v>2027</v>
       </c>
       <c r="D260">
-        <v>1736.689414623867</v>
+        <v>1876.297556606977</v>
       </c>
     </row>
     <row r="261">
@@ -3753,7 +3753,7 @@
         <v>2028</v>
       </c>
       <c r="D261">
-        <v>1876.342595556797</v>
+        <v>2027.421468166711</v>
       </c>
     </row>
     <row r="262">
@@ -3766,7 +3766,7 @@
         <v>2024</v>
       </c>
       <c r="D262">
-        <v>1476.83484069519</v>
+        <v>1476.834840695186</v>
       </c>
     </row>
     <row r="263">
@@ -3792,7 +3792,7 @@
         <v>2026</v>
       </c>
       <c r="D264">
-        <v>1603.488021057656</v>
+        <v>1742.126787596825</v>
       </c>
     </row>
     <row r="265">
@@ -3805,7 +3805,7 @@
         <v>2027</v>
       </c>
       <c r="D265">
-        <v>1741.769736644425</v>
+        <v>1892.809866222139</v>
       </c>
     </row>
     <row r="266">
@@ -3818,7 +3818,7 @@
         <v>2028</v>
       </c>
       <c r="D266">
-        <v>1892.933106358956</v>
+        <v>2056.927814431382</v>
       </c>
     </row>
     <row r="267">
@@ -3831,7 +3831,7 @@
         <v>2024</v>
       </c>
       <c r="D267">
-        <v>1485.832580345213</v>
+        <v>1485.832580345211</v>
       </c>
     </row>
     <row r="268">
@@ -3857,7 +3857,7 @@
         <v>2026</v>
       </c>
       <c r="D269">
-        <v>1603.978593724889</v>
+        <v>1731.90697429318</v>
       </c>
     </row>
     <row r="270">
@@ -3870,7 +3870,7 @@
         <v>2027</v>
       </c>
       <c r="D270">
-        <v>1732.037930634004</v>
+        <v>1870.881880087317</v>
       </c>
     </row>
     <row r="271">
@@ -3883,7 +3883,7 @@
         <v>2028</v>
       </c>
       <c r="D271">
-        <v>1870.929620372057</v>
+        <v>2021.163386564761</v>
       </c>
     </row>
     <row r="272">
@@ -3896,7 +3896,7 @@
         <v>2024</v>
       </c>
       <c r="D272">
-        <v>1144.100961778938</v>
+        <v>1144.100961778937</v>
       </c>
     </row>
     <row r="273">
@@ -3922,7 +3922,7 @@
         <v>2026</v>
       </c>
       <c r="D274">
-        <v>1210.145399971484</v>
+        <v>1280.296023218029</v>
       </c>
     </row>
     <row r="275">
@@ -3935,7 +3935,7 @@
         <v>2027</v>
       </c>
       <c r="D275">
-        <v>1280.424030410166</v>
+        <v>1355.230404222168</v>
       </c>
     </row>
     <row r="276">
@@ -3948,7 +3948,7 @@
         <v>2028</v>
       </c>
       <c r="D276">
-        <v>1355.289449307838</v>
+        <v>1434.738126778079</v>
       </c>
     </row>
     <row r="277">
@@ -3961,7 +3961,7 @@
         <v>2024</v>
       </c>
       <c r="D277">
-        <v>1559.886312970241</v>
+        <v>1559.886312970236</v>
       </c>
     </row>
     <row r="278">
@@ -3987,7 +3987,7 @@
         <v>2026</v>
       </c>
       <c r="D279">
-        <v>1646.928896171735</v>
+        <v>1738.009603218948</v>
       </c>
     </row>
     <row r="280">
@@ -4000,7 +4000,7 @@
         <v>2027</v>
       </c>
       <c r="D280">
-        <v>1737.566944226906</v>
+        <v>1831.863192685846</v>
       </c>
     </row>
     <row r="281">
@@ -4013,7 +4013,7 @@
         <v>2028</v>
       </c>
       <c r="D281">
-        <v>1831.610885598293</v>
+        <v>1929.987248212923</v>
       </c>
     </row>
     <row r="282">
@@ -4026,7 +4026,7 @@
         <v>2024</v>
       </c>
       <c r="D282">
-        <v>1559.88631295132</v>
+        <v>1559.886312951319</v>
       </c>
     </row>
     <row r="283">
@@ -4052,7 +4052,7 @@
         <v>2026</v>
       </c>
       <c r="D284">
-        <v>1646.928896118996</v>
+        <v>1738.009603126662</v>
       </c>
     </row>
     <row r="285">
@@ -4065,7 +4065,7 @@
         <v>2027</v>
       </c>
       <c r="D285">
-        <v>1737.566944133524</v>
+        <v>1831.863192544255</v>
       </c>
     </row>
     <row r="286">
@@ -4078,7 +4078,7 @@
         <v>2028</v>
       </c>
       <c r="D286">
-        <v>1831.610885456081</v>
+        <v>1929.987248015037</v>
       </c>
     </row>
     <row r="287">
@@ -4091,7 +4091,7 @@
         <v>2024</v>
       </c>
       <c r="D287">
-        <v>1559.88631295132</v>
+        <v>1559.886312951319</v>
       </c>
     </row>
     <row r="288">
@@ -4117,7 +4117,7 @@
         <v>2026</v>
       </c>
       <c r="D289">
-        <v>1646.928896118996</v>
+        <v>1738.009603126662</v>
       </c>
     </row>
     <row r="290">
@@ -4130,7 +4130,7 @@
         <v>2027</v>
       </c>
       <c r="D290">
-        <v>1737.566944133524</v>
+        <v>1831.863192544255</v>
       </c>
     </row>
     <row r="291">
@@ -4143,7 +4143,7 @@
         <v>2028</v>
       </c>
       <c r="D291">
-        <v>1831.610885456081</v>
+        <v>1929.987248015037</v>
       </c>
     </row>
     <row r="292">
@@ -4156,7 +4156,7 @@
         <v>2024</v>
       </c>
       <c r="D292">
-        <v>1559.88631295132</v>
+        <v>1559.886312951319</v>
       </c>
     </row>
     <row r="293">
@@ -4182,7 +4182,7 @@
         <v>2026</v>
       </c>
       <c r="D294">
-        <v>1646.928896118996</v>
+        <v>1738.009603126662</v>
       </c>
     </row>
     <row r="295">
@@ -4195,7 +4195,7 @@
         <v>2027</v>
       </c>
       <c r="D295">
-        <v>1737.566944133524</v>
+        <v>1831.863192544255</v>
       </c>
     </row>
     <row r="296">
@@ -4208,7 +4208,7 @@
         <v>2028</v>
       </c>
       <c r="D296">
-        <v>1831.610885456081</v>
+        <v>1929.987248015037</v>
       </c>
     </row>
     <row r="297">
@@ -4221,7 +4221,7 @@
         <v>2024</v>
       </c>
       <c r="D297">
-        <v>1144.046329105066</v>
+        <v>1144.046329105065</v>
       </c>
     </row>
     <row r="298">
@@ -4247,7 +4247,7 @@
         <v>2026</v>
       </c>
       <c r="D299">
-        <v>1206.608980095068</v>
+        <v>1272.76502420194</v>
       </c>
     </row>
     <row r="300">
@@ -4260,7 +4260,7 @@
         <v>2027</v>
       </c>
       <c r="D300">
-        <v>1272.845232488974</v>
+        <v>1342.983735313944</v>
       </c>
     </row>
     <row r="301">
@@ -4273,7 +4273,7 @@
         <v>2028</v>
       </c>
       <c r="D301">
-        <v>1343.023168150598</v>
+        <v>1417.201256051555</v>
       </c>
     </row>
     <row r="302">
@@ -4286,7 +4286,7 @@
         <v>2024</v>
       </c>
       <c r="D302">
-        <v>1144.046329095645</v>
+        <v>1144.046329095643</v>
       </c>
     </row>
     <row r="303">
@@ -4312,7 +4312,7 @@
         <v>2026</v>
       </c>
       <c r="D304">
-        <v>1206.608980071777</v>
+        <v>1272.765024163008</v>
       </c>
     </row>
     <row r="305">
@@ -4325,7 +4325,7 @@
         <v>2027</v>
       </c>
       <c r="D305">
-        <v>1272.845232450024</v>
+        <v>1342.983735257364</v>
       </c>
     </row>
     <row r="306">
@@ -4338,7 +4338,7 @@
         <v>2028</v>
       </c>
       <c r="D306">
-        <v>1343.023168094065</v>
+        <v>1417.201255975641</v>
       </c>
     </row>
     <row r="307">
@@ -4351,7 +4351,7 @@
         <v>2024</v>
       </c>
       <c r="D307">
-        <v>1144.046329105066</v>
+        <v>1144.046329105065</v>
       </c>
     </row>
     <row r="308">
@@ -4377,7 +4377,7 @@
         <v>2026</v>
       </c>
       <c r="D309">
-        <v>1206.608980095068</v>
+        <v>1272.76502420194</v>
       </c>
     </row>
     <row r="310">
@@ -4390,7 +4390,7 @@
         <v>2027</v>
       </c>
       <c r="D310">
-        <v>1272.845232488974</v>
+        <v>1342.983735313944</v>
       </c>
     </row>
     <row r="311">
@@ -4403,7 +4403,7 @@
         <v>2028</v>
       </c>
       <c r="D311">
-        <v>1343.023168150598</v>
+        <v>1417.201256051555</v>
       </c>
     </row>
     <row r="312">
@@ -4416,7 +4416,7 @@
         <v>2024</v>
       </c>
       <c r="D312">
-        <v>1495.645656251703</v>
+        <v>1495.645656251699</v>
       </c>
     </row>
     <row r="313">
@@ -4442,7 +4442,7 @@
         <v>2026</v>
       </c>
       <c r="D314">
-        <v>1578.711756075565</v>
+        <v>1665.729464453318</v>
       </c>
     </row>
     <row r="315">
@@ -4455,7 +4455,7 @@
         <v>2027</v>
       </c>
       <c r="D315">
-        <v>1665.374433692358</v>
+        <v>1755.722459114588</v>
       </c>
     </row>
     <row r="316">
@@ -4468,7 +4468,7 @@
         <v>2028</v>
       </c>
       <c r="D316">
-        <v>1755.521627795475</v>
+        <v>1849.942459457764</v>
       </c>
     </row>
     <row r="317">
@@ -4481,7 +4481,7 @@
         <v>2024</v>
       </c>
       <c r="D317">
-        <v>1559.88631295132</v>
+        <v>1559.886312951319</v>
       </c>
     </row>
     <row r="318">
@@ -4507,7 +4507,7 @@
         <v>2026</v>
       </c>
       <c r="D319">
-        <v>1646.928896118996</v>
+        <v>1738.009603126662</v>
       </c>
     </row>
     <row r="320">
@@ -4520,7 +4520,7 @@
         <v>2027</v>
       </c>
       <c r="D320">
-        <v>1737.566944133524</v>
+        <v>1831.863192544255</v>
       </c>
     </row>
     <row r="321">
@@ -4533,7 +4533,7 @@
         <v>2028</v>
       </c>
       <c r="D321">
-        <v>1831.610885456081</v>
+        <v>1929.987248015037</v>
       </c>
     </row>
     <row r="322">
@@ -4546,7 +4546,7 @@
         <v>2024</v>
       </c>
       <c r="D322">
-        <v>1556.66301802536</v>
+        <v>1556.663018025357</v>
       </c>
     </row>
     <row r="323">
@@ -4572,7 +4572,7 @@
         <v>2026</v>
       </c>
       <c r="D324">
-        <v>1643.505450175641</v>
+        <v>1734.381529573017</v>
       </c>
     </row>
     <row r="325">
@@ -4585,7 +4585,7 @@
         <v>2027</v>
       </c>
       <c r="D325">
-        <v>1733.943224343726</v>
+        <v>1828.040364208928</v>
       </c>
     </row>
     <row r="326">
@@ -4598,7 +4598,7 @@
         <v>2028</v>
       </c>
       <c r="D326">
-        <v>1827.790610308505</v>
+        <v>1925.96728154081</v>
       </c>
     </row>
     <row r="327">
@@ -4637,7 +4637,7 @@
         <v>2026</v>
       </c>
       <c r="D329">
-        <v>1206.608980071376</v>
+        <v>1272.765024162345</v>
       </c>
     </row>
     <row r="330">
@@ -4650,7 +4650,7 @@
         <v>2027</v>
       </c>
       <c r="D330">
-        <v>1272.845232449361</v>
+        <v>1342.983735256412</v>
       </c>
     </row>
     <row r="331">
@@ -4663,7 +4663,7 @@
         <v>2028</v>
       </c>
       <c r="D331">
-        <v>1343.023168093115</v>
+        <v>1417.201255974379</v>
       </c>
     </row>
     <row r="332">
@@ -4676,7 +4676,7 @@
         <v>2024</v>
       </c>
       <c r="D332">
-        <v>1144.046329105066</v>
+        <v>1144.046329105065</v>
       </c>
     </row>
     <row r="333">
@@ -4702,7 +4702,7 @@
         <v>2026</v>
       </c>
       <c r="D334">
-        <v>1206.608980095068</v>
+        <v>1272.76502420194</v>
       </c>
     </row>
     <row r="335">
@@ -4715,7 +4715,7 @@
         <v>2027</v>
       </c>
       <c r="D335">
-        <v>1272.845232488974</v>
+        <v>1342.983735313944</v>
       </c>
     </row>
     <row r="336">
@@ -4728,7 +4728,7 @@
         <v>2028</v>
       </c>
       <c r="D336">
-        <v>1343.023168150598</v>
+        <v>1417.201256051555</v>
       </c>
     </row>
     <row r="337">
@@ -4741,7 +4741,7 @@
         <v>2024</v>
       </c>
       <c r="D337">
-        <v>1144.046329105066</v>
+        <v>1144.046329105065</v>
       </c>
     </row>
     <row r="338">
@@ -4767,7 +4767,7 @@
         <v>2026</v>
       </c>
       <c r="D339">
-        <v>1206.608980095068</v>
+        <v>1272.76502420194</v>
       </c>
     </row>
     <row r="340">
@@ -4780,7 +4780,7 @@
         <v>2027</v>
       </c>
       <c r="D340">
-        <v>1272.845232488974</v>
+        <v>1342.983735313944</v>
       </c>
     </row>
     <row r="341">
@@ -4793,7 +4793,7 @@
         <v>2028</v>
       </c>
       <c r="D341">
-        <v>1343.023168150598</v>
+        <v>1417.201256051555</v>
       </c>
     </row>
     <row r="342">
@@ -4832,7 +4832,7 @@
         <v>2026</v>
       </c>
       <c r="D344">
-        <v>1209.978624471403</v>
+        <v>1279.946069209597</v>
       </c>
     </row>
     <row r="345">
@@ -4845,7 +4845,7 @@
         <v>2027</v>
       </c>
       <c r="D345">
-        <v>1280.072432206109</v>
+        <v>1354.666236787851</v>
       </c>
     </row>
     <row r="346">
@@ -4858,7 +4858,7 @@
         <v>2028</v>
       </c>
       <c r="D346">
-        <v>1354.724719597217</v>
+        <v>1433.934086417451</v>
       </c>
     </row>
     <row r="347">
@@ -4871,7 +4871,7 @@
         <v>2024</v>
       </c>
       <c r="D347">
-        <v>1644.628739861137</v>
+        <v>1644.628739861135</v>
       </c>
     </row>
     <row r="348">
@@ -4897,7 +4897,7 @@
         <v>2026</v>
       </c>
       <c r="D349">
-        <v>1765.384254794709</v>
+        <v>1920.792684883751</v>
       </c>
     </row>
     <row r="350">
@@ -4910,7 +4910,7 @@
         <v>2027</v>
       </c>
       <c r="D350">
-        <v>1902.921612026129</v>
+        <v>2059.741998176912</v>
       </c>
     </row>
     <row r="351">
@@ -4923,7 +4923,7 @@
         <v>2028</v>
       </c>
       <c r="D351">
-        <v>2073.10087245</v>
+        <v>2251.997923702262</v>
       </c>
     </row>
     <row r="352">
@@ -4936,7 +4936,7 @@
         <v>2024</v>
       </c>
       <c r="D352">
-        <v>1355.368613385806</v>
+        <v>1355.368613385803</v>
       </c>
     </row>
     <row r="353">
@@ -4962,7 +4962,7 @@
         <v>2026</v>
       </c>
       <c r="D354">
-        <v>1476.794348448303</v>
+        <v>1609.158027256417</v>
       </c>
     </row>
     <row r="355">
@@ -4975,7 +4975,7 @@
         <v>2027</v>
       </c>
       <c r="D355">
-        <v>1609.154585308447</v>
+        <v>1753.438994862773</v>
       </c>
     </row>
     <row r="356">
@@ -4988,7 +4988,7 @@
         <v>2028</v>
       </c>
       <c r="D356">
-        <v>1753.439211573756</v>
+        <v>1910.657248446899</v>
       </c>
     </row>
     <row r="357">
@@ -5001,7 +5001,7 @@
         <v>2024</v>
       </c>
       <c r="D357">
-        <v>1974.149955503941</v>
+        <v>1974.149955503938</v>
       </c>
     </row>
     <row r="358">
@@ -5027,7 +5027,7 @@
         <v>2026</v>
       </c>
       <c r="D359">
-        <v>2119.95814146771</v>
+        <v>2306.118247478619</v>
       </c>
     </row>
     <row r="360">
@@ -5040,7 +5040,7 @@
         <v>2027</v>
       </c>
       <c r="D360">
-        <v>2285.911174457421</v>
+        <v>2475.006436520565</v>
       </c>
     </row>
     <row r="361">
@@ -5053,7 +5053,7 @@
         <v>2028</v>
       </c>
       <c r="D361">
-        <v>2489.899561287548</v>
+        <v>2704.503707388008</v>
       </c>
     </row>
     <row r="362">
@@ -5092,7 +5092,7 @@
         <v>2026</v>
       </c>
       <c r="D364">
-        <v>2140.948470482953</v>
+        <v>2329.333209661329</v>
       </c>
     </row>
     <row r="365">
@@ -5105,7 +5105,7 @@
         <v>2027</v>
       </c>
       <c r="D365">
-        <v>2307.889363435612</v>
+        <v>2498.214192365253</v>
       </c>
     </row>
     <row r="366">
@@ -5118,7 +5118,7 @@
         <v>2028</v>
       </c>
       <c r="D366">
-        <v>2514.203982354255</v>
+        <v>2731.116588208785</v>
       </c>
     </row>
     <row r="367">
@@ -5131,7 +5131,7 @@
         <v>2024</v>
       </c>
       <c r="D367">
-        <v>999.9962648106847</v>
+        <v>999.9962648106838</v>
       </c>
     </row>
     <row r="368">
@@ -5157,7 +5157,7 @@
         <v>2026</v>
       </c>
       <c r="D369">
-        <v>1085.99679475946</v>
+        <v>1179.512851315484</v>
       </c>
     </row>
     <row r="370">
@@ -5170,7 +5170,7 @@
         <v>2027</v>
       </c>
       <c r="D370">
-        <v>1179.536049274757</v>
+        <v>1281.286949704955</v>
       </c>
     </row>
     <row r="371">
@@ -5183,7 +5183,7 @@
         <v>2028</v>
       </c>
       <c r="D371">
-        <v>1281.291845021592</v>
+        <v>1391.858564865246</v>
       </c>
     </row>
     <row r="372">
@@ -5196,7 +5196,7 @@
         <v>2024</v>
       </c>
       <c r="D372">
-        <v>989.0958816970813</v>
+        <v>989.0958816970777</v>
       </c>
     </row>
     <row r="373">
@@ -5222,7 +5222,7 @@
         <v>2026</v>
       </c>
       <c r="D374">
-        <v>1066.216920638724</v>
+        <v>1149.376966302065</v>
       </c>
     </row>
     <row r="375">
@@ -5235,7 +5235,7 @@
         <v>2027</v>
       </c>
       <c r="D375">
-        <v>1149.386108155766</v>
+        <v>1239.080475660327</v>
       </c>
     </row>
     <row r="376">
@@ -5248,7 +5248,7 @@
         <v>2028</v>
       </c>
       <c r="D376">
-        <v>1239.083969970697</v>
+        <v>1335.796226484521</v>
       </c>
     </row>
     <row r="377">
@@ -5261,7 +5261,7 @@
         <v>2024</v>
       </c>
       <c r="D377">
-        <v>989.0958816970813</v>
+        <v>989.0958816970777</v>
       </c>
     </row>
     <row r="378">
@@ -5287,7 +5287,7 @@
         <v>2026</v>
       </c>
       <c r="D379">
-        <v>1066.216920638724</v>
+        <v>1149.376966302065</v>
       </c>
     </row>
     <row r="380">
@@ -5300,7 +5300,7 @@
         <v>2027</v>
       </c>
       <c r="D380">
-        <v>1149.386108155766</v>
+        <v>1239.080475660327</v>
       </c>
     </row>
     <row r="381">
@@ -5313,7 +5313,7 @@
         <v>2028</v>
       </c>
       <c r="D381">
-        <v>1239.083969970697</v>
+        <v>1335.796226484521</v>
       </c>
     </row>
     <row r="382">
@@ -5326,7 +5326,7 @@
         <v>2024</v>
       </c>
       <c r="D382">
-        <v>990.6232761791877</v>
+        <v>990.623276179186</v>
       </c>
     </row>
     <row r="383">
@@ -5352,7 +5352,7 @@
         <v>2026</v>
       </c>
       <c r="D384">
-        <v>1068.893385223931</v>
+        <v>1153.414729407779</v>
       </c>
     </row>
     <row r="385">
@@ -5365,7 +5365,7 @@
         <v>2027</v>
       </c>
       <c r="D385">
-        <v>1153.438060938351</v>
+        <v>1244.767366177164</v>
       </c>
     </row>
     <row r="386">
@@ -5378,7 +5378,7 @@
         <v>2028</v>
       </c>
       <c r="D386">
-        <v>1244.776129129584</v>
+        <v>1343.38367643111</v>
       </c>
     </row>
     <row r="387">
@@ -5391,7 +5391,7 @@
         <v>2024</v>
       </c>
       <c r="D387">
-        <v>989.0958816970813</v>
+        <v>989.0958816970777</v>
       </c>
     </row>
     <row r="388">
@@ -5417,7 +5417,7 @@
         <v>2026</v>
       </c>
       <c r="D389">
-        <v>1066.216920638724</v>
+        <v>1149.376966302065</v>
       </c>
     </row>
     <row r="390">
@@ -5430,7 +5430,7 @@
         <v>2027</v>
       </c>
       <c r="D390">
-        <v>1149.386108155766</v>
+        <v>1239.080475660327</v>
       </c>
     </row>
     <row r="391">
@@ -5443,7 +5443,7 @@
         <v>2028</v>
       </c>
       <c r="D391">
-        <v>1239.083969970697</v>
+        <v>1335.796226484521</v>
       </c>
     </row>
     <row r="392">
@@ -5456,7 +5456,7 @@
         <v>2024</v>
       </c>
       <c r="D392">
-        <v>989.0958816970813</v>
+        <v>989.0958816970777</v>
       </c>
     </row>
     <row r="393">
@@ -5482,7 +5482,7 @@
         <v>2026</v>
       </c>
       <c r="D394">
-        <v>1066.216920638724</v>
+        <v>1149.376966302065</v>
       </c>
     </row>
     <row r="395">
@@ -5495,7 +5495,7 @@
         <v>2027</v>
       </c>
       <c r="D395">
-        <v>1149.386108155766</v>
+        <v>1239.080475660327</v>
       </c>
     </row>
     <row r="396">
@@ -5508,7 +5508,7 @@
         <v>2028</v>
       </c>
       <c r="D396">
-        <v>1239.083969970697</v>
+        <v>1335.796226484521</v>
       </c>
     </row>
     <row r="397">
@@ -5521,7 +5521,7 @@
         <v>2024</v>
       </c>
       <c r="D397">
-        <v>989.0958816970813</v>
+        <v>989.0958816970777</v>
       </c>
     </row>
     <row r="398">
@@ -5547,7 +5547,7 @@
         <v>2026</v>
       </c>
       <c r="D399">
-        <v>1066.216920638724</v>
+        <v>1149.376966302065</v>
       </c>
     </row>
     <row r="400">
@@ -5560,7 +5560,7 @@
         <v>2027</v>
       </c>
       <c r="D400">
-        <v>1149.386108155766</v>
+        <v>1239.080475660327</v>
       </c>
     </row>
     <row r="401">
@@ -5573,7 +5573,7 @@
         <v>2028</v>
       </c>
       <c r="D401">
-        <v>1239.083969970697</v>
+        <v>1335.796226484521</v>
       </c>
     </row>
     <row r="402">
@@ -5586,7 +5586,7 @@
         <v>2024</v>
       </c>
       <c r="D402">
-        <v>989.0958816970813</v>
+        <v>989.0958816970777</v>
       </c>
     </row>
     <row r="403">
@@ -5612,7 +5612,7 @@
         <v>2026</v>
       </c>
       <c r="D404">
-        <v>1066.216920638724</v>
+        <v>1149.376966302065</v>
       </c>
     </row>
     <row r="405">
@@ -5625,7 +5625,7 @@
         <v>2027</v>
       </c>
       <c r="D405">
-        <v>1149.386108155766</v>
+        <v>1239.080475660327</v>
       </c>
     </row>
     <row r="406">
@@ -5638,7 +5638,7 @@
         <v>2028</v>
       </c>
       <c r="D406">
-        <v>1239.083969970697</v>
+        <v>1335.796226484521</v>
       </c>
     </row>
     <row r="407">
@@ -5651,7 +5651,7 @@
         <v>2024</v>
       </c>
       <c r="D407">
-        <v>1296.274731969841</v>
+        <v>1296.274731969837</v>
       </c>
     </row>
     <row r="408">
@@ -5677,7 +5677,7 @@
         <v>2026</v>
       </c>
       <c r="D409">
-        <v>1635.658184753941</v>
+        <v>2063.956540662065</v>
       </c>
     </row>
     <row r="410">
@@ -5690,7 +5690,7 @@
         <v>2027</v>
       </c>
       <c r="D410">
-        <v>2063.957889064045</v>
+        <v>2604.485226808949</v>
       </c>
     </row>
     <row r="411">
@@ -5703,7 +5703,7 @@
         <v>2028</v>
       </c>
       <c r="D411">
-        <v>2604.485265426066</v>
+        <v>3286.572883081778</v>
       </c>
     </row>
     <row r="412">
@@ -5716,7 +5716,7 @@
         <v>2024</v>
       </c>
       <c r="D412">
-        <v>1387.347851293452</v>
+        <v>1387.347851293451</v>
       </c>
     </row>
     <row r="413">
@@ -5742,7 +5742,7 @@
         <v>2026</v>
       </c>
       <c r="D414">
-        <v>1494.451222280168</v>
+        <v>1611.43941243517</v>
       </c>
     </row>
     <row r="415">
@@ -5755,7 +5755,7 @@
         <v>2027</v>
       </c>
       <c r="D415">
-        <v>1610.685559635651</v>
+        <v>1736.890450653714</v>
       </c>
     </row>
     <row r="416">
@@ -5768,7 +5768,7 @@
         <v>2028</v>
       </c>
       <c r="D416">
-        <v>1737.269422847491</v>
+        <v>1873.333582833612</v>
       </c>
     </row>
     <row r="417">
@@ -5781,7 +5781,7 @@
         <v>2024</v>
       </c>
       <c r="D417">
-        <v>1201.28277208153</v>
+        <v>1201.282772081527</v>
       </c>
     </row>
     <row r="418">
@@ -5807,7 +5807,7 @@
         <v>2026</v>
       </c>
       <c r="D419">
-        <v>1296.417380237399</v>
+        <v>1398.286439948724</v>
       </c>
     </row>
     <row r="420">
@@ -5820,7 +5820,7 @@
         <v>2027</v>
       </c>
       <c r="D420">
-        <v>1397.776419520539</v>
+        <v>1505.649359127841</v>
       </c>
     </row>
     <row r="421">
@@ -5833,7 +5833,7 @@
         <v>2028</v>
       </c>
       <c r="D421">
-        <v>1505.2989046203</v>
+        <v>1620.123968546537</v>
       </c>
     </row>
     <row r="422">
@@ -5846,7 +5846,7 @@
         <v>2024</v>
       </c>
       <c r="D422">
-        <v>1251.159338528732</v>
+        <v>1251.159338528728</v>
       </c>
     </row>
     <row r="423">
@@ -5872,7 +5872,7 @@
         <v>2026</v>
       </c>
       <c r="D424">
-        <v>1349.443285600936</v>
+        <v>1454.907753129763</v>
       </c>
     </row>
     <row r="425">
@@ -5885,7 +5885,7 @@
         <v>2027</v>
       </c>
       <c r="D425">
-        <v>1454.56343981284</v>
+        <v>1566.919603291836</v>
       </c>
     </row>
     <row r="426">
@@ -5898,7 +5898,7 @@
         <v>2028</v>
       </c>
       <c r="D426">
-        <v>1566.683125546499</v>
+        <v>1686.791194021059</v>
       </c>
     </row>
     <row r="427">
@@ -5911,7 +5911,7 @@
         <v>2024</v>
       </c>
       <c r="D427">
-        <v>1489.165773263901</v>
+        <v>1489.165773263898</v>
       </c>
     </row>
     <row r="428">
@@ -5937,7 +5937,7 @@
         <v>2026</v>
       </c>
       <c r="D429">
-        <v>1607.937886216509</v>
+        <v>1736.56346334983</v>
       </c>
     </row>
     <row r="430">
@@ -5950,7 +5950,7 @@
         <v>2027</v>
       </c>
       <c r="D430">
-        <v>1736.689414623867</v>
+        <v>1876.297556606977</v>
       </c>
     </row>
     <row r="431">
@@ -5963,7 +5963,7 @@
         <v>2028</v>
       </c>
       <c r="D431">
-        <v>1876.342595556797</v>
+        <v>2027.421468166711</v>
       </c>
     </row>
     <row r="432">
@@ -5976,7 +5976,7 @@
         <v>2024</v>
       </c>
       <c r="D432">
-        <v>1027.117335737308</v>
+        <v>1027.117335737307</v>
       </c>
     </row>
     <row r="433">
@@ -6002,7 +6002,7 @@
         <v>2026</v>
       </c>
       <c r="D434">
-        <v>1099.79149468284</v>
+        <v>1177.399050906694</v>
       </c>
     </row>
     <row r="435">
@@ -6015,7 +6015,7 @@
         <v>2027</v>
       </c>
       <c r="D435">
-        <v>1177.292848388036</v>
+        <v>1259.918656092133</v>
       </c>
     </row>
     <row r="436">
@@ -6028,7 +6028,7 @@
         <v>2028</v>
       </c>
       <c r="D436">
-        <v>1259.86081432411</v>
+        <v>1348.036080898575</v>
       </c>
     </row>
     <row r="437">
@@ -6041,7 +6041,7 @@
         <v>2024</v>
       </c>
       <c r="D437">
-        <v>1027.117335737308</v>
+        <v>1027.117335737307</v>
       </c>
     </row>
     <row r="438">
@@ -6067,7 +6067,7 @@
         <v>2026</v>
       </c>
       <c r="D439">
-        <v>1099.79149468284</v>
+        <v>1177.399050906694</v>
       </c>
     </row>
     <row r="440">
@@ -6080,7 +6080,7 @@
         <v>2027</v>
       </c>
       <c r="D440">
-        <v>1177.292848388036</v>
+        <v>1259.918656092133</v>
       </c>
     </row>
     <row r="441">
@@ -6093,7 +6093,7 @@
         <v>2028</v>
       </c>
       <c r="D441">
-        <v>1259.86081432411</v>
+        <v>1348.036080898575</v>
       </c>
     </row>
     <row r="442">
@@ -6106,7 +6106,7 @@
         <v>2024</v>
       </c>
       <c r="D442">
-        <v>1027.117335737308</v>
+        <v>1027.117335737307</v>
       </c>
     </row>
     <row r="443">
@@ -6132,7 +6132,7 @@
         <v>2026</v>
       </c>
       <c r="D444">
-        <v>1099.79149468284</v>
+        <v>1177.399050906694</v>
       </c>
     </row>
     <row r="445">
@@ -6145,7 +6145,7 @@
         <v>2027</v>
       </c>
       <c r="D445">
-        <v>1177.292848388036</v>
+        <v>1259.918656092133</v>
       </c>
     </row>
     <row r="446">
@@ -6158,7 +6158,7 @@
         <v>2028</v>
       </c>
       <c r="D446">
-        <v>1259.86081432411</v>
+        <v>1348.036080898575</v>
       </c>
     </row>
     <row r="447">
@@ -6171,7 +6171,7 @@
         <v>2024</v>
       </c>
       <c r="D447">
-        <v>1219.771220007621</v>
+        <v>1219.77122000762</v>
       </c>
     </row>
     <row r="448">
@@ -6197,7 +6197,7 @@
         <v>2026</v>
       </c>
       <c r="D449">
-        <v>1506.606393371805</v>
+        <v>1881.977999984401</v>
       </c>
     </row>
     <row r="450">
@@ -6210,7 +6210,7 @@
         <v>2027</v>
       </c>
       <c r="D450">
-        <v>1895.999633772531</v>
+        <v>2431.048993256307</v>
       </c>
     </row>
     <row r="451">
@@ -6223,7 +6223,7 @@
         <v>2028</v>
       </c>
       <c r="D451">
-        <v>2442.966347814211</v>
+        <v>3186.722157379639</v>
       </c>
     </row>
     <row r="452">
@@ -6236,7 +6236,7 @@
         <v>2024</v>
       </c>
       <c r="D452">
-        <v>1489.165773263901</v>
+        <v>1489.165773263898</v>
       </c>
     </row>
     <row r="453">
@@ -6262,7 +6262,7 @@
         <v>2026</v>
       </c>
       <c r="D454">
-        <v>1607.937886216509</v>
+        <v>1736.56346334983</v>
       </c>
     </row>
     <row r="455">
@@ -6275,7 +6275,7 @@
         <v>2027</v>
       </c>
       <c r="D455">
-        <v>1736.689414623867</v>
+        <v>1876.297556606977</v>
       </c>
     </row>
     <row r="456">
@@ -6288,7 +6288,7 @@
         <v>2028</v>
       </c>
       <c r="D456">
-        <v>1876.342595556797</v>
+        <v>2027.421468166711</v>
       </c>
     </row>
     <row r="457">
@@ -6301,7 +6301,7 @@
         <v>2024</v>
       </c>
       <c r="D457">
-        <v>1274.339646535498</v>
+        <v>1274.339646535497</v>
       </c>
     </row>
     <row r="458">
@@ -6327,7 +6327,7 @@
         <v>2026</v>
       </c>
       <c r="D459">
-        <v>1374.098165253175</v>
+        <v>1481.250843230369</v>
       </c>
     </row>
     <row r="460">
@@ -6340,7 +6340,7 @@
         <v>2027</v>
       </c>
       <c r="D460">
-        <v>1480.988147903832</v>
+        <v>1595.462733583083</v>
       </c>
     </row>
     <row r="461">
@@ -6353,7 +6353,7 @@
         <v>2028</v>
       </c>
       <c r="D461">
-        <v>1595.283660440269</v>
+        <v>1717.90235833593</v>
       </c>
     </row>
     <row r="462">
@@ -6366,7 +6366,7 @@
         <v>2024</v>
       </c>
       <c r="D462">
-        <v>1201.28277208153</v>
+        <v>1201.282772081527</v>
       </c>
     </row>
     <row r="463">
@@ -6392,7 +6392,7 @@
         <v>2026</v>
       </c>
       <c r="D464">
-        <v>1296.417380237399</v>
+        <v>1398.286439948724</v>
       </c>
     </row>
     <row r="465">
@@ -6405,7 +6405,7 @@
         <v>2027</v>
       </c>
       <c r="D465">
-        <v>1397.776419520539</v>
+        <v>1505.649359127841</v>
       </c>
     </row>
     <row r="466">
@@ -6418,7 +6418,7 @@
         <v>2028</v>
       </c>
       <c r="D466">
-        <v>1505.2989046203</v>
+        <v>1620.123968546537</v>
       </c>
     </row>
     <row r="467">
@@ -6431,7 +6431,7 @@
         <v>2024</v>
       </c>
       <c r="D467">
-        <v>1259.160861960486</v>
+        <v>1259.160861960484</v>
       </c>
     </row>
     <row r="468">
@@ -6457,7 +6457,7 @@
         <v>2026</v>
       </c>
       <c r="D469">
-        <v>1357.950319371355</v>
+        <v>1463.993113267014</v>
       </c>
     </row>
     <row r="470">
@@ -6470,7 +6470,7 @@
         <v>2027</v>
       </c>
       <c r="D470">
-        <v>1463.676682634864</v>
+        <v>1576.757968044049</v>
       </c>
     </row>
     <row r="471">
@@ -6483,7 +6483,7 @@
         <v>2028</v>
       </c>
       <c r="D471">
-        <v>1576.541067032163</v>
+        <v>1697.507868858743</v>
       </c>
     </row>
     <row r="472">
@@ -6496,7 +6496,7 @@
         <v>2024</v>
       </c>
       <c r="D472">
-        <v>1417.252237396007</v>
+        <v>1417.252237396002</v>
       </c>
     </row>
     <row r="473">
@@ -6522,7 +6522,7 @@
         <v>2026</v>
       </c>
       <c r="D474">
-        <v>1591.019657192704</v>
+        <v>1786.19143560442</v>
       </c>
     </row>
     <row r="475">
@@ -6535,7 +6535,7 @@
         <v>2027</v>
       </c>
       <c r="D475">
-        <v>1786.197557701279</v>
+        <v>2005.436839710124</v>
       </c>
     </row>
     <row r="476">
@@ -6548,7 +6548,7 @@
         <v>2028</v>
       </c>
       <c r="D476">
-        <v>2005.437264901511</v>
+        <v>2251.59487162673</v>
       </c>
     </row>
     <row r="477">
@@ -6561,7 +6561,7 @@
         <v>2024</v>
       </c>
       <c r="D477">
-        <v>1469.381234964764</v>
+        <v>1469.381234964761</v>
       </c>
     </row>
     <row r="478">
@@ -6587,7 +6587,7 @@
         <v>2026</v>
       </c>
       <c r="D479">
-        <v>1643.226622522047</v>
+        <v>1838.75517483274</v>
       </c>
     </row>
     <row r="480">
@@ -6600,7 +6600,7 @@
         <v>2027</v>
       </c>
       <c r="D480">
-        <v>1839.003800901351</v>
+        <v>2059.633667861199</v>
       </c>
     </row>
     <row r="481">
@@ -6613,7 +6613,7 @@
         <v>2028</v>
       </c>
       <c r="D481">
-        <v>2059.695730841348</v>
+        <v>2307.253513910126</v>
       </c>
     </row>
     <row r="482">
@@ -6626,7 +6626,7 @@
         <v>2024</v>
       </c>
       <c r="D482">
-        <v>1027.117335737308</v>
+        <v>1027.117335737307</v>
       </c>
     </row>
     <row r="483">
@@ -6652,7 +6652,7 @@
         <v>2026</v>
       </c>
       <c r="D484">
-        <v>1099.79149468284</v>
+        <v>1177.399050906694</v>
       </c>
     </row>
     <row r="485">
@@ -6665,7 +6665,7 @@
         <v>2027</v>
       </c>
       <c r="D485">
-        <v>1177.292848388036</v>
+        <v>1259.918656092133</v>
       </c>
     </row>
     <row r="486">
@@ -6678,7 +6678,7 @@
         <v>2028</v>
       </c>
       <c r="D486">
-        <v>1259.86081432411</v>
+        <v>1348.036080898575</v>
       </c>
     </row>
     <row r="487">
@@ -6717,7 +6717,7 @@
         <v>2026</v>
       </c>
       <c r="D489">
-        <v>1099.791494682885</v>
+        <v>1177.399050907325</v>
       </c>
     </row>
     <row r="490">
@@ -6730,7 +6730,7 @@
         <v>2027</v>
       </c>
       <c r="D490">
-        <v>1177.292848388828</v>
+        <v>1259.918656094166</v>
       </c>
     </row>
     <row r="491">
@@ -6743,7 +6743,7 @@
         <v>2028</v>
       </c>
       <c r="D491">
-        <v>1259.860814326263</v>
+        <v>1348.036080902589</v>
       </c>
     </row>
     <row r="492">
@@ -6756,7 +6756,7 @@
         <v>2024</v>
       </c>
       <c r="D492">
-        <v>1027.117335737308</v>
+        <v>1027.117335737307</v>
       </c>
     </row>
     <row r="493">
@@ -6782,7 +6782,7 @@
         <v>2026</v>
       </c>
       <c r="D494">
-        <v>1099.79149468284</v>
+        <v>1177.399050906694</v>
       </c>
     </row>
     <row r="495">
@@ -6795,7 +6795,7 @@
         <v>2027</v>
       </c>
       <c r="D495">
-        <v>1177.292848388036</v>
+        <v>1259.918656092133</v>
       </c>
     </row>
     <row r="496">
@@ -6808,7 +6808,7 @@
         <v>2028</v>
       </c>
       <c r="D496">
-        <v>1259.86081432411</v>
+        <v>1348.036080898575</v>
       </c>
     </row>
     <row r="497">
@@ -6821,7 +6821,7 @@
         <v>2024</v>
       </c>
       <c r="D497">
-        <v>1098.615899030694</v>
+        <v>1098.615899030695</v>
       </c>
     </row>
     <row r="498">
@@ -6847,7 +6847,7 @@
         <v>2026</v>
       </c>
       <c r="D499">
-        <v>1194.877939418817</v>
+        <v>1298.854674479154</v>
       </c>
     </row>
     <row r="500">
@@ -6860,7 +6860,7 @@
         <v>2027</v>
       </c>
       <c r="D500">
-        <v>1298.349922143288</v>
+        <v>1409.452744205094</v>
       </c>
     </row>
     <row r="501">
@@ -6873,7 +6873,7 @@
         <v>2028</v>
       </c>
       <c r="D501">
-        <v>1409.068502901873</v>
+        <v>1528.217752266503</v>
       </c>
     </row>
     <row r="502">
@@ -6886,7 +6886,7 @@
         <v>2024</v>
       </c>
       <c r="D502">
-        <v>1108.804614153114</v>
+        <v>1108.804614153112</v>
       </c>
     </row>
     <row r="503">
@@ -6912,7 +6912,7 @@
         <v>2026</v>
       </c>
       <c r="D504">
-        <v>1256.665588867</v>
+        <v>1427.478226898895</v>
       </c>
     </row>
     <row r="505">
@@ -6925,7 +6925,7 @@
         <v>2027</v>
       </c>
       <c r="D505">
-        <v>1429.169908336475</v>
+        <v>1630.975531851635</v>
       </c>
     </row>
     <row r="506">
@@ -6938,7 +6938,7 @@
         <v>2028</v>
       </c>
       <c r="D506">
-        <v>1631.984510946365</v>
+        <v>1866.943432602477</v>
       </c>
     </row>
     <row r="507">
@@ -6951,7 +6951,7 @@
         <v>2024</v>
       </c>
       <c r="D507">
-        <v>1125.561607850815</v>
+        <v>1125.561607850813</v>
       </c>
     </row>
     <row r="508">
@@ -6977,7 +6977,7 @@
         <v>2026</v>
       </c>
       <c r="D509">
-        <v>1265.083125115205</v>
+        <v>1422.074923318761</v>
       </c>
     </row>
     <row r="510">
@@ -6990,7 +6990,7 @@
         <v>2027</v>
       </c>
       <c r="D510">
-        <v>1422.095179528333</v>
+        <v>1598.814490967251</v>
       </c>
     </row>
     <row r="511">
@@ -7003,7 +7003,7 @@
         <v>2028</v>
       </c>
       <c r="D511">
-        <v>1598.817118145336</v>
+        <v>1797.528622256546</v>
       </c>
     </row>
     <row r="512">
@@ -7042,7 +7042,7 @@
         <v>2026</v>
       </c>
       <c r="D514">
-        <v>1441.65460013753</v>
+        <v>1517.493113656014</v>
       </c>
     </row>
     <row r="515">
@@ -7055,7 +7055,7 @@
         <v>2027</v>
       </c>
       <c r="D515">
-        <v>1517.493487579189</v>
+        <v>1597.315536320434</v>
       </c>
     </row>
     <row r="516">
@@ -7068,7 +7068,7 @@
         <v>2028</v>
       </c>
       <c r="D516">
-        <v>1597.315513441287</v>
+        <v>1681.336666357585</v>
       </c>
     </row>
     <row r="517">
@@ -7107,7 +7107,7 @@
         <v>2026</v>
       </c>
       <c r="D519">
-        <v>1441.65460013753</v>
+        <v>1517.493113656014</v>
       </c>
     </row>
     <row r="520">
@@ -7120,7 +7120,7 @@
         <v>2027</v>
       </c>
       <c r="D520">
-        <v>1517.493487579189</v>
+        <v>1597.315536320434</v>
       </c>
     </row>
     <row r="521">
@@ -7133,7 +7133,7 @@
         <v>2028</v>
       </c>
       <c r="D521">
-        <v>1597.315513441287</v>
+        <v>1681.336666357585</v>
       </c>
     </row>
     <row r="522">
@@ -7146,7 +7146,7 @@
         <v>2024</v>
       </c>
       <c r="D522">
-        <v>1954.511344129649</v>
+        <v>1954.511344129645</v>
       </c>
     </row>
     <row r="523">
@@ -7172,7 +7172,7 @@
         <v>2026</v>
       </c>
       <c r="D524">
-        <v>2478.202443508378</v>
+        <v>3145.23694344636</v>
       </c>
     </row>
     <row r="525">
@@ -7185,7 +7185,7 @@
         <v>2027</v>
       </c>
       <c r="D525">
-        <v>3144.893295273958</v>
+        <v>3994.345217791162</v>
       </c>
     </row>
     <row r="526">
@@ -7198,7 +7198,7 @@
         <v>2028</v>
       </c>
       <c r="D526">
-        <v>3994.394765448094</v>
+        <v>5072.872964576304</v>
       </c>
     </row>
     <row r="527">
@@ -7211,7 +7211,7 @@
         <v>2024</v>
       </c>
       <c r="D527">
-        <v>1102.140782647695</v>
+        <v>1102.140782647694</v>
       </c>
     </row>
     <row r="528">
@@ -7237,7 +7237,7 @@
         <v>2026</v>
       </c>
       <c r="D529">
-        <v>1196.908143214904</v>
+        <v>1298.683499529731</v>
       </c>
     </row>
     <row r="530">
@@ -7250,7 +7250,7 @@
         <v>2027</v>
       </c>
       <c r="D530">
-        <v>1297.795899679555</v>
+        <v>1404.991836452143</v>
       </c>
     </row>
     <row r="531">
@@ -7263,7 +7263,7 @@
         <v>2028</v>
       </c>
       <c r="D531">
-        <v>1404.243908547583</v>
+        <v>1517.576254184347</v>
       </c>
     </row>
     <row r="532">
@@ -7276,7 +7276,7 @@
         <v>2024</v>
       </c>
       <c r="D532">
-        <v>1102.14078263447</v>
+        <v>1102.140782634466</v>
       </c>
     </row>
     <row r="533">
@@ -7302,7 +7302,7 @@
         <v>2026</v>
       </c>
       <c r="D534">
-        <v>1196.908143178189</v>
+        <v>1298.683499464748</v>
       </c>
     </row>
     <row r="535">
@@ -7315,7 +7315,7 @@
         <v>2027</v>
       </c>
       <c r="D535">
-        <v>1297.795899614802</v>
+        <v>1404.991836354276</v>
       </c>
     </row>
     <row r="536">
@@ -7328,7 +7328,7 @@
         <v>2028</v>
       </c>
       <c r="D536">
-        <v>1404.243908450667</v>
+        <v>1517.576254051779</v>
       </c>
     </row>
     <row r="537">
@@ -7341,7 +7341,7 @@
         <v>2024</v>
       </c>
       <c r="D537">
-        <v>1102.14078263447</v>
+        <v>1102.140782634466</v>
       </c>
     </row>
     <row r="538">
@@ -7367,7 +7367,7 @@
         <v>2026</v>
       </c>
       <c r="D539">
-        <v>1196.908143178189</v>
+        <v>1298.683499464748</v>
       </c>
     </row>
     <row r="540">
@@ -7380,7 +7380,7 @@
         <v>2027</v>
       </c>
       <c r="D540">
-        <v>1297.795899614802</v>
+        <v>1404.991836354276</v>
       </c>
     </row>
     <row r="541">
@@ -7393,7 +7393,7 @@
         <v>2028</v>
       </c>
       <c r="D541">
-        <v>1404.243908450667</v>
+        <v>1517.576254051779</v>
       </c>
     </row>
     <row r="542">
@@ -7406,7 +7406,7 @@
         <v>2024</v>
       </c>
       <c r="D542">
-        <v>1102.14078263447</v>
+        <v>1102.140782634466</v>
       </c>
     </row>
     <row r="543">
@@ -7432,7 +7432,7 @@
         <v>2026</v>
       </c>
       <c r="D544">
-        <v>1196.908143178189</v>
+        <v>1298.683499464748</v>
       </c>
     </row>
     <row r="545">
@@ -7445,7 +7445,7 @@
         <v>2027</v>
       </c>
       <c r="D545">
-        <v>1297.795899614802</v>
+        <v>1404.991836354276</v>
       </c>
     </row>
     <row r="546">
@@ -7458,7 +7458,7 @@
         <v>2028</v>
       </c>
       <c r="D546">
-        <v>1404.243908450667</v>
+        <v>1517.576254051779</v>
       </c>
     </row>
     <row r="547">
@@ -7471,7 +7471,7 @@
         <v>2024</v>
       </c>
       <c r="D547">
-        <v>1102.140782647695</v>
+        <v>1102.140782647694</v>
       </c>
     </row>
     <row r="548">
@@ -7497,7 +7497,7 @@
         <v>2026</v>
       </c>
       <c r="D549">
-        <v>1196.908143214904</v>
+        <v>1298.683499529731</v>
       </c>
     </row>
     <row r="550">
@@ -7510,7 +7510,7 @@
         <v>2027</v>
       </c>
       <c r="D550">
-        <v>1297.795899679555</v>
+        <v>1404.991836452143</v>
       </c>
     </row>
     <row r="551">
@@ -7523,7 +7523,7 @@
         <v>2028</v>
       </c>
       <c r="D551">
-        <v>1404.243908547583</v>
+        <v>1517.576254184347</v>
       </c>
     </row>
     <row r="552">
@@ -7536,7 +7536,7 @@
         <v>2024</v>
       </c>
       <c r="D552">
-        <v>1102.14078263447</v>
+        <v>1102.140782634466</v>
       </c>
     </row>
     <row r="553">
@@ -7562,7 +7562,7 @@
         <v>2026</v>
       </c>
       <c r="D554">
-        <v>1196.908143178189</v>
+        <v>1298.683499464748</v>
       </c>
     </row>
     <row r="555">
@@ -7575,7 +7575,7 @@
         <v>2027</v>
       </c>
       <c r="D555">
-        <v>1297.795899614802</v>
+        <v>1404.991836354276</v>
       </c>
     </row>
     <row r="556">
@@ -7588,7 +7588,7 @@
         <v>2028</v>
       </c>
       <c r="D556">
-        <v>1404.243908450667</v>
+        <v>1517.576254051779</v>
       </c>
     </row>
     <row r="557">
@@ -7601,7 +7601,7 @@
         <v>2024</v>
       </c>
       <c r="D557">
-        <v>1096.781958136696</v>
+        <v>1096.781958136691</v>
       </c>
     </row>
     <row r="558">
@@ -7627,7 +7627,7 @@
         <v>2026</v>
       </c>
       <c r="D559">
-        <v>1193.635032130132</v>
+        <v>1298.543499831651</v>
       </c>
     </row>
     <row r="560">
@@ -7640,7 +7640,7 @@
         <v>2027</v>
       </c>
       <c r="D560">
-        <v>1298.237716828806</v>
+        <v>1411.134127260468</v>
       </c>
     </row>
     <row r="561">
@@ -7653,7 +7653,7 @@
         <v>2028</v>
       </c>
       <c r="D561">
-        <v>1410.929759649669</v>
+        <v>1532.820795251915</v>
       </c>
     </row>
     <row r="562">
@@ -7666,7 +7666,7 @@
         <v>2024</v>
       </c>
       <c r="D562">
-        <v>1099.712611473211</v>
+        <v>1099.712611473212</v>
       </c>
     </row>
     <row r="563">
@@ -7692,7 +7692,7 @@
         <v>2026</v>
       </c>
       <c r="D564">
-        <v>1195.664346892341</v>
+        <v>1299.143510256634</v>
       </c>
     </row>
     <row r="565">
@@ -7705,7 +7705,7 @@
         <v>2027</v>
       </c>
       <c r="D565">
-        <v>1298.520562646633</v>
+        <v>1408.633009406429</v>
       </c>
     </row>
     <row r="566">
@@ -7718,7 +7718,7 @@
         <v>2028</v>
       </c>
       <c r="D566">
-        <v>1408.134461438102</v>
+        <v>1525.72896814552</v>
       </c>
     </row>
     <row r="567">
@@ -7757,7 +7757,7 @@
         <v>2026</v>
       </c>
       <c r="D569">
-        <v>1278.437248543831</v>
+        <v>1383.79725945458</v>
       </c>
     </row>
     <row r="570">
@@ -7770,7 +7770,7 @@
         <v>2027</v>
       </c>
       <c r="D570">
-        <v>1383.693493890746</v>
+        <v>1497.293837534714</v>
       </c>
     </row>
     <row r="571">
@@ -7783,7 +7783,7 @@
         <v>2028</v>
       </c>
       <c r="D571">
-        <v>1497.233674034487</v>
+        <v>1619.903915944565</v>
       </c>
     </row>
     <row r="572">
@@ -7796,7 +7796,7 @@
         <v>2024</v>
       </c>
       <c r="D572">
-        <v>1126.669040237352</v>
+        <v>1126.669040237351</v>
       </c>
     </row>
     <row r="573">
@@ -7822,7 +7822,7 @@
         <v>2026</v>
       </c>
       <c r="D574">
-        <v>1220.555900933931</v>
+        <v>1321.21927065098</v>
       </c>
     </row>
     <row r="575">
@@ -7835,7 +7835,7 @@
         <v>2027</v>
       </c>
       <c r="D575">
-        <v>1320.442951560455</v>
+        <v>1426.534451078045</v>
       </c>
     </row>
     <row r="576">
@@ -7848,7 +7848,7 @@
         <v>2028</v>
       </c>
       <c r="D576">
-        <v>1425.912599821616</v>
+        <v>1538.230987440375</v>
       </c>
     </row>
     <row r="577">
@@ -7861,7 +7861,7 @@
         <v>2024</v>
       </c>
       <c r="D577">
-        <v>1237.117205893998</v>
+        <v>1237.117205893994</v>
       </c>
     </row>
     <row r="578">
@@ -7887,7 +7887,7 @@
         <v>2026</v>
       </c>
       <c r="D579">
-        <v>1378.934518354994</v>
+        <v>1539.158079308317</v>
       </c>
     </row>
     <row r="580">
@@ -7900,7 +7900,7 @@
         <v>2027</v>
       </c>
       <c r="D580">
-        <v>1538.464858489175</v>
+        <v>1718.077138865654</v>
       </c>
     </row>
     <row r="581">
@@ -7913,7 +7913,7 @@
         <v>2028</v>
       </c>
       <c r="D581">
-        <v>1718.326710172685</v>
+        <v>1918.630470729699</v>
       </c>
     </row>
     <row r="582">
@@ -7926,7 +7926,7 @@
         <v>2024</v>
       </c>
       <c r="D582">
-        <v>1313.869631279914</v>
+        <v>1313.869631279915</v>
       </c>
     </row>
     <row r="583">
@@ -7952,7 +7952,7 @@
         <v>2026</v>
       </c>
       <c r="D584">
-        <v>1417.22516912768</v>
+        <v>1528.745324895768</v>
       </c>
     </row>
     <row r="585">
@@ -7965,7 +7965,7 @@
         <v>2027</v>
       </c>
       <c r="D585">
-        <v>1528.750277804093</v>
+        <v>1649.093772712047</v>
       </c>
     </row>
     <row r="586">
@@ -7978,7 +7978,7 @@
         <v>2028</v>
       </c>
       <c r="D586">
-        <v>1649.094547458411</v>
+        <v>1778.918999652934</v>
       </c>
     </row>
     <row r="587">
@@ -8017,7 +8017,7 @@
         <v>2026</v>
       </c>
       <c r="D589">
-        <v>2616.013907599478</v>
+        <v>3441.680770849725</v>
       </c>
     </row>
     <row r="590">
@@ -8030,7 +8030,7 @@
         <v>2027</v>
       </c>
       <c r="D590">
-        <v>3435.644294657553</v>
+        <v>4534.569816902381</v>
       </c>
     </row>
     <row r="591">
@@ -8043,7 +8043,7 @@
         <v>2028</v>
       </c>
       <c r="D591">
-        <v>4536.647148941259</v>
+        <v>5982.71518037104</v>
       </c>
     </row>
     <row r="592">
@@ -8056,7 +8056,7 @@
         <v>2024</v>
       </c>
       <c r="D592">
-        <v>1239.962491344342</v>
+        <v>1239.96249134434</v>
       </c>
     </row>
     <row r="593">
@@ -8082,7 +8082,7 @@
         <v>2026</v>
       </c>
       <c r="D594">
-        <v>1418.576178221469</v>
+        <v>1630.351181161309</v>
       </c>
     </row>
     <row r="595">
@@ -8095,7 +8095,7 @@
         <v>2027</v>
       </c>
       <c r="D595">
-        <v>1634.828177800591</v>
+        <v>1897.871936543206</v>
       </c>
     </row>
     <row r="596">
@@ -8108,7 +8108,7 @@
         <v>2028</v>
       </c>
       <c r="D596">
-        <v>1900.998034837005</v>
+        <v>2220.224737823919</v>
       </c>
     </row>
     <row r="597">
@@ -8121,7 +8121,7 @@
         <v>2024</v>
       </c>
       <c r="D597">
-        <v>955.0791805721416</v>
+        <v>955.0791805721399</v>
       </c>
     </row>
     <row r="598">
@@ -8147,7 +8147,7 @@
         <v>2026</v>
       </c>
       <c r="D599">
-        <v>1027.938046831152</v>
+        <v>1106.405791844594</v>
       </c>
     </row>
     <row r="600">
@@ -8160,7 +8160,7 @@
         <v>2027</v>
       </c>
       <c r="D600">
-        <v>1106.42213336782</v>
+        <v>1190.970819519613</v>
       </c>
     </row>
     <row r="601">
@@ -8173,7 +8173,7 @@
         <v>2028</v>
       </c>
       <c r="D601">
-        <v>1190.976478967482</v>
+        <v>1282.017614342298</v>
       </c>
     </row>
     <row r="602">
@@ -8186,7 +8186,7 @@
         <v>2024</v>
       </c>
       <c r="D602">
-        <v>1317.162412681181</v>
+        <v>1317.162412681178</v>
       </c>
     </row>
     <row r="603">
@@ -8212,7 +8212,7 @@
         <v>2026</v>
       </c>
       <c r="D604">
-        <v>1417.643051952812</v>
+        <v>1525.858970521967</v>
       </c>
     </row>
     <row r="605">
@@ -8225,7 +8225,7 @@
         <v>2027</v>
       </c>
       <c r="D605">
-        <v>1525.881506733458</v>
+        <v>1642.483730646015</v>
       </c>
     </row>
     <row r="606">
@@ -8238,7 +8238,7 @@
         <v>2028</v>
       </c>
       <c r="D606">
-        <v>1642.491535373422</v>
+        <v>1768.047581822119</v>
       </c>
     </row>
     <row r="607">
@@ -8251,7 +8251,7 @@
         <v>2024</v>
       </c>
       <c r="D607">
-        <v>1317.162412681181</v>
+        <v>1317.162412681178</v>
       </c>
     </row>
     <row r="608">
@@ -8277,7 +8277,7 @@
         <v>2026</v>
       </c>
       <c r="D609">
-        <v>1417.643051952812</v>
+        <v>1525.858970521967</v>
       </c>
     </row>
     <row r="610">
@@ -8290,7 +8290,7 @@
         <v>2027</v>
       </c>
       <c r="D610">
-        <v>1525.881506733458</v>
+        <v>1642.483730646015</v>
       </c>
     </row>
     <row r="611">
@@ -8303,7 +8303,7 @@
         <v>2028</v>
       </c>
       <c r="D611">
-        <v>1642.491535373422</v>
+        <v>1768.047581822119</v>
       </c>
     </row>
     <row r="612">
@@ -8316,7 +8316,7 @@
         <v>2024</v>
       </c>
       <c r="D612">
-        <v>1317.162412681181</v>
+        <v>1317.162412681178</v>
       </c>
     </row>
     <row r="613">
@@ -8342,7 +8342,7 @@
         <v>2026</v>
       </c>
       <c r="D614">
-        <v>1417.643051952812</v>
+        <v>1525.858970521967</v>
       </c>
     </row>
     <row r="615">
@@ -8355,7 +8355,7 @@
         <v>2027</v>
       </c>
       <c r="D615">
-        <v>1525.881506733458</v>
+        <v>1642.483730646015</v>
       </c>
     </row>
     <row r="616">
@@ -8368,7 +8368,7 @@
         <v>2028</v>
       </c>
       <c r="D616">
-        <v>1642.491535373422</v>
+        <v>1768.047581822119</v>
       </c>
     </row>
     <row r="617">
@@ -8381,7 +8381,7 @@
         <v>2024</v>
       </c>
       <c r="D617">
-        <v>1317.16241268131</v>
+        <v>1317.162412681308</v>
       </c>
     </row>
     <row r="618">
@@ -8407,7 +8407,7 @@
         <v>2026</v>
       </c>
       <c r="D619">
-        <v>1417.64305195314</v>
+        <v>1525.858970522532</v>
       </c>
     </row>
     <row r="620">
@@ -8420,7 +8420,7 @@
         <v>2027</v>
       </c>
       <c r="D620">
-        <v>1525.881506734026</v>
+        <v>1642.483730646861</v>
       </c>
     </row>
     <row r="621">
@@ -8433,7 +8433,7 @@
         <v>2028</v>
       </c>
       <c r="D621">
-        <v>1642.49153537427</v>
+        <v>1768.047581823295</v>
       </c>
     </row>
     <row r="622">
@@ -8446,7 +8446,7 @@
         <v>2024</v>
       </c>
       <c r="D622">
-        <v>1317.162412681181</v>
+        <v>1317.162412681178</v>
       </c>
     </row>
     <row r="623">
@@ -8472,7 +8472,7 @@
         <v>2026</v>
       </c>
       <c r="D624">
-        <v>1417.643051952812</v>
+        <v>1525.858970521967</v>
       </c>
     </row>
     <row r="625">
@@ -8485,7 +8485,7 @@
         <v>2027</v>
       </c>
       <c r="D625">
-        <v>1525.881506733458</v>
+        <v>1642.483730646015</v>
       </c>
     </row>
     <row r="626">
@@ -8498,7 +8498,7 @@
         <v>2028</v>
       </c>
       <c r="D626">
-        <v>1642.491535373422</v>
+        <v>1768.047581822119</v>
       </c>
     </row>
     <row r="627">
@@ -8511,7 +8511,7 @@
         <v>2024</v>
       </c>
       <c r="D627">
-        <v>1317.162412681181</v>
+        <v>1317.162412681178</v>
       </c>
     </row>
     <row r="628">
@@ -8537,7 +8537,7 @@
         <v>2026</v>
       </c>
       <c r="D629">
-        <v>1417.643051952812</v>
+        <v>1525.858970521967</v>
       </c>
     </row>
     <row r="630">
@@ -8550,7 +8550,7 @@
         <v>2027</v>
       </c>
       <c r="D630">
-        <v>1525.881506733458</v>
+        <v>1642.483730646015</v>
       </c>
     </row>
     <row r="631">
@@ -8563,7 +8563,7 @@
         <v>2028</v>
       </c>
       <c r="D631">
-        <v>1642.491535373422</v>
+        <v>1768.047581822119</v>
       </c>
     </row>
     <row r="632">
@@ -8576,7 +8576,7 @@
         <v>2024</v>
       </c>
       <c r="D632">
-        <v>1317.162412681181</v>
+        <v>1317.162412681178</v>
       </c>
     </row>
     <row r="633">
@@ -8602,7 +8602,7 @@
         <v>2026</v>
       </c>
       <c r="D634">
-        <v>1417.643051952812</v>
+        <v>1525.858970521967</v>
       </c>
     </row>
     <row r="635">
@@ -8615,7 +8615,7 @@
         <v>2027</v>
       </c>
       <c r="D635">
-        <v>1525.881506733458</v>
+        <v>1642.483730646015</v>
       </c>
     </row>
     <row r="636">
@@ -8628,7 +8628,7 @@
         <v>2028</v>
       </c>
       <c r="D636">
-        <v>1642.491535373422</v>
+        <v>1768.047581822119</v>
       </c>
     </row>
     <row r="637">
@@ -8667,7 +8667,7 @@
         <v>2026</v>
       </c>
       <c r="D639">
-        <v>474.0213414842395</v>
+        <v>510.2057991176965</v>
       </c>
     </row>
     <row r="640">
@@ -8680,7 +8680,7 @@
         <v>2027</v>
       </c>
       <c r="D640">
-        <v>510.2133352989738</v>
+        <v>549.2019475304099</v>
       </c>
     </row>
     <row r="641">
@@ -8693,7 +8693,7 @@
         <v>2028</v>
       </c>
       <c r="D641">
-        <v>549.2045575522549</v>
+        <v>591.1870856828351</v>
       </c>
     </row>
     <row r="642">
@@ -8706,7 +8706,7 @@
         <v>2024</v>
       </c>
       <c r="D642">
-        <v>224.3697784915646</v>
+        <v>224.3697784915644</v>
       </c>
     </row>
     <row r="643">
@@ -8732,7 +8732,7 @@
         <v>2026</v>
       </c>
       <c r="D644">
-        <v>241.485974811375</v>
+        <v>259.9198241286077</v>
       </c>
     </row>
     <row r="645">
@@ -8745,7 +8745,7 @@
         <v>2027</v>
       </c>
       <c r="D645">
-        <v>259.9236635839964</v>
+        <v>279.786065198734</v>
       </c>
     </row>
     <row r="646">
@@ -8758,7 +8758,7 @@
         <v>2028</v>
       </c>
       <c r="D646">
-        <v>279.7873949556797</v>
+        <v>301.1750207569866</v>
       </c>
     </row>
     <row r="647">
@@ -8797,7 +8797,7 @@
         <v>2026</v>
       </c>
       <c r="D649">
-        <v>1605.90636935421</v>
+        <v>1697.452378410154</v>
       </c>
     </row>
     <row r="650">
@@ -8810,7 +8810,7 @@
         <v>2027</v>
       </c>
       <c r="D650">
-        <v>1696.322341059088</v>
+        <v>1789.176141079215</v>
       </c>
     </row>
     <row r="651">
@@ -8823,7 +8823,7 @@
         <v>2028</v>
       </c>
       <c r="D651">
-        <v>1788.203581444336</v>
+        <v>1882.782633595598</v>
       </c>
     </row>
     <row r="652">
@@ -8836,7 +8836,7 @@
         <v>2024</v>
       </c>
       <c r="D652">
-        <v>1027.117335737308</v>
+        <v>1027.117335737307</v>
       </c>
     </row>
     <row r="653">
@@ -8862,7 +8862,7 @@
         <v>2026</v>
       </c>
       <c r="D654">
-        <v>1099.79149468284</v>
+        <v>1177.399050906694</v>
       </c>
     </row>
     <row r="655">
@@ -8875,7 +8875,7 @@
         <v>2027</v>
       </c>
       <c r="D655">
-        <v>1177.292848388036</v>
+        <v>1259.918656092133</v>
       </c>
     </row>
     <row r="656">
@@ -8888,7 +8888,7 @@
         <v>2028</v>
       </c>
       <c r="D656">
-        <v>1259.86081432411</v>
+        <v>1348.036080898575</v>
       </c>
     </row>
     <row r="657">
@@ -8927,7 +8927,7 @@
         <v>2026</v>
       </c>
       <c r="D659">
-        <v>1099.79149467694</v>
+        <v>1177.399050897183</v>
       </c>
     </row>
     <row r="660">
@@ -8940,7 +8940,7 @@
         <v>2027</v>
       </c>
       <c r="D660">
-        <v>1177.292848378681</v>
+        <v>1259.918656079157</v>
       </c>
     </row>
     <row r="661">
@@ -8953,7 +8953,7 @@
         <v>2028</v>
       </c>
       <c r="D661">
-        <v>1259.86081431127</v>
+        <v>1348.036080882136</v>
       </c>
     </row>
     <row r="662">
@@ -8966,7 +8966,7 @@
         <v>2024</v>
       </c>
       <c r="D662">
-        <v>1142.324985386801</v>
+        <v>1142.324985386798</v>
       </c>
     </row>
     <row r="663">
@@ -8992,7 +8992,7 @@
         <v>2026</v>
       </c>
       <c r="D664">
-        <v>1210.822460109351</v>
+        <v>1283.792229960093</v>
       </c>
     </row>
     <row r="665">
@@ -9005,7 +9005,7 @@
         <v>2027</v>
       </c>
       <c r="D665">
-        <v>1283.940303596934</v>
+        <v>1362.017747306137</v>
       </c>
     </row>
     <row r="666">
@@ -9018,7 +9018,7 @@
         <v>2028</v>
       </c>
       <c r="D666">
-        <v>1362.081469212865</v>
+        <v>1445.212616156559</v>
       </c>
     </row>
     <row r="667">
@@ -9031,7 +9031,7 @@
         <v>2024</v>
       </c>
       <c r="D667">
-        <v>1144.046329105066</v>
+        <v>1144.046329105065</v>
       </c>
     </row>
     <row r="668">
@@ -9057,7 +9057,7 @@
         <v>2026</v>
       </c>
       <c r="D669">
-        <v>1206.608980095068</v>
+        <v>1272.76502420194</v>
       </c>
     </row>
     <row r="670">
@@ -9070,7 +9070,7 @@
         <v>2027</v>
       </c>
       <c r="D670">
-        <v>1272.845232488974</v>
+        <v>1342.983735313944</v>
       </c>
     </row>
     <row r="671">
@@ -9083,7 +9083,7 @@
         <v>2028</v>
       </c>
       <c r="D671">
-        <v>1343.023168150598</v>
+        <v>1417.201256051555</v>
       </c>
     </row>
     <row r="672">
@@ -9122,7 +9122,7 @@
         <v>2026</v>
       </c>
       <c r="D674">
-        <v>991.9413088870192</v>
+        <v>1059.715785583131</v>
       </c>
     </row>
     <row r="675">
@@ -9135,7 +9135,7 @@
         <v>2027</v>
       </c>
       <c r="D675">
-        <v>1059.746549537962</v>
+        <v>1132.377143185583</v>
       </c>
     </row>
     <row r="676">
@@ -9148,7 +9148,7 @@
         <v>2028</v>
       </c>
       <c r="D676">
-        <v>1132.384000215747</v>
+        <v>1210.042641836528</v>
       </c>
     </row>
     <row r="677">
@@ -9161,7 +9161,7 @@
         <v>2024</v>
       </c>
       <c r="D677">
-        <v>933.6917837602247</v>
+        <v>933.691783760223</v>
       </c>
     </row>
     <row r="678">
@@ -9187,7 +9187,7 @@
         <v>2026</v>
       </c>
       <c r="D679">
-        <v>997.4632690084591</v>
+        <v>1065.751161019673</v>
       </c>
     </row>
     <row r="680">
@@ -9200,7 +9200,7 @@
         <v>2027</v>
       </c>
       <c r="D680">
-        <v>1065.787827833246</v>
+        <v>1139.003527000757</v>
       </c>
     </row>
     <row r="681">
@@ -9213,7 +9213,7 @@
         <v>2028</v>
       </c>
       <c r="D681">
-        <v>1139.012462255342</v>
+        <v>1217.319402568495</v>
       </c>
     </row>
     <row r="682">
@@ -9252,7 +9252,7 @@
         <v>2026</v>
       </c>
       <c r="D684">
-        <v>1688.078249166725</v>
+        <v>1819.276271207014</v>
       </c>
     </row>
     <row r="685">
@@ -9265,7 +9265,7 @@
         <v>2027</v>
       </c>
       <c r="D685">
-        <v>1825.947462951303</v>
+        <v>2013.630897581444</v>
       </c>
     </row>
     <row r="686">
@@ -9278,7 +9278,7 @@
         <v>2028</v>
       </c>
       <c r="D686">
-        <v>1988.793887749151</v>
+        <v>2147.290526818341</v>
       </c>
     </row>
     <row r="687">
@@ -9291,7 +9291,7 @@
         <v>2024</v>
       </c>
       <c r="D687">
-        <v>1559.88631295132</v>
+        <v>1559.886312951319</v>
       </c>
     </row>
     <row r="688">
@@ -9317,7 +9317,7 @@
         <v>2026</v>
       </c>
       <c r="D689">
-        <v>1646.928896118996</v>
+        <v>1738.009603126662</v>
       </c>
     </row>
     <row r="690">
@@ -9330,7 +9330,7 @@
         <v>2027</v>
       </c>
       <c r="D690">
-        <v>1737.566944133524</v>
+        <v>1831.863192544255</v>
       </c>
     </row>
     <row r="691">
@@ -9343,7 +9343,7 @@
         <v>2028</v>
       </c>
       <c r="D691">
-        <v>1831.610885456081</v>
+        <v>1929.987248015037</v>
       </c>
     </row>
     <row r="692">
@@ -9356,7 +9356,7 @@
         <v>2024</v>
       </c>
       <c r="D692">
-        <v>1592.952952253476</v>
+        <v>1592.952952253474</v>
       </c>
     </row>
     <row r="693">
@@ -9382,7 +9382,7 @@
         <v>2026</v>
       </c>
       <c r="D694">
-        <v>1690.037040620934</v>
+        <v>1821.368712397048</v>
       </c>
     </row>
     <row r="695">
@@ -9395,7 +9395,7 @@
         <v>2027</v>
       </c>
       <c r="D695">
-        <v>1828.06052090495</v>
+        <v>2015.978929207843</v>
       </c>
     </row>
     <row r="696">
@@ -9408,7 +9408,7 @@
         <v>2028</v>
       </c>
       <c r="D696">
-        <v>1991.111608447058</v>
+        <v>2149.824225822761</v>
       </c>
     </row>
     <row r="697">
@@ -9421,7 +9421,7 @@
         <v>2024</v>
       </c>
       <c r="D697">
-        <v>1559.88631295132</v>
+        <v>1559.886312951319</v>
       </c>
     </row>
     <row r="698">
@@ -9447,7 +9447,7 @@
         <v>2026</v>
       </c>
       <c r="D699">
-        <v>1646.928896118996</v>
+        <v>1738.009603126662</v>
       </c>
     </row>
     <row r="700">
@@ -9460,7 +9460,7 @@
         <v>2027</v>
       </c>
       <c r="D700">
-        <v>1737.566944133524</v>
+        <v>1831.863192544255</v>
       </c>
     </row>
     <row r="701">
@@ -9473,7 +9473,7 @@
         <v>2028</v>
       </c>
       <c r="D701">
-        <v>1831.610885456081</v>
+        <v>1929.987248015037</v>
       </c>
     </row>
     <row r="702">
@@ -9486,7 +9486,7 @@
         <v>2024</v>
       </c>
       <c r="D702">
-        <v>1564.181525802859</v>
+        <v>1564.181525802855</v>
       </c>
     </row>
     <row r="703">
@@ -9512,7 +9512,7 @@
         <v>2026</v>
       </c>
       <c r="D704">
-        <v>1656.352614223466</v>
+        <v>1753.488580504545</v>
       </c>
     </row>
     <row r="705">
@@ -9525,7 +9525,7 @@
         <v>2027</v>
       </c>
       <c r="D705">
-        <v>1753.242212103312</v>
+        <v>1855.045281085703</v>
       </c>
     </row>
     <row r="706">
@@ -9538,7 +9538,7 @@
         <v>2028</v>
       </c>
       <c r="D706">
-        <v>1854.907571969901</v>
+        <v>1962.046813468323</v>
       </c>
     </row>
     <row r="707">
@@ -9551,7 +9551,7 @@
         <v>2024</v>
       </c>
       <c r="D707">
-        <v>1592.952952253476</v>
+        <v>1592.952952253474</v>
       </c>
     </row>
     <row r="708">
@@ -9577,7 +9577,7 @@
         <v>2026</v>
       </c>
       <c r="D709">
-        <v>1690.037040620934</v>
+        <v>1821.368712397048</v>
       </c>
     </row>
     <row r="710">
@@ -9590,7 +9590,7 @@
         <v>2027</v>
       </c>
       <c r="D710">
-        <v>1828.06052090495</v>
+        <v>2015.978929207843</v>
       </c>
     </row>
     <row r="711">
@@ -9603,7 +9603,7 @@
         <v>2028</v>
       </c>
       <c r="D711">
-        <v>1991.111608447058</v>
+        <v>2149.824225822761</v>
       </c>
     </row>
     <row r="712">
@@ -9616,7 +9616,7 @@
         <v>2024</v>
       </c>
       <c r="D712">
-        <v>1584.841903288434</v>
+        <v>1584.841903288433</v>
       </c>
     </row>
     <row r="713">
@@ -9642,7 +9642,7 @@
         <v>2026</v>
       </c>
       <c r="D714">
-        <v>1681.542450076157</v>
+        <v>1812.294594268357</v>
       </c>
     </row>
     <row r="715">
@@ -9655,7 +9655,7 @@
         <v>2027</v>
       </c>
       <c r="D715">
-        <v>1818.896471489009</v>
+        <v>2005.794243240898</v>
       </c>
     </row>
     <row r="716">
@@ -9668,7 +9668,7 @@
         <v>2028</v>
       </c>
       <c r="D716">
-        <v>1981.058677528801</v>
+        <v>2138.83283205651</v>
       </c>
     </row>
     <row r="717">
@@ -9707,7 +9707,7 @@
         <v>2026</v>
       </c>
       <c r="D719">
-        <v>991.9413088870192</v>
+        <v>1059.715785583131</v>
       </c>
     </row>
     <row r="720">
@@ -9720,7 +9720,7 @@
         <v>2027</v>
       </c>
       <c r="D720">
-        <v>1059.746549537962</v>
+        <v>1132.377143185583</v>
       </c>
     </row>
     <row r="721">
@@ -9733,7 +9733,7 @@
         <v>2028</v>
       </c>
       <c r="D721">
-        <v>1132.384000215747</v>
+        <v>1210.042641836528</v>
       </c>
     </row>
     <row r="722">
@@ -9772,7 +9772,7 @@
         <v>2026</v>
       </c>
       <c r="D724">
-        <v>991.9413088870192</v>
+        <v>1059.715785583131</v>
       </c>
     </row>
     <row r="725">
@@ -9785,7 +9785,7 @@
         <v>2027</v>
       </c>
       <c r="D725">
-        <v>1059.746549537962</v>
+        <v>1132.377143185583</v>
       </c>
     </row>
     <row r="726">
@@ -9798,7 +9798,7 @@
         <v>2028</v>
       </c>
       <c r="D726">
-        <v>1132.384000215747</v>
+        <v>1210.042641836528</v>
       </c>
     </row>
     <row r="727">
@@ -9837,7 +9837,7 @@
         <v>2026</v>
       </c>
       <c r="D729">
-        <v>991.9413088870192</v>
+        <v>1059.715785583131</v>
       </c>
     </row>
     <row r="730">
@@ -9850,7 +9850,7 @@
         <v>2027</v>
       </c>
       <c r="D730">
-        <v>1059.746549537962</v>
+        <v>1132.377143185583</v>
       </c>
     </row>
     <row r="731">
@@ -9863,7 +9863,7 @@
         <v>2028</v>
       </c>
       <c r="D731">
-        <v>1132.384000215747</v>
+        <v>1210.042641836528</v>
       </c>
     </row>
     <row r="732">
@@ -9902,7 +9902,7 @@
         <v>2026</v>
       </c>
       <c r="D734">
-        <v>991.9413088870192</v>
+        <v>1059.715785583131</v>
       </c>
     </row>
     <row r="735">
@@ -9915,7 +9915,7 @@
         <v>2027</v>
       </c>
       <c r="D735">
-        <v>1059.746549537962</v>
+        <v>1132.377143185583</v>
       </c>
     </row>
     <row r="736">
@@ -9928,7 +9928,7 @@
         <v>2028</v>
       </c>
       <c r="D736">
-        <v>1132.384000215747</v>
+        <v>1210.042641836528</v>
       </c>
     </row>
     <row r="737">
@@ -9941,7 +9941,7 @@
         <v>2024</v>
       </c>
       <c r="D737">
-        <v>975.0892549400928</v>
+        <v>975.0892549400902</v>
       </c>
     </row>
     <row r="738">
@@ -9967,7 +9967,7 @@
         <v>2026</v>
       </c>
       <c r="D739">
-        <v>1042.49565883858</v>
+        <v>1114.703367258284</v>
       </c>
     </row>
     <row r="740">
@@ -9980,7 +9980,7 @@
         <v>2027</v>
       </c>
       <c r="D740">
-        <v>1114.756470374713</v>
+        <v>1192.234295991942</v>
       </c>
     </row>
     <row r="741">
@@ -9993,7 +9993,7 @@
         <v>2028</v>
       </c>
       <c r="D741">
-        <v>1192.25559309039</v>
+        <v>1275.226067352736</v>
       </c>
     </row>
     <row r="742">
@@ -10032,7 +10032,7 @@
         <v>2026</v>
       </c>
       <c r="D744">
-        <v>991.9413088870192</v>
+        <v>1059.715785583131</v>
       </c>
     </row>
     <row r="745">
@@ -10045,7 +10045,7 @@
         <v>2027</v>
       </c>
       <c r="D745">
-        <v>1059.746549537962</v>
+        <v>1132.377143185583</v>
       </c>
     </row>
     <row r="746">
@@ -10058,7 +10058,7 @@
         <v>2028</v>
       </c>
       <c r="D746">
-        <v>1132.384000215747</v>
+        <v>1210.042641836528</v>
       </c>
     </row>
     <row r="747">
@@ -10097,7 +10097,7 @@
         <v>2026</v>
       </c>
       <c r="D749">
-        <v>991.9413088870192</v>
+        <v>1059.715785583131</v>
       </c>
     </row>
     <row r="750">
@@ -10110,7 +10110,7 @@
         <v>2027</v>
       </c>
       <c r="D750">
-        <v>1059.746549537962</v>
+        <v>1132.377143185583</v>
       </c>
     </row>
     <row r="751">
@@ -10123,7 +10123,7 @@
         <v>2028</v>
       </c>
       <c r="D751">
-        <v>1132.384000215747</v>
+        <v>1210.042641836528</v>
       </c>
     </row>
     <row r="752">
@@ -10162,7 +10162,7 @@
         <v>2026</v>
       </c>
       <c r="D754">
-        <v>1900.351128437264</v>
+        <v>1991.844896203598</v>
       </c>
     </row>
     <row r="755">
@@ -10175,7 +10175,7 @@
         <v>2027</v>
       </c>
       <c r="D755">
-        <v>1991.543610028225</v>
+        <v>2086.313890340407</v>
       </c>
     </row>
     <row r="756">
@@ -10188,7 +10188,7 @@
         <v>2028</v>
       </c>
       <c r="D756">
-        <v>2086.107477502446</v>
+        <v>2184.614805712347</v>
       </c>
     </row>
     <row r="757">
@@ -10201,7 +10201,7 @@
         <v>2024</v>
       </c>
       <c r="D757">
-        <v>1420.265668191145</v>
+        <v>1420.265668191143</v>
       </c>
     </row>
     <row r="758">
@@ -10227,7 +10227,7 @@
         <v>2026</v>
       </c>
       <c r="D759">
-        <v>1531.710791911441</v>
+        <v>1651.952444734422</v>
       </c>
     </row>
     <row r="760">
@@ -10240,7 +10240,7 @@
         <v>2027</v>
       </c>
       <c r="D760">
-        <v>1651.957074274228</v>
+        <v>1781.703965290146</v>
       </c>
     </row>
     <row r="761">
@@ -10253,7 +10253,7 @@
         <v>2028</v>
       </c>
       <c r="D761">
-        <v>1781.704412614476</v>
+        <v>1921.648181246638</v>
       </c>
     </row>
     <row r="762">
@@ -10292,7 +10292,7 @@
         <v>2026</v>
       </c>
       <c r="D764">
-        <v>2012.668807522058</v>
+        <v>2253.128447721095</v>
       </c>
     </row>
     <row r="765">
@@ -10305,7 +10305,7 @@
         <v>2027</v>
       </c>
       <c r="D765">
-        <v>2257.79526606075</v>
+        <v>2547.560595242753</v>
       </c>
     </row>
     <row r="766">
@@ -10318,7 +10318,7 @@
         <v>2028</v>
       </c>
       <c r="D766">
-        <v>2550.469811457721</v>
+        <v>2890.34768837939</v>
       </c>
     </row>
     <row r="767">
@@ -10331,7 +10331,7 @@
         <v>2024</v>
       </c>
       <c r="D767">
-        <v>1814.329901781613</v>
+        <v>1814.32990178161</v>
       </c>
     </row>
     <row r="768">
@@ -10357,7 +10357,7 @@
         <v>2026</v>
       </c>
       <c r="D769">
-        <v>1901.804262248687</v>
+        <v>1993.00451414605</v>
       </c>
     </row>
     <row r="770">
@@ -10370,7 +10370,7 @@
         <v>2027</v>
       </c>
       <c r="D770">
-        <v>1992.680973555916</v>
+        <v>2087.046528694405</v>
       </c>
     </row>
     <row r="771">
@@ -10383,7 +10383,7 @@
         <v>2028</v>
       </c>
       <c r="D771">
-        <v>2086.823455773566</v>
+        <v>2184.825292974873</v>
       </c>
     </row>
     <row r="772">
@@ -10396,7 +10396,7 @@
         <v>2024</v>
       </c>
       <c r="D772">
-        <v>1517.421791641794</v>
+        <v>1517.42179164179</v>
       </c>
     </row>
     <row r="773">
@@ -10422,7 +10422,7 @@
         <v>2026</v>
       </c>
       <c r="D774">
-        <v>1605.29223739983</v>
+        <v>1696.871873470263</v>
       </c>
     </row>
     <row r="775">
@@ -10435,7 +10435,7 @@
         <v>2027</v>
       </c>
       <c r="D775">
-        <v>1695.749265303787</v>
+        <v>1788.66460301438</v>
       </c>
     </row>
     <row r="776">
@@ -10448,7 +10448,7 @@
         <v>2028</v>
       </c>
       <c r="D776">
-        <v>1787.700641377133</v>
+        <v>1882.376204711294</v>
       </c>
     </row>
     <row r="777">
@@ -10487,7 +10487,7 @@
         <v>2026</v>
       </c>
       <c r="D779">
-        <v>1605.90636935421</v>
+        <v>1697.452378410154</v>
       </c>
     </row>
     <row r="780">
@@ -10500,7 +10500,7 @@
         <v>2027</v>
       </c>
       <c r="D780">
-        <v>1696.322341059088</v>
+        <v>1789.176141079215</v>
       </c>
     </row>
     <row r="781">
@@ -10513,7 +10513,7 @@
         <v>2028</v>
       </c>
       <c r="D781">
-        <v>1788.203581444336</v>
+        <v>1882.782633595598</v>
       </c>
     </row>
     <row r="782">
@@ -10552,7 +10552,7 @@
         <v>2026</v>
       </c>
       <c r="D784">
-        <v>1605.90636935421</v>
+        <v>1697.452378410154</v>
       </c>
     </row>
     <row r="785">
@@ -10565,7 +10565,7 @@
         <v>2027</v>
       </c>
       <c r="D785">
-        <v>1696.322341059088</v>
+        <v>1789.176141079215</v>
       </c>
     </row>
     <row r="786">
@@ -10578,7 +10578,7 @@
         <v>2028</v>
       </c>
       <c r="D786">
-        <v>1788.203581444336</v>
+        <v>1882.782633595598</v>
       </c>
     </row>
     <row r="787">
@@ -10617,7 +10617,7 @@
         <v>2026</v>
       </c>
       <c r="D789">
-        <v>1605.906369328452</v>
+        <v>1697.452378366033</v>
       </c>
     </row>
     <row r="790">
@@ -10630,7 +10630,7 @@
         <v>2027</v>
       </c>
       <c r="D790">
-        <v>1696.322341015428</v>
+        <v>1789.176141015797</v>
       </c>
     </row>
     <row r="791">
@@ -10643,7 +10643,7 @@
         <v>2028</v>
       </c>
       <c r="D791">
-        <v>1788.203581382009</v>
+        <v>1882.782633514399</v>
       </c>
     </row>
     <row r="792">
@@ -10656,7 +10656,7 @@
         <v>2024</v>
       </c>
       <c r="D792">
-        <v>1518.058871826676</v>
+        <v>1518.058871826674</v>
       </c>
     </row>
     <row r="793">
@@ -10682,7 +10682,7 @@
         <v>2026</v>
       </c>
       <c r="D794">
-        <v>1605.906369316887</v>
+        <v>1697.452378345185</v>
       </c>
     </row>
     <row r="795">
@@ -10695,7 +10695,7 @@
         <v>2027</v>
       </c>
       <c r="D795">
-        <v>1696.322340994152</v>
+        <v>1789.176140982622</v>
       </c>
     </row>
     <row r="796">
@@ -10708,7 +10708,7 @@
         <v>2028</v>
       </c>
       <c r="D796">
-        <v>1788.203581348568</v>
+        <v>1882.782633466805</v>
       </c>
     </row>
     <row r="797">
@@ -10721,7 +10721,7 @@
         <v>2024</v>
       </c>
       <c r="D797">
-        <v>1317.162412681181</v>
+        <v>1317.162412681178</v>
       </c>
     </row>
     <row r="798">
@@ -10747,7 +10747,7 @@
         <v>2026</v>
       </c>
       <c r="D799">
-        <v>1417.643051952812</v>
+        <v>1525.858970521967</v>
       </c>
     </row>
     <row r="800">
@@ -10760,7 +10760,7 @@
         <v>2027</v>
       </c>
       <c r="D800">
-        <v>1525.881506733458</v>
+        <v>1642.483730646015</v>
       </c>
     </row>
     <row r="801">
@@ -10773,7 +10773,7 @@
         <v>2028</v>
       </c>
       <c r="D801">
-        <v>1642.491535373422</v>
+        <v>1768.047581822119</v>
       </c>
     </row>
     <row r="802">
@@ -10786,7 +10786,7 @@
         <v>2024</v>
       </c>
       <c r="D802">
-        <v>1517.313181108339</v>
+        <v>1517.313181108337</v>
       </c>
     </row>
     <row r="803">
@@ -10812,7 +10812,7 @@
         <v>2026</v>
       </c>
       <c r="D804">
-        <v>1728.505934917542</v>
+        <v>1970.809827749514</v>
       </c>
     </row>
     <row r="805">
@@ -10825,7 +10825,7 @@
         <v>2027</v>
       </c>
       <c r="D805">
-        <v>1971.175607349045</v>
+        <v>2250.290331678721</v>
       </c>
     </row>
     <row r="806">
@@ -10838,7 +10838,7 @@
         <v>2028</v>
       </c>
       <c r="D806">
-        <v>2250.379329441965</v>
+        <v>2569.708828177721</v>
       </c>
     </row>
     <row r="807">
@@ -10851,7 +10851,7 @@
         <v>2024</v>
       </c>
       <c r="D807">
-        <v>1798.802746582032</v>
+        <v>1798.802746582036</v>
       </c>
     </row>
     <row r="808">
@@ -10877,7 +10877,7 @@
         <v>2026</v>
       </c>
       <c r="D809">
-        <v>2161.187011985236</v>
+        <v>2601.599276052432</v>
       </c>
     </row>
     <row r="810">
@@ -10890,7 +10890,7 @@
         <v>2027</v>
       </c>
       <c r="D810">
-        <v>2602.761305674055</v>
+        <v>3142.024159798781</v>
       </c>
     </row>
     <row r="811">
@@ -10903,7 +10903,7 @@
         <v>2028</v>
       </c>
       <c r="D811">
-        <v>3142.348414254731</v>
+        <v>3795.885351406241</v>
       </c>
     </row>
     <row r="812">
@@ -10916,7 +10916,7 @@
         <v>2024</v>
       </c>
       <c r="D812">
-        <v>1810.45044671235</v>
+        <v>1810.450446712346</v>
       </c>
     </row>
     <row r="813">
@@ -10942,7 +10942,7 @@
         <v>2026</v>
       </c>
       <c r="D814">
-        <v>1897.963438166572</v>
+        <v>1989.215710463475</v>
       </c>
     </row>
     <row r="815">
@@ -10955,7 +10955,7 @@
         <v>2027</v>
       </c>
       <c r="D815">
-        <v>1988.892308125611</v>
+        <v>2083.324497712939</v>
       </c>
     </row>
     <row r="816">
@@ -10968,7 +10968,7 @@
         <v>2028</v>
       </c>
       <c r="D816">
-        <v>2083.101308240779</v>
+        <v>2181.184353762359</v>
       </c>
     </row>
     <row r="817">
@@ -10981,7 +10981,7 @@
         <v>2024</v>
       </c>
       <c r="D817">
-        <v>1814.329901781613</v>
+        <v>1814.32990178161</v>
       </c>
     </row>
     <row r="818">
@@ -11007,7 +11007,7 @@
         <v>2026</v>
       </c>
       <c r="D819">
-        <v>1901.804262248687</v>
+        <v>1993.00451414605</v>
       </c>
     </row>
     <row r="820">
@@ -11020,7 +11020,7 @@
         <v>2027</v>
       </c>
       <c r="D820">
-        <v>1992.680973555916</v>
+        <v>2087.046528694405</v>
       </c>
     </row>
     <row r="821">
@@ -11033,7 +11033,7 @@
         <v>2028</v>
       </c>
       <c r="D821">
-        <v>2086.823455773566</v>
+        <v>2184.825292974873</v>
       </c>
     </row>
     <row r="822">
@@ -11046,7 +11046,7 @@
         <v>2024</v>
       </c>
       <c r="D822">
-        <v>1814.329901781613</v>
+        <v>1814.32990178161</v>
       </c>
     </row>
     <row r="823">
@@ -11072,7 +11072,7 @@
         <v>2026</v>
       </c>
       <c r="D824">
-        <v>1901.804262248687</v>
+        <v>1993.00451414605</v>
       </c>
     </row>
     <row r="825">
@@ -11085,7 +11085,7 @@
         <v>2027</v>
       </c>
       <c r="D825">
-        <v>1992.680973555916</v>
+        <v>2087.046528694405</v>
       </c>
     </row>
     <row r="826">
@@ -11098,7 +11098,7 @@
         <v>2028</v>
       </c>
       <c r="D826">
-        <v>2086.823455773566</v>
+        <v>2184.825292974873</v>
       </c>
     </row>
     <row r="827">
@@ -11111,7 +11111,7 @@
         <v>2024</v>
       </c>
       <c r="D827">
-        <v>1814.329901778909</v>
+        <v>1814.329901778906</v>
       </c>
     </row>
     <row r="828">
@@ -11137,7 +11137,7 @@
         <v>2026</v>
       </c>
       <c r="D829">
-        <v>1901.80426223362</v>
+        <v>1993.004514114733</v>
       </c>
     </row>
     <row r="830">
@@ -11150,7 +11150,7 @@
         <v>2027</v>
       </c>
       <c r="D830">
-        <v>1992.680973522075</v>
+        <v>2087.046528634562</v>
       </c>
     </row>
     <row r="831">
@@ -11163,7 +11163,7 @@
         <v>2028</v>
       </c>
       <c r="D831">
-        <v>2086.823455711467</v>
+        <v>2184.825292876805</v>
       </c>
     </row>
     <row r="832">
@@ -11176,7 +11176,7 @@
         <v>2024</v>
       </c>
       <c r="D832">
-        <v>1201.28277208153</v>
+        <v>1201.282772081527</v>
       </c>
     </row>
     <row r="833">
@@ -11202,7 +11202,7 @@
         <v>2026</v>
       </c>
       <c r="D834">
-        <v>1296.417380237399</v>
+        <v>1398.286439948724</v>
       </c>
     </row>
     <row r="835">
@@ -11215,7 +11215,7 @@
         <v>2027</v>
       </c>
       <c r="D835">
-        <v>1397.776419520539</v>
+        <v>1505.649359127841</v>
       </c>
     </row>
     <row r="836">
@@ -11228,7 +11228,7 @@
         <v>2028</v>
       </c>
       <c r="D836">
-        <v>1505.2989046203</v>
+        <v>1620.123968546537</v>
       </c>
     </row>
     <row r="837">
@@ -11267,7 +11267,7 @@
         <v>2026</v>
       </c>
       <c r="D839">
-        <v>1206.608980071824</v>
+        <v>1272.765024163082</v>
       </c>
     </row>
     <row r="840">
@@ -11280,7 +11280,7 @@
         <v>2027</v>
       </c>
       <c r="D840">
-        <v>1272.845232450096</v>
+        <v>1342.983735257462</v>
       </c>
     </row>
     <row r="841">
@@ -11293,7 +11293,7 @@
         <v>2028</v>
       </c>
       <c r="D841">
-        <v>1343.023168094161</v>
+        <v>1417.201255975761</v>
       </c>
     </row>
     <row r="842">
@@ -11332,7 +11332,7 @@
         <v>2026</v>
       </c>
       <c r="D844">
-        <v>1208.161309020305</v>
+        <v>1275.160662789741</v>
       </c>
     </row>
     <row r="845">
@@ -11345,7 +11345,7 @@
         <v>2027</v>
       </c>
       <c r="D845">
-        <v>1275.254050000017</v>
+        <v>1346.389753044363</v>
       </c>
     </row>
     <row r="846">
@@ -11358,7 +11358,7 @@
         <v>2028</v>
       </c>
       <c r="D846">
-        <v>1346.434239295974</v>
+        <v>1421.738541223259</v>
       </c>
     </row>
     <row r="847">
@@ -11371,7 +11371,7 @@
         <v>2024</v>
       </c>
       <c r="D847">
-        <v>989.0958816970813</v>
+        <v>989.0958816970777</v>
       </c>
     </row>
     <row r="848">
@@ -11397,7 +11397,7 @@
         <v>2026</v>
       </c>
       <c r="D849">
-        <v>1066.216920638724</v>
+        <v>1149.376966302065</v>
       </c>
     </row>
     <row r="850">
@@ -11410,7 +11410,7 @@
         <v>2027</v>
       </c>
       <c r="D850">
-        <v>1149.386108155766</v>
+        <v>1239.080475660327</v>
       </c>
     </row>
     <row r="851">
@@ -11423,7 +11423,7 @@
         <v>2028</v>
       </c>
       <c r="D851">
-        <v>1239.083969970697</v>
+        <v>1335.796226484521</v>
       </c>
     </row>
     <row r="852">
@@ -11436,7 +11436,7 @@
         <v>2024</v>
       </c>
       <c r="D852">
-        <v>1485.770376560127</v>
+        <v>1485.770376560128</v>
       </c>
     </row>
     <row r="853">
@@ -11462,7 +11462,7 @@
         <v>2026</v>
       </c>
       <c r="D854">
-        <v>1722.393094134249</v>
+        <v>1999.972551653459</v>
       </c>
     </row>
     <row r="855">
@@ -11475,7 +11475,7 @@
         <v>2027</v>
       </c>
       <c r="D855">
-        <v>2000.920867045066</v>
+        <v>2329.402882970619</v>
       </c>
     </row>
     <row r="856">
@@ -11488,7 +11488,7 @@
         <v>2028</v>
       </c>
       <c r="D856">
-        <v>2329.722574584779</v>
+        <v>2714.213335092657</v>
       </c>
     </row>
     <row r="857">
@@ -11527,7 +11527,7 @@
         <v>2026</v>
       </c>
       <c r="D859">
-        <v>1441.65460013753</v>
+        <v>1517.493113656014</v>
       </c>
     </row>
     <row r="860">
@@ -11540,7 +11540,7 @@
         <v>2027</v>
       </c>
       <c r="D860">
-        <v>1517.493487579189</v>
+        <v>1597.315536320434</v>
       </c>
     </row>
     <row r="861">
@@ -11553,7 +11553,7 @@
         <v>2028</v>
       </c>
       <c r="D861">
-        <v>1597.315513441287</v>
+        <v>1681.336666357585</v>
       </c>
     </row>
     <row r="862">
@@ -11566,7 +11566,7 @@
         <v>2024</v>
       </c>
       <c r="D862">
-        <v>1065.50339659177</v>
+        <v>1065.503396591767</v>
       </c>
     </row>
     <row r="863">
@@ -11592,7 +11592,7 @@
         <v>2026</v>
       </c>
       <c r="D864">
-        <v>1224.04114820928</v>
+        <v>1407.892765896542</v>
       </c>
     </row>
     <row r="865">
@@ -11605,7 +11605,7 @@
         <v>2027</v>
       </c>
       <c r="D865">
-        <v>1407.581198408635</v>
+        <v>1620.269128012004</v>
       </c>
     </row>
     <row r="866">
@@ -11618,7 +11618,7 @@
         <v>2028</v>
       </c>
       <c r="D866">
-        <v>1620.333874923414</v>
+        <v>1864.905371794094</v>
       </c>
     </row>
   </sheetData>
